--- a/data/Desvios de DTOs.xlsx
+++ b/data/Desvios de DTOs.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89871FDE-CEF9-4F6B-B417-1803E33DB3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EA4D24-3089-4D37-8159-0C4CE3366699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$576</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="551">
   <si>
     <t>Colaborador</t>
   </si>
@@ -1209,6 +1212,486 @@
   </si>
   <si>
     <t>Execução Segura de Direção de equipamentos motorizados ( Empilhadeira e Máquina de limpeza)</t>
+  </si>
+  <si>
+    <t>Não fechou a corrente da TC.</t>
+  </si>
+  <si>
+    <t>Feito o ver e agir, ajudante foi orientado sobre o processo de fechar a corrente.</t>
+  </si>
+  <si>
+    <t>ROBERTO SANTOS VALE</t>
+  </si>
+  <si>
+    <t>Chave está na porta do caminhão na execução da atividade.</t>
+  </si>
+  <si>
+    <t>Treinamento de controle de chaves.</t>
+  </si>
+  <si>
+    <t>Ajudante não fez o checklist da paleteira</t>
+  </si>
+  <si>
+    <t>Orientação ao ajudante de quando utilizar um equipamento sempre fazer o checklist antes</t>
+  </si>
+  <si>
+    <t>CARLOS HENRIQUE MACHADO LIMA</t>
+  </si>
+  <si>
+    <t>Colaborador puxou a paleteira ao invés de empurrar</t>
+  </si>
+  <si>
+    <t>Orientei o mesmo para empurrar a paleteira.</t>
+  </si>
+  <si>
+    <t>GUSTAVO CALEB PHELIPPE ALVES BATISTA</t>
+  </si>
+  <si>
+    <t>Colaborador nao estava usando a cinta.</t>
+  </si>
+  <si>
+    <t>Orientei o mesmo a colocar a cinta lombar e expliquei a importância de usar a cinta.</t>
+  </si>
+  <si>
+    <t>VILTON SEBASTIAO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Ausência de check de pré uso e uso da luva inadequada</t>
+  </si>
+  <si>
+    <t>Usar lugar correta e criar um check de pré uso antes da descarga. Construir um linha de vida.</t>
+  </si>
+  <si>
+    <t>Execução segura de segregação</t>
+  </si>
+  <si>
+    <t>Retreinar time</t>
+  </si>
+  <si>
+    <t>Colaborador não fechou a segregação quando foi passar o stretch no palete</t>
+  </si>
+  <si>
+    <t>Orientei o mesmobsobre a importância de fechar a segregação</t>
+  </si>
+  <si>
+    <t>Estava deixando a chave em cima do painel</t>
+  </si>
+  <si>
+    <t>Treinamento de controle de chave</t>
+  </si>
+  <si>
+    <t>Controle de chave não foi feito corretamente</t>
+  </si>
+  <si>
+    <t>Realizado ver e agir com o colaborador. Em seguida o bloqueio de energia foi realizado corretamente.</t>
+  </si>
+  <si>
+    <t>EVERTON DIOGO FERNANDES CAMBUY</t>
+  </si>
+  <si>
+    <t>Condutor andando de frente com carga nos cargos, orientados no ato.</t>
+  </si>
+  <si>
+    <t>Treinamento padrão de manuseio de empilhadeira.</t>
+  </si>
+  <si>
+    <t>Não segregou a área da amarração</t>
+  </si>
+  <si>
+    <t>Foi abordado no ato. Relato de segurança.</t>
+  </si>
+  <si>
+    <t>Não fez o check list da paleteira</t>
+  </si>
+  <si>
+    <t>Relato de segurança.Abordagem no ato do ocorrido</t>
+  </si>
+  <si>
+    <t>não segregou a área</t>
+  </si>
+  <si>
+    <t>Foi abordado no ato e feito relato de segurança</t>
+  </si>
+  <si>
+    <t>Execução Segura de Prevenção da Violência</t>
+  </si>
+  <si>
+    <t>Não realizou, check-list de palheteira</t>
+  </si>
+  <si>
+    <t>Ver e agir</t>
+  </si>
+  <si>
+    <t>ARCELINO DA SILVA</t>
+  </si>
+  <si>
+    <t>Ao estacionar o veículo para carregamento a chave fixa na ignição do veiculo</t>
+  </si>
+  <si>
+    <t>Realizado ver e agir sobre controle de chaves.</t>
+  </si>
+  <si>
+    <t>GABRIEL VARELA DE LIMA</t>
+  </si>
+  <si>
+    <t>Colaborador não tinha realizado checklist de paleteira</t>
+  </si>
+  <si>
+    <t>Estava sem conexão com a internet</t>
+  </si>
+  <si>
+    <t>DOUGLAS GOMES DA SILVA</t>
+  </si>
+  <si>
+    <t>A chave estava na caixinha, mas a caixinha não estava travada</t>
+  </si>
+  <si>
+    <t>Reciclagem no padrão de controle de chave para os operadores do turno Feito ver e agir imediato</t>
+  </si>
+  <si>
+    <t>Ausência de cinta lembrar.</t>
+  </si>
+  <si>
+    <t>Solicitar cinta lombar Verificar  padrão sobre uso de cinta para amareador</t>
+  </si>
+  <si>
+    <t>Manobrista não utilizou o crachá de identificação pois esqueceu em casa.</t>
+  </si>
+  <si>
+    <t>Orientado sobre a importância da utilização do crachá para vigência do caminhão.</t>
+  </si>
+  <si>
+    <t>WESLEY DOS REIS SANTOS</t>
+  </si>
+  <si>
+    <t>Pegando pallet de uma pilha com mais de 10 pallets de altura.</t>
+  </si>
+  <si>
+    <t>Orientação e solicitação para operador reduzir o tamanho das pilhas de pallets.</t>
+  </si>
+  <si>
+    <t>ADRYAN FELIPE MORAES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Colaborador não estava utilizando o cinto lombar</t>
+  </si>
+  <si>
+    <t>MDT verbal Treinar 100 do Time para que o checkList da paleteira seja feito de formaCorreta e o uso de cinto lombadas.</t>
+  </si>
+  <si>
+    <t>TAINAN LUCAS LOPES SANTOS</t>
+  </si>
+  <si>
+    <t>Trabalhando com fone de ouvido.</t>
+  </si>
+  <si>
+    <t>Relato de segurança. Foi abordado no ato. E pedido pra tirar</t>
+  </si>
+  <si>
+    <t>Uso de adorno</t>
+  </si>
+  <si>
+    <t>Foi abordado no ato e relato de segurança</t>
+  </si>
+  <si>
+    <t>Havia tirado o óculos para olhar um palete</t>
+  </si>
+  <si>
+    <t>Orientado colocar o óculos mesmo que não esteja operando,  precisa usar o óculos estando no armazém</t>
+  </si>
+  <si>
+    <t>EVERTON BISPO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Jogou a caixaria.</t>
+  </si>
+  <si>
+    <t>O mesmo foi orientado a não jogar e sim colocar, risco de quebra e estouro de garrafa.</t>
+  </si>
+  <si>
+    <t>KAUA CORDEIRO DUARTE CORREA</t>
+  </si>
+  <si>
+    <t>Soprador com o bico pra cima no balcão</t>
+  </si>
+  <si>
+    <t>Foi instruído sobre o correto e conscientizado sobre os riscos.</t>
+  </si>
+  <si>
+    <t>LUIZ ROGERIO DA SILVA SEUANES</t>
+  </si>
+  <si>
+    <t>Estava puxando ao invés de empurrar</t>
+  </si>
+  <si>
+    <t>Foi orientado sobre o uso correto da paleteira. Risco de queda do pallet.</t>
+  </si>
+  <si>
+    <t>RAQUEL LUIZA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Passou fora da faixa de pedestre</t>
+  </si>
+  <si>
+    <t>Treinamento sobre a importância do uso da faixa de pedestre</t>
+  </si>
+  <si>
+    <t>Passar fora da faixa de pedestre</t>
+  </si>
+  <si>
+    <t>Manobrista instruída da importância do uso da faixa de pedestre</t>
+  </si>
+  <si>
+    <t>EVERTON FELIPE CARNIEL</t>
+  </si>
+  <si>
+    <t>Não bloqueou a chave da carreta.</t>
+  </si>
+  <si>
+    <t>Aplicar MTD.</t>
+  </si>
+  <si>
+    <t>EDIMILSON DE ARAUJO SILVA</t>
+  </si>
+  <si>
+    <t>Não uso de cone para sinalização da área e falta de acessibilidade ao padrão</t>
+  </si>
+  <si>
+    <t>Direcionado a supervisora ter cone disponível para o colaborador</t>
+  </si>
+  <si>
+    <t>Montando produto avariado</t>
+  </si>
+  <si>
+    <t>Realizado feedback com colaborador</t>
+  </si>
+  <si>
+    <t>BRUNO DE SOUZA</t>
+  </si>
+  <si>
+    <t>Pendência no check list</t>
+  </si>
+  <si>
+    <t>Treinamento para realização de check list</t>
+  </si>
+  <si>
+    <t>JULIO CESAR MANSO COSTA</t>
+  </si>
+  <si>
+    <t>Treinamento para realização do check list</t>
+  </si>
+  <si>
+    <t>JOSÉ ALVES SOBRINHO</t>
+  </si>
+  <si>
+    <t>Não utilizou o plano de trafego</t>
+  </si>
+  <si>
+    <t>Treinamento com time de segurança com foco no plano de tráfego interno do armazém</t>
+  </si>
+  <si>
+    <t>JONATHAN ASSUMPCAO DA SILVA</t>
+  </si>
+  <si>
+    <t>A chave estava na ignição</t>
+  </si>
+  <si>
+    <t>Treinar mecânico no processo de controle de chave</t>
+  </si>
+  <si>
+    <t>Falta de 5s na área do carregamento</t>
+  </si>
+  <si>
+    <t>Realizar o 5s na área do carregamento</t>
+  </si>
+  <si>
+    <t>IGOR DE OLIVEIRA DEMARCHI</t>
+  </si>
+  <si>
+    <t>Colaborador puxando a paleteira, o correto seria empurrar a mesma.</t>
+  </si>
+  <si>
+    <t>Colaborador realizou a tarefa no padrão, porém teve um pequeno desvio, passei a orientação correta</t>
+  </si>
+  <si>
+    <t>Nao segregou a area de amarração</t>
+  </si>
+  <si>
+    <t>Abordagem no ato. E relato de segurança</t>
+  </si>
+  <si>
+    <t>EDNALDO RODRIGUES LOPES</t>
+  </si>
+  <si>
+    <t>Chave na ignição durante o abastecimento e sem utilização dos epis Luva PVC/Capacete</t>
+  </si>
+  <si>
+    <t>Orientado no Ato para realizar o bloqueio de chave e colocar os epis necessários para a atividade</t>
+  </si>
+  <si>
+    <t>DEIVISSON CAUA DA SILVA PINTO</t>
+  </si>
+  <si>
+    <t>Puxando paleteira</t>
+  </si>
+  <si>
+    <t>Passei orientação correta sobre a atividade.</t>
+  </si>
+  <si>
+    <t>Trafegando fora da faixa</t>
+  </si>
+  <si>
+    <t>Agordado no ato e relato de segurança</t>
+  </si>
+  <si>
+    <t>LUCAS CORREA SOUZA</t>
+  </si>
+  <si>
+    <t>Colaborador puxando a paleteira</t>
+  </si>
+  <si>
+    <t>Orientação para o mesmo, sobre a segurança de puxar.</t>
+  </si>
+  <si>
+    <t>VINICIUS BARRETO PIRES</t>
+  </si>
+  <si>
+    <t>Orientação correta sobre o ato, os perigos e expliquei que o correto seria empurrar.</t>
+  </si>
+  <si>
+    <t>Manuseio de latas inadequado pelas laterais podendo gerar avarias</t>
+  </si>
+  <si>
+    <t>Feedback realizado sobre o manuseio manual e como podem contribuir na redução de avarias.</t>
+  </si>
+  <si>
+    <t>Realização de check-list, soprador antes da utilização</t>
+  </si>
+  <si>
+    <t>Falta de 5s no repack</t>
+  </si>
+  <si>
+    <t>Direcionar um ajudantes para organização da área</t>
+  </si>
+  <si>
+    <t>MOISES FLOR REIS</t>
+  </si>
+  <si>
+    <t>Uso de ardono</t>
+  </si>
+  <si>
+    <t>Abordagem no ato e relato de segurança Colaborador em fase de treinamento</t>
+  </si>
+  <si>
+    <t>VALDENILSON JESUS SANTOS</t>
+  </si>
+  <si>
+    <t>Movimento paleteira</t>
+  </si>
+  <si>
+    <t>Colaborador puxando a paleteira, o correto seria empurrar.</t>
+  </si>
+  <si>
+    <t>Não foi segredo a chave do caminhão</t>
+  </si>
+  <si>
+    <t>Relato de segurança</t>
+  </si>
+  <si>
+    <t>RICARDO AMERICO DA SILVA</t>
+  </si>
+  <si>
+    <t>Checklist não realizado</t>
+  </si>
+  <si>
+    <t>Retreinar colaborador no check da bateria do tablet no final do turno</t>
+  </si>
+  <si>
+    <t>JOEL ARAUJO DE LIMA</t>
+  </si>
+  <si>
+    <t>5s na rua da empurrada NOK</t>
+  </si>
+  <si>
+    <t>Direcionar ajudante para realizar o 5s quando tiver oportunidade Trocar bota do Colaborador</t>
+  </si>
+  <si>
+    <t>5s nok na maria mole</t>
+  </si>
+  <si>
+    <t>Realizar o 5s na maria mole</t>
+  </si>
+  <si>
+    <t>5s na maria mole nok</t>
+  </si>
+  <si>
+    <t>Realizar o 5s na rua da empurrada.</t>
+  </si>
+  <si>
+    <t>5s nok</t>
+  </si>
+  <si>
+    <t>Realizar 5s na maria mole.</t>
+  </si>
+  <si>
+    <t>LUCIANO DE ALMEIDA ALVES</t>
+  </si>
+  <si>
+    <t>Caixinha quebrada</t>
+  </si>
+  <si>
+    <t>Realizar a troca da caixinha do caminhão</t>
+  </si>
+  <si>
+    <t>RONALDO VIEIRA DE ANDRADE</t>
+  </si>
+  <si>
+    <t>FELIPE AKIM SANT ANNA DE SOUZA</t>
+  </si>
+  <si>
+    <t>Empurrando paleteira</t>
+  </si>
+  <si>
+    <t>Colaborador realizou a tarefa, porém estava empurrando a paleteira. Orientei o mesmo sobre o padrão e por conta da própria segurança.</t>
+  </si>
+  <si>
+    <t>CESAR ALEXANDER MEDINA PERAZA</t>
+  </si>
+  <si>
+    <t>Colaborador pegando caixa de pet pelas alças</t>
+  </si>
+  <si>
+    <t>Colaborador foi orientado a executar manuseio Manual de forma correta ..</t>
+  </si>
+  <si>
+    <t>RUAN GABRIEL DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t>Colaborador descarregando caixaria por pilha.</t>
+  </si>
+  <si>
+    <t>Colaborador Orientado e descarregar caixarias por lastros e não por pilha.Orientado a sempre colocar o fitilho antes de subir a paleteira com caixarias.Colaborador apresenta dificuldade de montagem em paletes complexos com.produtos de diferentes tamanhos.</t>
+  </si>
+  <si>
+    <t>Operador que estava utilizando a empilhadeira desceu e deixou ligada para o abastecer Gildo pegar ela, precisamos providenciar bota e luva para cada abastecer que fique individual de cada um.</t>
+  </si>
+  <si>
+    <t>No momento do ato abordamos operador que deixou empilhadeira ligada, acho importante reforçar isso com todos.Resolver sobre os epis (bota e luvas), que são utilizados por todos abastecedor</t>
+  </si>
+  <si>
+    <t>EDSON JOSE BISPO</t>
+  </si>
+  <si>
+    <t>Colaborador não está utilizando a cinta lombar, advertido verbalmente e orientado sobre a importância da utilização do EPIs, em caso de recorrência está ciente das consequências</t>
+  </si>
+  <si>
+    <t>O colaborador é novo na função e ainda está em fase de aprendizado, em processo de desenvolvimento das habilidades conforme o SOP.</t>
+  </si>
+  <si>
+    <t>Não segregou a cheve do caminhão na caixinha de bloqueio</t>
+  </si>
+  <si>
+    <t>Foi a bordado no ato da ocorrencia.Relato de segurança</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +2044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}">
-  <dimension ref="A1:D576"/>
+  <dimension ref="A1:F646"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
@@ -9634,7 +10117,1411 @@
         <v>390</v>
       </c>
     </row>
+    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>118</v>
+      </c>
+      <c r="B577" t="s">
+        <v>11</v>
+      </c>
+      <c r="C577" s="1">
+        <v>45933</v>
+      </c>
+      <c r="D577" t="s">
+        <v>360</v>
+      </c>
+      <c r="E577" t="s">
+        <v>391</v>
+      </c>
+      <c r="F577" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>393</v>
+      </c>
+      <c r="B578" t="s">
+        <v>11</v>
+      </c>
+      <c r="C578" s="1">
+        <v>45933</v>
+      </c>
+      <c r="D578" t="s">
+        <v>378</v>
+      </c>
+      <c r="E578" t="s">
+        <v>394</v>
+      </c>
+      <c r="F578" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>393</v>
+      </c>
+      <c r="B579" t="s">
+        <v>11</v>
+      </c>
+      <c r="C579" s="1">
+        <v>45933</v>
+      </c>
+      <c r="D579" t="s">
+        <v>355</v>
+      </c>
+      <c r="E579" t="s">
+        <v>394</v>
+      </c>
+      <c r="F579" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>393</v>
+      </c>
+      <c r="B580" t="s">
+        <v>11</v>
+      </c>
+      <c r="C580" s="1">
+        <v>45933</v>
+      </c>
+      <c r="D580" t="s">
+        <v>388</v>
+      </c>
+      <c r="E580" t="s">
+        <v>394</v>
+      </c>
+      <c r="F580" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>393</v>
+      </c>
+      <c r="B581" t="s">
+        <v>11</v>
+      </c>
+      <c r="C581" s="1">
+        <v>45933</v>
+      </c>
+      <c r="D581" t="s">
+        <v>360</v>
+      </c>
+      <c r="E581" t="s">
+        <v>394</v>
+      </c>
+      <c r="F581" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>214</v>
+      </c>
+      <c r="B582" t="s">
+        <v>192</v>
+      </c>
+      <c r="C582" s="1">
+        <v>45936</v>
+      </c>
+      <c r="D582" t="s">
+        <v>362</v>
+      </c>
+      <c r="E582" t="s">
+        <v>396</v>
+      </c>
+      <c r="F582" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>398</v>
+      </c>
+      <c r="B583" t="s">
+        <v>13</v>
+      </c>
+      <c r="C583" s="1">
+        <v>45938</v>
+      </c>
+      <c r="D583" t="s">
+        <v>362</v>
+      </c>
+      <c r="E583" t="s">
+        <v>399</v>
+      </c>
+      <c r="F583" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>401</v>
+      </c>
+      <c r="B584" t="s">
+        <v>13</v>
+      </c>
+      <c r="C584" s="1">
+        <v>45938</v>
+      </c>
+      <c r="D584" t="s">
+        <v>353</v>
+      </c>
+      <c r="E584" t="s">
+        <v>402</v>
+      </c>
+      <c r="F584" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>404</v>
+      </c>
+      <c r="B585" t="s">
+        <v>8</v>
+      </c>
+      <c r="C585" s="1">
+        <v>45940</v>
+      </c>
+      <c r="D585" t="s">
+        <v>386</v>
+      </c>
+      <c r="E585" t="s">
+        <v>405</v>
+      </c>
+      <c r="F585" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>10</v>
+      </c>
+      <c r="B586" t="s">
+        <v>11</v>
+      </c>
+      <c r="C586" s="1">
+        <v>45954</v>
+      </c>
+      <c r="D586" t="s">
+        <v>360</v>
+      </c>
+      <c r="E586" t="s">
+        <v>407</v>
+      </c>
+      <c r="F586" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>111</v>
+      </c>
+      <c r="B587" t="s">
+        <v>13</v>
+      </c>
+      <c r="C587" s="1">
+        <v>45955</v>
+      </c>
+      <c r="D587" t="s">
+        <v>360</v>
+      </c>
+      <c r="E587" t="s">
+        <v>409</v>
+      </c>
+      <c r="F587" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
+        <v>221</v>
+      </c>
+      <c r="B588" t="s">
+        <v>192</v>
+      </c>
+      <c r="C588" s="1">
+        <v>45957</v>
+      </c>
+      <c r="D588" t="s">
+        <v>355</v>
+      </c>
+      <c r="E588" t="s">
+        <v>411</v>
+      </c>
+      <c r="F588" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
+        <v>98</v>
+      </c>
+      <c r="B589" t="s">
+        <v>19</v>
+      </c>
+      <c r="C589" s="1">
+        <v>45958</v>
+      </c>
+      <c r="D589" t="s">
+        <v>355</v>
+      </c>
+      <c r="E589" t="s">
+        <v>413</v>
+      </c>
+      <c r="F589" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>415</v>
+      </c>
+      <c r="B590" t="s">
+        <v>11</v>
+      </c>
+      <c r="C590" s="1">
+        <v>45962</v>
+      </c>
+      <c r="D590" t="s">
+        <v>378</v>
+      </c>
+      <c r="E590" t="s">
+        <v>416</v>
+      </c>
+      <c r="F590" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>343</v>
+      </c>
+      <c r="B591" t="s">
+        <v>8</v>
+      </c>
+      <c r="C591" s="1">
+        <v>45964</v>
+      </c>
+      <c r="D591" t="s">
+        <v>360</v>
+      </c>
+      <c r="E591" t="s">
+        <v>418</v>
+      </c>
+      <c r="F591" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>307</v>
+      </c>
+      <c r="B592" t="s">
+        <v>8</v>
+      </c>
+      <c r="C592" s="1">
+        <v>45964</v>
+      </c>
+      <c r="D592" t="s">
+        <v>386</v>
+      </c>
+      <c r="E592" t="s">
+        <v>420</v>
+      </c>
+      <c r="F592" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
+        <v>186</v>
+      </c>
+      <c r="B593" t="s">
+        <v>8</v>
+      </c>
+      <c r="C593" s="1">
+        <v>45964</v>
+      </c>
+      <c r="D593" t="s">
+        <v>360</v>
+      </c>
+      <c r="E593" t="s">
+        <v>422</v>
+      </c>
+      <c r="F593" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
+        <v>71</v>
+      </c>
+      <c r="B594" t="s">
+        <v>19</v>
+      </c>
+      <c r="C594" s="1">
+        <v>45967</v>
+      </c>
+      <c r="D594" t="s">
+        <v>424</v>
+      </c>
+      <c r="E594" t="s">
+        <v>425</v>
+      </c>
+      <c r="F594" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>427</v>
+      </c>
+      <c r="B595" t="s">
+        <v>19</v>
+      </c>
+      <c r="C595" s="1">
+        <v>45973</v>
+      </c>
+      <c r="D595" t="s">
+        <v>355</v>
+      </c>
+      <c r="E595" t="s">
+        <v>428</v>
+      </c>
+      <c r="F595" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>430</v>
+      </c>
+      <c r="B596" t="s">
+        <v>19</v>
+      </c>
+      <c r="C596" s="1">
+        <v>45973</v>
+      </c>
+      <c r="D596" t="s">
+        <v>368</v>
+      </c>
+      <c r="E596" t="s">
+        <v>431</v>
+      </c>
+      <c r="F596" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>430</v>
+      </c>
+      <c r="B597" t="s">
+        <v>19</v>
+      </c>
+      <c r="C597" s="1">
+        <v>45973</v>
+      </c>
+      <c r="D597" t="s">
+        <v>386</v>
+      </c>
+      <c r="E597" t="s">
+        <v>431</v>
+      </c>
+      <c r="F597" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>433</v>
+      </c>
+      <c r="B598" t="s">
+        <v>5</v>
+      </c>
+      <c r="C598" s="1">
+        <v>45974</v>
+      </c>
+      <c r="D598" t="s">
+        <v>355</v>
+      </c>
+      <c r="E598" t="s">
+        <v>434</v>
+      </c>
+      <c r="F598" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>118</v>
+      </c>
+      <c r="B599" t="s">
+        <v>11</v>
+      </c>
+      <c r="C599" s="1">
+        <v>45978</v>
+      </c>
+      <c r="D599" t="s">
+        <v>357</v>
+      </c>
+      <c r="E599" t="s">
+        <v>436</v>
+      </c>
+      <c r="F599" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>65</v>
+      </c>
+      <c r="B600" t="s">
+        <v>13</v>
+      </c>
+      <c r="C600" s="1">
+        <v>45979</v>
+      </c>
+      <c r="D600" t="s">
+        <v>364</v>
+      </c>
+      <c r="E600" t="s">
+        <v>438</v>
+      </c>
+      <c r="F600" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>440</v>
+      </c>
+      <c r="B601" t="s">
+        <v>54</v>
+      </c>
+      <c r="C601" s="1">
+        <v>45980</v>
+      </c>
+      <c r="D601" t="s">
+        <v>353</v>
+      </c>
+      <c r="E601" t="s">
+        <v>441</v>
+      </c>
+      <c r="F601" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>443</v>
+      </c>
+      <c r="B602" t="s">
+        <v>8</v>
+      </c>
+      <c r="C602" s="1">
+        <v>45988</v>
+      </c>
+      <c r="D602" t="s">
+        <v>353</v>
+      </c>
+      <c r="E602" t="s">
+        <v>444</v>
+      </c>
+      <c r="F602" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>446</v>
+      </c>
+      <c r="B603" t="s">
+        <v>8</v>
+      </c>
+      <c r="C603" s="1">
+        <v>45989</v>
+      </c>
+      <c r="D603" t="s">
+        <v>357</v>
+      </c>
+      <c r="E603" t="s">
+        <v>447</v>
+      </c>
+      <c r="F603" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>307</v>
+      </c>
+      <c r="B604" t="s">
+        <v>8</v>
+      </c>
+      <c r="C604" s="1">
+        <v>45996</v>
+      </c>
+      <c r="D604" t="s">
+        <v>353</v>
+      </c>
+      <c r="E604" t="s">
+        <v>449</v>
+      </c>
+      <c r="F604" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>415</v>
+      </c>
+      <c r="B605" t="s">
+        <v>11</v>
+      </c>
+      <c r="C605" s="1">
+        <v>46001</v>
+      </c>
+      <c r="D605" t="s">
+        <v>357</v>
+      </c>
+      <c r="E605" t="s">
+        <v>451</v>
+      </c>
+      <c r="F605" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>453</v>
+      </c>
+      <c r="B606" t="s">
+        <v>13</v>
+      </c>
+      <c r="C606" s="1">
+        <v>46003</v>
+      </c>
+      <c r="D606" t="s">
+        <v>362</v>
+      </c>
+      <c r="E606" t="s">
+        <v>454</v>
+      </c>
+      <c r="F606" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>453</v>
+      </c>
+      <c r="B607" t="s">
+        <v>13</v>
+      </c>
+      <c r="C607" s="1">
+        <v>46003</v>
+      </c>
+      <c r="D607" t="s">
+        <v>353</v>
+      </c>
+      <c r="E607" t="s">
+        <v>454</v>
+      </c>
+      <c r="F607" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>456</v>
+      </c>
+      <c r="B608" t="s">
+        <v>13</v>
+      </c>
+      <c r="C608" s="1">
+        <v>46003</v>
+      </c>
+      <c r="D608" t="s">
+        <v>357</v>
+      </c>
+      <c r="E608" t="s">
+        <v>457</v>
+      </c>
+      <c r="F608" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>459</v>
+      </c>
+      <c r="B609" t="s">
+        <v>13</v>
+      </c>
+      <c r="C609" s="1">
+        <v>46003</v>
+      </c>
+      <c r="D609" t="s">
+        <v>362</v>
+      </c>
+      <c r="E609" t="s">
+        <v>460</v>
+      </c>
+      <c r="F609" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>462</v>
+      </c>
+      <c r="B610" t="s">
+        <v>192</v>
+      </c>
+      <c r="C610" s="1">
+        <v>46003</v>
+      </c>
+      <c r="D610" t="s">
+        <v>368</v>
+      </c>
+      <c r="E610" t="s">
+        <v>463</v>
+      </c>
+      <c r="F610" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>221</v>
+      </c>
+      <c r="B611" t="s">
+        <v>192</v>
+      </c>
+      <c r="C611" s="1">
+        <v>46006</v>
+      </c>
+      <c r="D611" t="s">
+        <v>368</v>
+      </c>
+      <c r="E611" t="s">
+        <v>465</v>
+      </c>
+      <c r="F611" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>467</v>
+      </c>
+      <c r="B612" t="s">
+        <v>54</v>
+      </c>
+      <c r="C612" s="1">
+        <v>46006</v>
+      </c>
+      <c r="D612" t="s">
+        <v>355</v>
+      </c>
+      <c r="E612" t="s">
+        <v>468</v>
+      </c>
+      <c r="F612" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>470</v>
+      </c>
+      <c r="B613" t="s">
+        <v>5</v>
+      </c>
+      <c r="C613" s="1">
+        <v>46009</v>
+      </c>
+      <c r="D613" t="s">
+        <v>360</v>
+      </c>
+      <c r="E613" t="s">
+        <v>471</v>
+      </c>
+      <c r="F613" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A614" t="s">
+        <v>135</v>
+      </c>
+      <c r="B614" t="s">
+        <v>54</v>
+      </c>
+      <c r="C614" s="1">
+        <v>46009</v>
+      </c>
+      <c r="D614" t="s">
+        <v>353</v>
+      </c>
+      <c r="E614" t="s">
+        <v>473</v>
+      </c>
+      <c r="F614" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
+        <v>475</v>
+      </c>
+      <c r="B615" t="s">
+        <v>192</v>
+      </c>
+      <c r="C615" s="1">
+        <v>46022</v>
+      </c>
+      <c r="D615" t="s">
+        <v>362</v>
+      </c>
+      <c r="E615" t="s">
+        <v>476</v>
+      </c>
+      <c r="F615" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A616" t="s">
+        <v>478</v>
+      </c>
+      <c r="B616" t="s">
+        <v>192</v>
+      </c>
+      <c r="C616" s="1">
+        <v>46022</v>
+      </c>
+      <c r="D616" t="s">
+        <v>362</v>
+      </c>
+      <c r="E616" t="s">
+        <v>476</v>
+      </c>
+      <c r="F616" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A617" t="s">
+        <v>480</v>
+      </c>
+      <c r="B617" t="s">
+        <v>15</v>
+      </c>
+      <c r="C617" s="1">
+        <v>46025</v>
+      </c>
+      <c r="D617" t="s">
+        <v>368</v>
+      </c>
+      <c r="E617" t="s">
+        <v>481</v>
+      </c>
+      <c r="F617" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A618" t="s">
+        <v>483</v>
+      </c>
+      <c r="B618" t="s">
+        <v>192</v>
+      </c>
+      <c r="C618" s="1">
+        <v>46028</v>
+      </c>
+      <c r="D618" t="s">
+        <v>355</v>
+      </c>
+      <c r="E618" t="s">
+        <v>484</v>
+      </c>
+      <c r="F618" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A619" t="s">
+        <v>389</v>
+      </c>
+      <c r="B619" t="s">
+        <v>5</v>
+      </c>
+      <c r="C619" s="1">
+        <v>46043</v>
+      </c>
+      <c r="D619" t="s">
+        <v>357</v>
+      </c>
+      <c r="E619" t="s">
+        <v>486</v>
+      </c>
+      <c r="F619" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A620" t="s">
+        <v>488</v>
+      </c>
+      <c r="B620" t="s">
+        <v>5</v>
+      </c>
+      <c r="C620" s="1">
+        <v>46044</v>
+      </c>
+      <c r="D620" t="s">
+        <v>362</v>
+      </c>
+      <c r="E620" t="s">
+        <v>489</v>
+      </c>
+      <c r="F620" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A621" t="s">
+        <v>343</v>
+      </c>
+      <c r="B621" t="s">
+        <v>8</v>
+      </c>
+      <c r="C621" s="1">
+        <v>46045</v>
+      </c>
+      <c r="D621" t="s">
+        <v>387</v>
+      </c>
+      <c r="E621" t="s">
+        <v>491</v>
+      </c>
+      <c r="F621" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A622" t="s">
+        <v>493</v>
+      </c>
+      <c r="B622" t="s">
+        <v>8</v>
+      </c>
+      <c r="C622" s="1">
+        <v>46045</v>
+      </c>
+      <c r="D622" t="s">
+        <v>355</v>
+      </c>
+      <c r="E622" t="s">
+        <v>494</v>
+      </c>
+      <c r="F622" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A623" t="s">
+        <v>496</v>
+      </c>
+      <c r="B623" t="s">
+        <v>5</v>
+      </c>
+      <c r="C623" s="1">
+        <v>46046</v>
+      </c>
+      <c r="D623" t="s">
+        <v>362</v>
+      </c>
+      <c r="E623" t="s">
+        <v>497</v>
+      </c>
+      <c r="F623" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A624" t="s">
+        <v>307</v>
+      </c>
+      <c r="B624" t="s">
+        <v>8</v>
+      </c>
+      <c r="C624" s="1">
+        <v>46046</v>
+      </c>
+      <c r="D624" t="s">
+        <v>368</v>
+      </c>
+      <c r="E624" t="s">
+        <v>499</v>
+      </c>
+      <c r="F624" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
+        <v>501</v>
+      </c>
+      <c r="B625" t="s">
+        <v>5</v>
+      </c>
+      <c r="C625" s="1">
+        <v>46046</v>
+      </c>
+      <c r="D625" t="s">
+        <v>362</v>
+      </c>
+      <c r="E625" t="s">
+        <v>502</v>
+      </c>
+      <c r="F625" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A626" t="s">
+        <v>504</v>
+      </c>
+      <c r="B626" t="s">
+        <v>5</v>
+      </c>
+      <c r="C626" s="1">
+        <v>46046</v>
+      </c>
+      <c r="D626" t="s">
+        <v>362</v>
+      </c>
+      <c r="E626" t="s">
+        <v>502</v>
+      </c>
+      <c r="F626" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A627" t="s">
+        <v>63</v>
+      </c>
+      <c r="B627" t="s">
+        <v>11</v>
+      </c>
+      <c r="C627" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D627" t="s">
+        <v>353</v>
+      </c>
+      <c r="E627" t="s">
+        <v>506</v>
+      </c>
+      <c r="F627" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A628" t="s">
+        <v>83</v>
+      </c>
+      <c r="B628" t="s">
+        <v>19</v>
+      </c>
+      <c r="C628" s="1">
+        <v>46050</v>
+      </c>
+      <c r="D628" t="s">
+        <v>386</v>
+      </c>
+      <c r="E628" t="s">
+        <v>508</v>
+      </c>
+      <c r="F628" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A629" t="s">
+        <v>26</v>
+      </c>
+      <c r="B629" t="s">
+        <v>5</v>
+      </c>
+      <c r="C629" s="1">
+        <v>46052</v>
+      </c>
+      <c r="D629" t="s">
+        <v>353</v>
+      </c>
+      <c r="E629" t="s">
+        <v>509</v>
+      </c>
+      <c r="F629" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A630" t="s">
+        <v>511</v>
+      </c>
+      <c r="B630" t="s">
+        <v>8</v>
+      </c>
+      <c r="C630" s="1">
+        <v>46052</v>
+      </c>
+      <c r="D630" t="s">
+        <v>353</v>
+      </c>
+      <c r="E630" t="s">
+        <v>512</v>
+      </c>
+      <c r="F630" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A631" t="s">
+        <v>514</v>
+      </c>
+      <c r="B631" t="s">
+        <v>5</v>
+      </c>
+      <c r="C631" s="1">
+        <v>46052</v>
+      </c>
+      <c r="D631" t="s">
+        <v>362</v>
+      </c>
+      <c r="E631" t="s">
+        <v>515</v>
+      </c>
+      <c r="F631" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A632" t="s">
+        <v>186</v>
+      </c>
+      <c r="B632" t="s">
+        <v>8</v>
+      </c>
+      <c r="C632" s="1">
+        <v>46052</v>
+      </c>
+      <c r="D632" t="s">
+        <v>355</v>
+      </c>
+      <c r="E632" t="s">
+        <v>517</v>
+      </c>
+      <c r="F632" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A633" t="s">
+        <v>519</v>
+      </c>
+      <c r="B633" t="s">
+        <v>192</v>
+      </c>
+      <c r="C633" s="1">
+        <v>46062</v>
+      </c>
+      <c r="D633" t="s">
+        <v>386</v>
+      </c>
+      <c r="E633" t="s">
+        <v>520</v>
+      </c>
+      <c r="F633" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
+        <v>522</v>
+      </c>
+      <c r="B634" t="s">
+        <v>5</v>
+      </c>
+      <c r="C634" s="1">
+        <v>46063</v>
+      </c>
+      <c r="D634" t="s">
+        <v>378</v>
+      </c>
+      <c r="E634" t="s">
+        <v>523</v>
+      </c>
+      <c r="F634" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A635" t="s">
+        <v>119</v>
+      </c>
+      <c r="B635" t="s">
+        <v>5</v>
+      </c>
+      <c r="C635" s="1">
+        <v>46065</v>
+      </c>
+      <c r="D635" t="s">
+        <v>353</v>
+      </c>
+      <c r="E635" t="s">
+        <v>525</v>
+      </c>
+      <c r="F635" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>470</v>
+      </c>
+      <c r="B636" t="s">
+        <v>5</v>
+      </c>
+      <c r="C636" s="1">
+        <v>46065</v>
+      </c>
+      <c r="D636" t="s">
+        <v>353</v>
+      </c>
+      <c r="E636" t="s">
+        <v>527</v>
+      </c>
+      <c r="F636" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A637" t="s">
+        <v>30</v>
+      </c>
+      <c r="B637" t="s">
+        <v>5</v>
+      </c>
+      <c r="C637" s="1">
+        <v>46065</v>
+      </c>
+      <c r="D637" t="s">
+        <v>353</v>
+      </c>
+      <c r="E637" t="s">
+        <v>527</v>
+      </c>
+      <c r="F637" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A638" t="s">
+        <v>33</v>
+      </c>
+      <c r="B638" t="s">
+        <v>5</v>
+      </c>
+      <c r="C638" s="1">
+        <v>46065</v>
+      </c>
+      <c r="D638" t="s">
+        <v>353</v>
+      </c>
+      <c r="E638" t="s">
+        <v>529</v>
+      </c>
+      <c r="F638" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A639" t="s">
+        <v>531</v>
+      </c>
+      <c r="B639" t="s">
+        <v>5</v>
+      </c>
+      <c r="C639" s="1">
+        <v>46065</v>
+      </c>
+      <c r="D639" t="s">
+        <v>355</v>
+      </c>
+      <c r="E639" t="s">
+        <v>532</v>
+      </c>
+      <c r="F639" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A640" t="s">
+        <v>534</v>
+      </c>
+      <c r="B640" t="s">
+        <v>5</v>
+      </c>
+      <c r="C640" s="1">
+        <v>46065</v>
+      </c>
+      <c r="D640" t="s">
+        <v>355</v>
+      </c>
+      <c r="E640" t="s">
+        <v>532</v>
+      </c>
+      <c r="F640" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A641" t="s">
+        <v>535</v>
+      </c>
+      <c r="B641" t="s">
+        <v>5</v>
+      </c>
+      <c r="C641" s="1">
+        <v>46073</v>
+      </c>
+      <c r="D641" t="s">
+        <v>362</v>
+      </c>
+      <c r="E641" t="s">
+        <v>536</v>
+      </c>
+      <c r="F641" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A642" t="s">
+        <v>538</v>
+      </c>
+      <c r="B642" t="s">
+        <v>54</v>
+      </c>
+      <c r="C642" s="1">
+        <v>46074</v>
+      </c>
+      <c r="D642" t="s">
+        <v>353</v>
+      </c>
+      <c r="E642" t="s">
+        <v>539</v>
+      </c>
+      <c r="F642" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>541</v>
+      </c>
+      <c r="B643" t="s">
+        <v>13</v>
+      </c>
+      <c r="C643" s="1">
+        <v>46076</v>
+      </c>
+      <c r="D643" t="s">
+        <v>353</v>
+      </c>
+      <c r="E643" t="s">
+        <v>542</v>
+      </c>
+      <c r="F643" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>16</v>
+      </c>
+      <c r="B644" t="s">
+        <v>8</v>
+      </c>
+      <c r="C644" s="1">
+        <v>46077</v>
+      </c>
+      <c r="D644" t="s">
+        <v>355</v>
+      </c>
+      <c r="E644" t="s">
+        <v>544</v>
+      </c>
+      <c r="F644" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>546</v>
+      </c>
+      <c r="B645" t="s">
+        <v>11</v>
+      </c>
+      <c r="C645" s="1">
+        <v>46078</v>
+      </c>
+      <c r="D645" t="s">
+        <v>357</v>
+      </c>
+      <c r="E645" t="s">
+        <v>547</v>
+      </c>
+      <c r="F645" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>186</v>
+      </c>
+      <c r="B646" t="s">
+        <v>8</v>
+      </c>
+      <c r="C646" s="1">
+        <v>46079</v>
+      </c>
+      <c r="D646" t="s">
+        <v>355</v>
+      </c>
+      <c r="E646" t="s">
+        <v>549</v>
+      </c>
+      <c r="F646" t="s">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D576" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D576">
+    <sortCondition ref="C2:C576"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Desvios de DTOs.xlsx
+++ b/data/Desvios de DTOs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EA4D24-3089-4D37-8159-0C4CE3366699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D42C445-F05E-473A-B7E5-247F07B90C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="608">
   <si>
     <t>Colaborador</t>
   </si>
@@ -1692,6 +1692,177 @@
   </si>
   <si>
     <t>Foi a bordado no ato da ocorrencia.Relato de segurança</t>
+  </si>
+  <si>
+    <t>AHARON HASSAN PEREIRA DE CAMARGO</t>
+  </si>
+  <si>
+    <t>AMAURI SILVA SALVADOR DE SENE</t>
+  </si>
+  <si>
+    <t>DAVI MORAIS DO NASCIMENTO SILVA</t>
+  </si>
+  <si>
+    <t>HARON NEVES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JONATHAN HENRIQUE DE OLIVEIRA GARCIA</t>
+  </si>
+  <si>
+    <t>JORGE LUIS STEPHANO</t>
+  </si>
+  <si>
+    <t>LEONARDO ROGERIO RIBEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>PETERSON PATRICK DA SILVA CORREIA</t>
+  </si>
+  <si>
+    <t>RAIMUNDO ALMEIDA DE QUEIROZ</t>
+  </si>
+  <si>
+    <t>RONALDO MAGRI</t>
+  </si>
+  <si>
+    <t>Barra de segregação quebrada</t>
+  </si>
+  <si>
+    <t>Precisamos adequar barra quebrada, operador e ajudantes para não ter homem X máquina, combinaram local para nenhum dois ultrapassarPonto positivo ajudantes que estavam trabalhando no local com uso de 100% dos epis e parabenizei no momento</t>
+  </si>
+  <si>
+    <t>A chave da caixinha estava para o lado de fora e não com o colaborador</t>
+  </si>
+  <si>
+    <t>Feito o ver e agir, foi orientado a seguir o padrão de controle de chaves da unidade.</t>
+  </si>
+  <si>
+    <t>Não executou o check list do trava quedas para iniciar as atividades.</t>
+  </si>
+  <si>
+    <t>Treinamento de execução do check list</t>
+  </si>
+  <si>
+    <t>Puxou a paleteira ao invés de empurrar.</t>
+  </si>
+  <si>
+    <t>Colaborador orientado sobre as regras seguras do manuseio de paleteira.</t>
+  </si>
+  <si>
+    <t>Chave ficou coma caixinha aberta</t>
+  </si>
+  <si>
+    <t>Realizado o reforço com colaborador sobre a importância de manter as chaves na caixinha trancada</t>
+  </si>
+  <si>
+    <t>Colaborador trafegando com as baias em meia altura</t>
+  </si>
+  <si>
+    <t>Advertência escrita e conscientização da importância de praticar uma direção segura</t>
+  </si>
+  <si>
+    <t>Devido a um pallet alocado fora do local, a segregação não foi fechada</t>
+  </si>
+  <si>
+    <t>Operador orientado e pallet retirado</t>
+  </si>
+  <si>
+    <t>Puxando a paleteira</t>
+  </si>
+  <si>
+    <t>Passei o treinamento correto, para empurrar a paleteira. Passei sobre os riscos também.</t>
+  </si>
+  <si>
+    <t>Operador com protetor auricular quebrado, só tem um lado.</t>
+  </si>
+  <si>
+    <t>Orientado a trocar por um novo com o time de segurança.</t>
+  </si>
+  <si>
+    <t>Deixou a chave do caminhão na porta do caminhão</t>
+  </si>
+  <si>
+    <t>No manuseio da caixaria o colaborador agachava apenas para deixa a caixaria. Pra pegar ele não fazia a ergonomia correta.</t>
+  </si>
+  <si>
+    <t>Fazer a manobra correta de ergonomia na retirada das caixas. E fazer um Dto novamente pra verificar se o colaborador faz correto o movimento.</t>
+  </si>
+  <si>
+    <t>Ajudante estava dentro da TC da Maria mole e deu ok para operador entrar e alocar o palete. Ajudante orientado no feedback sobre liberar a tc para o operador, ele tem conhecimento do processo correto. Orientação realizada com o operador também, que não deveria ter acessado mesmo com o ajudante sinalizando.</t>
+  </si>
+  <si>
+    <t>SOP nao esta disponível na area. Somente no link do grupo geral do armazém.Revisar padrão com uso de presilha.Reciclar turno B sobre distânciamento homem máquina.</t>
+  </si>
+  <si>
+    <t>Chave em posse do motorista.</t>
+  </si>
+  <si>
+    <t>Replicar treinamento de controle de chave durante execução de recebimento de empurrada.</t>
+  </si>
+  <si>
+    <t>Chave estava fora lá da caixinha, outras pessoas tinham acesso</t>
+  </si>
+  <si>
+    <t>Orientei sobre o controle de chave correto</t>
+  </si>
+  <si>
+    <t>Execução Segura LOTO</t>
+  </si>
+  <si>
+    <t>Não fez o bloqueio do soprador antes de sair para o almoço.</t>
+  </si>
+  <si>
+    <t>Reforçado sobre a necessidade do bloqueio do equipamento antes de sair do local para almoço/troca de turno/etc.</t>
+  </si>
+  <si>
+    <t>Chave na porta do caminhão</t>
+  </si>
+  <si>
+    <t>Informado liderança</t>
+  </si>
+  <si>
+    <t>Bloqueio de chave.</t>
+  </si>
+  <si>
+    <t>Colocar caixinha de bloqueio próximo ao carregamento e descarregamento de caminhão frota fixa.</t>
+  </si>
+  <si>
+    <t>Realizar reciclagem com o operador Jhonathan na tarefa bloqueio de energia.</t>
+  </si>
+  <si>
+    <t>Trava rodas manual</t>
+  </si>
+  <si>
+    <t>Adquirir trava rodas empilhadeira para 100% da frota</t>
+  </si>
+  <si>
+    <t>Está puxando a paleteira</t>
+  </si>
+  <si>
+    <t>Relato abordagem positiva. E abordagem no ato da ocorrência</t>
+  </si>
+  <si>
+    <t>Não foi realizado o controle de chaves do caminhão no qual estava sendo realizado o carregamento.</t>
+  </si>
+  <si>
+    <t>- Treina-lo conforme o padrão, reforçando os pontos de segurança como o controle de chaves no qual foi apontado desvio.</t>
+  </si>
+  <si>
+    <t>Nok</t>
+  </si>
+  <si>
+    <t>Tudo ok</t>
+  </si>
+  <si>
+    <t>Colaborador não desligou a empilhadeira ao sair dele para retirada de um toco de madeira.</t>
+  </si>
+  <si>
+    <t>Orientado para sempre desligar a empilhadeira assim que precisar se ausentar dela.</t>
+  </si>
+  <si>
+    <t>Colaborador pegando algumas caixas somente com uma das mãos.</t>
+  </si>
+  <si>
+    <t>Motorista chegou as 15:19 e não acompanhou a Blitz Ajudante chegou as 15:26 e não acompanhou.Produtos da Companhia ( Caixaria ) sendo colocado no chão para a conferência ( orientar ajudante e Conferente a sempre colocar os produtos sobre os PBRs, conforme descrito no padrão)Manuseio incorreto, pegada inicial de algumas caixas sendo feita apenas por uma das mãos( orientação sobre Manuseio correto)Ajudante rasgou o strech e deixou no chão na área de passagem dele mesmo para realização da Blitz, risco de tropeçar ( Reforçar a importância e o dever do 5S)Atualizar no padrão o uso da presilha nos fitilhos Colocar o padrão impresso nas áreas.</t>
   </si>
 </sst>
 </file>
@@ -2044,16 +2215,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}">
-  <dimension ref="A1:F646"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F670"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="139.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="139.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2067,7 +2238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2081,7 +2252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2095,7 +2266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2109,7 +2280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2123,7 +2294,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2137,7 +2308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2151,7 +2322,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2165,7 +2336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -2179,7 +2350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2193,7 +2364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2207,7 +2378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2221,7 +2392,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2235,7 +2406,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2249,7 +2420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2263,7 +2434,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -2277,7 +2448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2291,7 +2462,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -2305,7 +2476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -2319,7 +2490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2333,7 +2504,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2347,7 +2518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -2361,7 +2532,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2375,7 +2546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -2389,7 +2560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2403,7 +2574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -2417,7 +2588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -2431,7 +2602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -2445,7 +2616,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -2459,7 +2630,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -2473,7 +2644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -2487,7 +2658,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -2501,7 +2672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -2515,7 +2686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2529,7 +2700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2543,7 +2714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2557,7 +2728,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2571,7 +2742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2585,7 +2756,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -2599,7 +2770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -2613,7 +2784,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2627,7 +2798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2641,7 +2812,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2655,7 +2826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2669,7 +2840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -2683,7 +2854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -2697,7 +2868,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -2711,7 +2882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -2725,7 +2896,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -2739,7 +2910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -2753,7 +2924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -2767,7 +2938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -2781,7 +2952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -2795,7 +2966,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -2809,7 +2980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -2823,7 +2994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -2837,7 +3008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -2851,7 +3022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -2865,7 +3036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -2879,7 +3050,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>32</v>
       </c>
@@ -2893,7 +3064,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -2907,7 +3078,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -2921,7 +3092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -2935,7 +3106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -2949,7 +3120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -2963,7 +3134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -2977,7 +3148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -2991,7 +3162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -3005,7 +3176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -3019,7 +3190,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -3033,7 +3204,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -3047,7 +3218,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -3061,7 +3232,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -3075,7 +3246,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>45</v>
       </c>
@@ -3089,7 +3260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -3103,7 +3274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -3117,7 +3288,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -3131,7 +3302,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -3145,7 +3316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -3159,7 +3330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -3173,7 +3344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>78</v>
       </c>
@@ -3187,7 +3358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>79</v>
       </c>
@@ -3201,7 +3372,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>80</v>
       </c>
@@ -3215,7 +3386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>81</v>
       </c>
@@ -3229,7 +3400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -3243,7 +3414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>82</v>
       </c>
@@ -3257,7 +3428,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3271,7 +3442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>84</v>
       </c>
@@ -3285,7 +3456,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>85</v>
       </c>
@@ -3299,7 +3470,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>86</v>
       </c>
@@ -3313,7 +3484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -3327,7 +3498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>87</v>
       </c>
@@ -3341,7 +3512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>55</v>
       </c>
@@ -3355,7 +3526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>63</v>
       </c>
@@ -3369,7 +3540,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>63</v>
       </c>
@@ -3383,7 +3554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>63</v>
       </c>
@@ -3397,7 +3568,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>63</v>
       </c>
@@ -3411,7 +3582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>63</v>
       </c>
@@ -3425,7 +3596,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>89</v>
       </c>
@@ -3439,7 +3610,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>89</v>
       </c>
@@ -3453,7 +3624,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>90</v>
       </c>
@@ -3467,7 +3638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>90</v>
       </c>
@@ -3481,7 +3652,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -3495,7 +3666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>91</v>
       </c>
@@ -3509,7 +3680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>92</v>
       </c>
@@ -3523,7 +3694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>64</v>
       </c>
@@ -3537,7 +3708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>37</v>
       </c>
@@ -3551,7 +3722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>93</v>
       </c>
@@ -3565,7 +3736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>31</v>
       </c>
@@ -3579,7 +3750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>94</v>
       </c>
@@ -3593,7 +3764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>95</v>
       </c>
@@ -3607,7 +3778,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>96</v>
       </c>
@@ -3621,7 +3792,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -3635,7 +3806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>98</v>
       </c>
@@ -3649,7 +3820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -3663,7 +3834,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>52</v>
       </c>
@@ -3677,7 +3848,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>99</v>
       </c>
@@ -3691,7 +3862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>100</v>
       </c>
@@ -3705,7 +3876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>100</v>
       </c>
@@ -3719,7 +3890,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>101</v>
       </c>
@@ -3733,7 +3904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>101</v>
       </c>
@@ -3747,7 +3918,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>100</v>
       </c>
@@ -3761,7 +3932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>100</v>
       </c>
@@ -3775,7 +3946,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>100</v>
       </c>
@@ -3789,7 +3960,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>36</v>
       </c>
@@ -3803,7 +3974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>102</v>
       </c>
@@ -3817,7 +3988,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>103</v>
       </c>
@@ -3831,7 +4002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>104</v>
       </c>
@@ -3845,7 +4016,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>105</v>
       </c>
@@ -3859,7 +4030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>106</v>
       </c>
@@ -3873,7 +4044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>107</v>
       </c>
@@ -3887,7 +4058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>108</v>
       </c>
@@ -3901,7 +4072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>109</v>
       </c>
@@ -3915,7 +4086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>110</v>
       </c>
@@ -3929,7 +4100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>36</v>
       </c>
@@ -3943,7 +4114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>111</v>
       </c>
@@ -3957,7 +4128,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>112</v>
       </c>
@@ -3971,7 +4142,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>113</v>
       </c>
@@ -3985,7 +4156,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>12</v>
       </c>
@@ -3999,7 +4170,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>114</v>
       </c>
@@ -4013,7 +4184,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>115</v>
       </c>
@@ -4027,7 +4198,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>116</v>
       </c>
@@ -4041,7 +4212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>117</v>
       </c>
@@ -4055,7 +4226,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>118</v>
       </c>
@@ -4069,7 +4240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>118</v>
       </c>
@@ -4083,7 +4254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>118</v>
       </c>
@@ -4097,7 +4268,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>118</v>
       </c>
@@ -4111,7 +4282,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>115</v>
       </c>
@@ -4125,7 +4296,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>119</v>
       </c>
@@ -4139,7 +4310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>120</v>
       </c>
@@ -4153,7 +4324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>121</v>
       </c>
@@ -4167,7 +4338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>121</v>
       </c>
@@ -4181,7 +4352,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>121</v>
       </c>
@@ -4195,7 +4366,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>122</v>
       </c>
@@ -4209,7 +4380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>55</v>
       </c>
@@ -4223,7 +4394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>80</v>
       </c>
@@ -4237,7 +4408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>80</v>
       </c>
@@ -4251,7 +4422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>80</v>
       </c>
@@ -4265,7 +4436,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>123</v>
       </c>
@@ -4279,7 +4450,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>123</v>
       </c>
@@ -4293,7 +4464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -4307,7 +4478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -4321,7 +4492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>124</v>
       </c>
@@ -4335,7 +4506,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -4349,7 +4520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>125</v>
       </c>
@@ -4363,7 +4534,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>126</v>
       </c>
@@ -4377,7 +4548,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>127</v>
       </c>
@@ -4391,7 +4562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>128</v>
       </c>
@@ -4405,7 +4576,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>129</v>
       </c>
@@ -4419,7 +4590,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>73</v>
       </c>
@@ -4433,7 +4604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>130</v>
       </c>
@@ -4447,7 +4618,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>131</v>
       </c>
@@ -4461,7 +4632,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>132</v>
       </c>
@@ -4475,7 +4646,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>133</v>
       </c>
@@ -4489,7 +4660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>134</v>
       </c>
@@ -4503,7 +4674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>134</v>
       </c>
@@ -4517,7 +4688,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>135</v>
       </c>
@@ -4531,7 +4702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>93</v>
       </c>
@@ -4545,7 +4716,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>93</v>
       </c>
@@ -4559,7 +4730,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>134</v>
       </c>
@@ -4573,7 +4744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>125</v>
       </c>
@@ -4587,7 +4758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>136</v>
       </c>
@@ -4601,7 +4772,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>137</v>
       </c>
@@ -4615,7 +4786,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>138</v>
       </c>
@@ -4629,7 +4800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>139</v>
       </c>
@@ -4643,7 +4814,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>139</v>
       </c>
@@ -4657,7 +4828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>137</v>
       </c>
@@ -4671,7 +4842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>137</v>
       </c>
@@ -4685,7 +4856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>137</v>
       </c>
@@ -4699,7 +4870,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>137</v>
       </c>
@@ -4713,7 +4884,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>140</v>
       </c>
@@ -4727,7 +4898,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>140</v>
       </c>
@@ -4741,7 +4912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>141</v>
       </c>
@@ -4755,7 +4926,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>142</v>
       </c>
@@ -4769,7 +4940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>143</v>
       </c>
@@ -4783,7 +4954,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>143</v>
       </c>
@@ -4797,7 +4968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>144</v>
       </c>
@@ -4811,7 +4982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>145</v>
       </c>
@@ -4825,7 +4996,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>135</v>
       </c>
@@ -4839,7 +5010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>146</v>
       </c>
@@ -4853,7 +5024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>147</v>
       </c>
@@ -4867,7 +5038,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>148</v>
       </c>
@@ -4881,7 +5052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>148</v>
       </c>
@@ -4895,7 +5066,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>149</v>
       </c>
@@ -4909,7 +5080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>149</v>
       </c>
@@ -4923,7 +5094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>150</v>
       </c>
@@ -4937,7 +5108,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>39</v>
       </c>
@@ -4951,7 +5122,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>151</v>
       </c>
@@ -4965,7 +5136,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>151</v>
       </c>
@@ -4979,7 +5150,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>152</v>
       </c>
@@ -4993,7 +5164,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>153</v>
       </c>
@@ -5007,7 +5178,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>153</v>
       </c>
@@ -5021,7 +5192,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>153</v>
       </c>
@@ -5035,7 +5206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>154</v>
       </c>
@@ -5049,7 +5220,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>155</v>
       </c>
@@ -5063,7 +5234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>155</v>
       </c>
@@ -5077,7 +5248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>155</v>
       </c>
@@ -5091,7 +5262,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>156</v>
       </c>
@@ -5105,7 +5276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>156</v>
       </c>
@@ -5119,7 +5290,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>107</v>
       </c>
@@ -5133,7 +5304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>127</v>
       </c>
@@ -5147,7 +5318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>157</v>
       </c>
@@ -5161,7 +5332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>67</v>
       </c>
@@ -5175,7 +5346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>158</v>
       </c>
@@ -5189,7 +5360,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>158</v>
       </c>
@@ -5203,7 +5374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>159</v>
       </c>
@@ -5217,7 +5388,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>160</v>
       </c>
@@ -5231,7 +5402,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>161</v>
       </c>
@@ -5245,7 +5416,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>161</v>
       </c>
@@ -5259,7 +5430,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>162</v>
       </c>
@@ -5273,7 +5444,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>162</v>
       </c>
@@ -5287,7 +5458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>163</v>
       </c>
@@ -5301,7 +5472,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>163</v>
       </c>
@@ -5315,7 +5486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>164</v>
       </c>
@@ -5329,7 +5500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>164</v>
       </c>
@@ -5343,7 +5514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>165</v>
       </c>
@@ -5357,7 +5528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>165</v>
       </c>
@@ -5371,7 +5542,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>12</v>
       </c>
@@ -5385,7 +5556,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>139</v>
       </c>
@@ -5399,7 +5570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>127</v>
       </c>
@@ -5413,7 +5584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>163</v>
       </c>
@@ -5427,7 +5598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>166</v>
       </c>
@@ -5441,7 +5612,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>166</v>
       </c>
@@ -5455,7 +5626,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>167</v>
       </c>
@@ -5469,7 +5640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>167</v>
       </c>
@@ -5483,7 +5654,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>168</v>
       </c>
@@ -5497,7 +5668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>155</v>
       </c>
@@ -5511,7 +5682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>169</v>
       </c>
@@ -5525,7 +5696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>170</v>
       </c>
@@ -5539,7 +5710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>171</v>
       </c>
@@ -5553,7 +5724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>172</v>
       </c>
@@ -5567,7 +5738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>153</v>
       </c>
@@ -5581,7 +5752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>122</v>
       </c>
@@ -5595,7 +5766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>173</v>
       </c>
@@ -5609,7 +5780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>173</v>
       </c>
@@ -5623,7 +5794,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>174</v>
       </c>
@@ -5637,7 +5808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>174</v>
       </c>
@@ -5651,7 +5822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>52</v>
       </c>
@@ -5665,7 +5836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>83</v>
       </c>
@@ -5679,7 +5850,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>175</v>
       </c>
@@ -5693,7 +5864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>175</v>
       </c>
@@ -5707,7 +5878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>176</v>
       </c>
@@ -5721,7 +5892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>118</v>
       </c>
@@ -5735,7 +5906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>177</v>
       </c>
@@ -5749,7 +5920,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>96</v>
       </c>
@@ -5763,7 +5934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>178</v>
       </c>
@@ -5777,7 +5948,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>10</v>
       </c>
@@ -5791,7 +5962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>10</v>
       </c>
@@ -5805,7 +5976,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>136</v>
       </c>
@@ -5819,7 +5990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>84</v>
       </c>
@@ -5833,7 +6004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>179</v>
       </c>
@@ -5847,7 +6018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>97</v>
       </c>
@@ -5861,7 +6032,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>180</v>
       </c>
@@ -5875,7 +6046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>181</v>
       </c>
@@ -5889,7 +6060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>181</v>
       </c>
@@ -5903,7 +6074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>182</v>
       </c>
@@ -5917,7 +6088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>183</v>
       </c>
@@ -5931,7 +6102,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>183</v>
       </c>
@@ -5945,7 +6116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>183</v>
       </c>
@@ -5959,7 +6130,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>184</v>
       </c>
@@ -5973,7 +6144,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>153</v>
       </c>
@@ -5987,7 +6158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>185</v>
       </c>
@@ -6001,7 +6172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>185</v>
       </c>
@@ -6015,7 +6186,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>123</v>
       </c>
@@ -6029,7 +6200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>186</v>
       </c>
@@ -6043,7 +6214,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>186</v>
       </c>
@@ -6057,7 +6228,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>187</v>
       </c>
@@ -6071,7 +6242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>7</v>
       </c>
@@ -6085,7 +6256,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>7</v>
       </c>
@@ -6099,7 +6270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>188</v>
       </c>
@@ -6113,7 +6284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>127</v>
       </c>
@@ -6127,7 +6298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>189</v>
       </c>
@@ -6141,7 +6312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>123</v>
       </c>
@@ -6155,7 +6326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>55</v>
       </c>
@@ -6169,7 +6340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>120</v>
       </c>
@@ -6183,7 +6354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>45</v>
       </c>
@@ -6197,7 +6368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>190</v>
       </c>
@@ -6211,7 +6382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>113</v>
       </c>
@@ -6225,7 +6396,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>191</v>
       </c>
@@ -6239,7 +6410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>193</v>
       </c>
@@ -6253,7 +6424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>194</v>
       </c>
@@ -6267,7 +6438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>195</v>
       </c>
@@ -6281,7 +6452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>196</v>
       </c>
@@ -6295,7 +6466,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>197</v>
       </c>
@@ -6309,7 +6480,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>197</v>
       </c>
@@ -6323,7 +6494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>198</v>
       </c>
@@ -6337,7 +6508,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>198</v>
       </c>
@@ -6351,7 +6522,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>199</v>
       </c>
@@ -6365,7 +6536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>199</v>
       </c>
@@ -6379,7 +6550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>58</v>
       </c>
@@ -6393,7 +6564,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>200</v>
       </c>
@@ -6407,7 +6578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>201</v>
       </c>
@@ -6421,7 +6592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>202</v>
       </c>
@@ -6435,7 +6606,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>203</v>
       </c>
@@ -6449,7 +6620,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>204</v>
       </c>
@@ -6463,7 +6634,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>205</v>
       </c>
@@ -6477,7 +6648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>121</v>
       </c>
@@ -6491,7 +6662,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>121</v>
       </c>
@@ -6505,7 +6676,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>206</v>
       </c>
@@ -6519,7 +6690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>207</v>
       </c>
@@ -6533,7 +6704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>208</v>
       </c>
@@ -6547,7 +6718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>209</v>
       </c>
@@ -6561,7 +6732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>210</v>
       </c>
@@ -6575,7 +6746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>116</v>
       </c>
@@ -6589,7 +6760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>116</v>
       </c>
@@ -6603,7 +6774,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>116</v>
       </c>
@@ -6617,7 +6788,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>116</v>
       </c>
@@ -6631,7 +6802,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>63</v>
       </c>
@@ -6645,7 +6816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>63</v>
       </c>
@@ -6659,7 +6830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>124</v>
       </c>
@@ -6673,7 +6844,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>96</v>
       </c>
@@ -6687,7 +6858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>96</v>
       </c>
@@ -6701,7 +6872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>211</v>
       </c>
@@ -6715,7 +6886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>212</v>
       </c>
@@ -6729,7 +6900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>213</v>
       </c>
@@ -6743,7 +6914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>214</v>
       </c>
@@ -6757,7 +6928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>215</v>
       </c>
@@ -6771,7 +6942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>216</v>
       </c>
@@ -6785,7 +6956,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>217</v>
       </c>
@@ -6799,7 +6970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>198</v>
       </c>
@@ -6813,7 +6984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>195</v>
       </c>
@@ -6827,7 +6998,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>218</v>
       </c>
@@ -6841,7 +7012,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>219</v>
       </c>
@@ -6855,7 +7026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>83</v>
       </c>
@@ -6869,7 +7040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>196</v>
       </c>
@@ -6883,7 +7054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>220</v>
       </c>
@@ -6897,7 +7068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>221</v>
       </c>
@@ -6911,7 +7082,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>222</v>
       </c>
@@ -6925,7 +7096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>204</v>
       </c>
@@ -6939,7 +7110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>223</v>
       </c>
@@ -6953,7 +7124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>157</v>
       </c>
@@ -6967,7 +7138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>76</v>
       </c>
@@ -6981,7 +7152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>224</v>
       </c>
@@ -6995,7 +7166,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>225</v>
       </c>
@@ -7009,7 +7180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>196</v>
       </c>
@@ -7023,7 +7194,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>105</v>
       </c>
@@ -7037,7 +7208,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>228</v>
       </c>
@@ -7051,7 +7222,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>230</v>
       </c>
@@ -7065,7 +7236,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>204</v>
       </c>
@@ -7079,7 +7250,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>205</v>
       </c>
@@ -7093,7 +7264,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>234</v>
       </c>
@@ -7107,7 +7278,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>236</v>
       </c>
@@ -7121,7 +7292,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>238</v>
       </c>
@@ -7135,7 +7306,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>195</v>
       </c>
@@ -7149,7 +7320,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>59</v>
       </c>
@@ -7163,7 +7334,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>242</v>
       </c>
@@ -7177,7 +7348,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>62</v>
       </c>
@@ -7191,7 +7362,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>245</v>
       </c>
@@ -7205,7 +7376,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>247</v>
       </c>
@@ -7219,7 +7390,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>57</v>
       </c>
@@ -7233,7 +7404,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>60</v>
       </c>
@@ -7247,7 +7418,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>236</v>
       </c>
@@ -7261,7 +7432,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>18</v>
       </c>
@@ -7275,7 +7446,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>121</v>
       </c>
@@ -7289,7 +7460,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>253</v>
       </c>
@@ -7303,7 +7474,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>255</v>
       </c>
@@ -7317,7 +7488,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>204</v>
       </c>
@@ -7331,7 +7502,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>62</v>
       </c>
@@ -7345,7 +7516,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>60</v>
       </c>
@@ -7359,7 +7530,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>260</v>
       </c>
@@ -7373,7 +7544,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>262</v>
       </c>
@@ -7387,7 +7558,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>264</v>
       </c>
@@ -7401,7 +7572,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>220</v>
       </c>
@@ -7415,7 +7586,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>266</v>
       </c>
@@ -7429,7 +7600,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>268</v>
       </c>
@@ -7443,7 +7614,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>107</v>
       </c>
@@ -7457,7 +7628,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>270</v>
       </c>
@@ -7471,7 +7642,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>202</v>
       </c>
@@ -7485,7 +7656,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>272</v>
       </c>
@@ -7499,7 +7670,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>274</v>
       </c>
@@ -7513,7 +7684,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>276</v>
       </c>
@@ -7527,7 +7698,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>242</v>
       </c>
@@ -7541,7 +7712,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>278</v>
       </c>
@@ -7555,7 +7726,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>23</v>
       </c>
@@ -7569,7 +7740,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>62</v>
       </c>
@@ -7583,7 +7754,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>60</v>
       </c>
@@ -7597,7 +7768,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>245</v>
       </c>
@@ -7611,7 +7782,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>281</v>
       </c>
@@ -7625,7 +7796,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>282</v>
       </c>
@@ -7639,7 +7810,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>283</v>
       </c>
@@ -7653,7 +7824,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>284</v>
       </c>
@@ -7667,7 +7838,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>207</v>
       </c>
@@ -7681,7 +7852,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>76</v>
       </c>
@@ -7695,7 +7866,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>285</v>
       </c>
@@ -7709,7 +7880,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>262</v>
       </c>
@@ -7723,7 +7894,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>286</v>
       </c>
@@ -7737,7 +7908,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>287</v>
       </c>
@@ -7751,7 +7922,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>135</v>
       </c>
@@ -7765,7 +7936,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>57</v>
       </c>
@@ -7779,7 +7950,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>289</v>
       </c>
@@ -7793,7 +7964,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>268</v>
       </c>
@@ -7807,7 +7978,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>290</v>
       </c>
@@ -7821,7 +7992,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>107</v>
       </c>
@@ -7835,7 +8006,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>255</v>
       </c>
@@ -7849,7 +8020,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>202</v>
       </c>
@@ -7863,7 +8034,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>291</v>
       </c>
@@ -7877,7 +8048,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>228</v>
       </c>
@@ -7891,7 +8062,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>292</v>
       </c>
@@ -7905,7 +8076,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>293</v>
       </c>
@@ -7919,7 +8090,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>274</v>
       </c>
@@ -7933,7 +8104,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>294</v>
       </c>
@@ -7947,7 +8118,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>276</v>
       </c>
@@ -7961,7 +8132,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>296</v>
       </c>
@@ -7975,7 +8146,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>297</v>
       </c>
@@ -7989,7 +8160,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>23</v>
       </c>
@@ -8003,7 +8174,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>281</v>
       </c>
@@ -8017,7 +8188,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>298</v>
       </c>
@@ -8031,7 +8202,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>236</v>
       </c>
@@ -8045,7 +8216,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>300</v>
       </c>
@@ -8059,7 +8230,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>286</v>
       </c>
@@ -8073,7 +8244,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>303</v>
       </c>
@@ -8087,7 +8258,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>289</v>
       </c>
@@ -8101,7 +8272,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>304</v>
       </c>
@@ -8115,7 +8286,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>305</v>
       </c>
@@ -8129,7 +8300,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>196</v>
       </c>
@@ -8143,7 +8314,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>107</v>
       </c>
@@ -8157,7 +8328,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>255</v>
       </c>
@@ -8171,7 +8342,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>228</v>
       </c>
@@ -8185,7 +8356,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>307</v>
       </c>
@@ -8199,7 +8370,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>293</v>
       </c>
@@ -8213,7 +8384,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>296</v>
       </c>
@@ -8227,7 +8398,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>309</v>
       </c>
@@ -8241,7 +8412,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>242</v>
       </c>
@@ -8255,7 +8426,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>205</v>
       </c>
@@ -8269,7 +8440,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>62</v>
       </c>
@@ -8283,7 +8454,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>245</v>
       </c>
@@ -8297,7 +8468,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>311</v>
       </c>
@@ -8311,7 +8482,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>283</v>
       </c>
@@ -8325,7 +8496,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>236</v>
       </c>
@@ -8339,7 +8510,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>262</v>
       </c>
@@ -8353,7 +8524,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>208</v>
       </c>
@@ -8367,7 +8538,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>286</v>
       </c>
@@ -8381,7 +8552,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>253</v>
       </c>
@@ -8395,7 +8566,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>304</v>
       </c>
@@ -8409,7 +8580,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>38</v>
       </c>
@@ -8423,7 +8594,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>126</v>
       </c>
@@ -8437,7 +8608,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>316</v>
       </c>
@@ -8451,7 +8622,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>196</v>
       </c>
@@ -8465,7 +8636,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>107</v>
       </c>
@@ -8479,7 +8650,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>318</v>
       </c>
@@ -8493,7 +8664,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>159</v>
       </c>
@@ -8507,7 +8678,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>228</v>
       </c>
@@ -8521,7 +8692,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>293</v>
       </c>
@@ -8535,7 +8706,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>296</v>
       </c>
@@ -8549,7 +8720,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>309</v>
       </c>
@@ -8563,7 +8734,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>242</v>
       </c>
@@ -8577,7 +8748,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>12</v>
       </c>
@@ -8591,7 +8762,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>62</v>
       </c>
@@ -8605,7 +8776,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>245</v>
       </c>
@@ -8619,7 +8790,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>283</v>
       </c>
@@ -8633,7 +8804,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>121</v>
       </c>
@@ -8647,7 +8818,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>286</v>
       </c>
@@ -8661,7 +8832,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>324</v>
       </c>
@@ -8675,7 +8846,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>38</v>
       </c>
@@ -8689,7 +8860,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>196</v>
       </c>
@@ -8703,7 +8874,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>327</v>
       </c>
@@ -8717,7 +8888,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>293</v>
       </c>
@@ -8731,7 +8902,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>296</v>
       </c>
@@ -8745,7 +8916,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>309</v>
       </c>
@@ -8759,7 +8930,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>62</v>
       </c>
@@ -8773,7 +8944,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>245</v>
       </c>
@@ -8787,7 +8958,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>330</v>
       </c>
@@ -8801,7 +8972,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>42</v>
       </c>
@@ -8815,7 +8986,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>286</v>
       </c>
@@ -8829,7 +9000,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>196</v>
       </c>
@@ -8843,7 +9014,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>333</v>
       </c>
@@ -8857,7 +9028,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>296</v>
       </c>
@@ -8871,7 +9042,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>309</v>
       </c>
@@ -8885,7 +9056,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>62</v>
       </c>
@@ -8899,7 +9070,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>152</v>
       </c>
@@ -8913,7 +9084,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>196</v>
       </c>
@@ -8927,7 +9098,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>242</v>
       </c>
@@ -8941,7 +9112,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>62</v>
       </c>
@@ -8955,7 +9126,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>152</v>
       </c>
@@ -8969,7 +9140,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>76</v>
       </c>
@@ -8983,7 +9154,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>126</v>
       </c>
@@ -8997,7 +9168,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>196</v>
       </c>
@@ -9011,7 +9182,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>107</v>
       </c>
@@ -9025,7 +9196,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>339</v>
       </c>
@@ -9039,7 +9210,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>341</v>
       </c>
@@ -9053,7 +9224,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>341</v>
       </c>
@@ -9067,7 +9238,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>341</v>
       </c>
@@ -9081,7 +9252,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>196</v>
       </c>
@@ -9095,7 +9266,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>343</v>
       </c>
@@ -9109,7 +9280,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>345</v>
       </c>
@@ -9123,7 +9294,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>345</v>
       </c>
@@ -9137,7 +9308,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>62</v>
       </c>
@@ -9151,7 +9322,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>260</v>
       </c>
@@ -9165,7 +9336,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>236</v>
       </c>
@@ -9179,7 +9350,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>348</v>
       </c>
@@ -9193,7 +9364,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>350</v>
       </c>
@@ -9207,7 +9378,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>72</v>
       </c>
@@ -9221,7 +9392,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>247</v>
       </c>
@@ -9235,7 +9406,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>354</v>
       </c>
@@ -9249,7 +9420,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>356</v>
       </c>
@@ -9263,7 +9434,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>358</v>
       </c>
@@ -9277,7 +9448,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>359</v>
       </c>
@@ -9291,7 +9462,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>361</v>
       </c>
@@ -9305,7 +9476,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>177</v>
       </c>
@@ -9319,7 +9490,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>361</v>
       </c>
@@ -9333,7 +9504,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>363</v>
       </c>
@@ -9347,7 +9518,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>190</v>
       </c>
@@ -9361,7 +9532,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>365</v>
       </c>
@@ -9375,7 +9546,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>366</v>
       </c>
@@ -9389,7 +9560,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>79</v>
       </c>
@@ -9403,7 +9574,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>361</v>
       </c>
@@ -9417,7 +9588,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>324</v>
       </c>
@@ -9431,7 +9602,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>367</v>
       </c>
@@ -9445,7 +9616,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>36</v>
       </c>
@@ -9459,7 +9630,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>36</v>
       </c>
@@ -9473,7 +9644,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>369</v>
       </c>
@@ -9487,7 +9658,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>196</v>
       </c>
@@ -9501,7 +9672,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>370</v>
       </c>
@@ -9515,7 +9686,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>290</v>
       </c>
@@ -9529,7 +9700,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>107</v>
       </c>
@@ -9543,7 +9714,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>371</v>
       </c>
@@ -9557,7 +9728,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>291</v>
       </c>
@@ -9571,7 +9742,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>228</v>
       </c>
@@ -9585,7 +9756,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>272</v>
       </c>
@@ -9599,7 +9770,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>296</v>
       </c>
@@ -9613,7 +9784,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>242</v>
       </c>
@@ -9627,7 +9798,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>62</v>
       </c>
@@ -9641,7 +9812,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>372</v>
       </c>
@@ -9655,7 +9826,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>282</v>
       </c>
@@ -9669,7 +9840,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>373</v>
       </c>
@@ -9683,7 +9854,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>236</v>
       </c>
@@ -9697,7 +9868,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>217</v>
       </c>
@@ -9711,7 +9882,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>374</v>
       </c>
@@ -9725,7 +9896,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>375</v>
       </c>
@@ -9739,7 +9910,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>376</v>
       </c>
@@ -9753,7 +9924,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>377</v>
       </c>
@@ -9767,7 +9938,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>379</v>
       </c>
@@ -9781,7 +9952,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>272</v>
       </c>
@@ -9795,7 +9966,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>296</v>
       </c>
@@ -9809,7 +9980,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>242</v>
       </c>
@@ -9823,7 +9994,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>373</v>
       </c>
@@ -9837,7 +10008,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>236</v>
       </c>
@@ -9851,7 +10022,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>380</v>
       </c>
@@ -9865,7 +10036,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>361</v>
       </c>
@@ -9879,7 +10050,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>381</v>
       </c>
@@ -9893,7 +10064,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>382</v>
       </c>
@@ -9907,7 +10078,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>126</v>
       </c>
@@ -9921,7 +10092,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>348</v>
       </c>
@@ -9935,7 +10106,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>132</v>
       </c>
@@ -9949,7 +10120,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>383</v>
       </c>
@@ -9963,7 +10134,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>384</v>
       </c>
@@ -9977,7 +10148,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>12</v>
       </c>
@@ -9991,7 +10162,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>385</v>
       </c>
@@ -10005,7 +10176,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>115</v>
       </c>
@@ -10019,7 +10190,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>115</v>
       </c>
@@ -10033,7 +10204,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>72</v>
       </c>
@@ -10047,7 +10218,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>72</v>
       </c>
@@ -10061,7 +10232,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>121</v>
       </c>
@@ -10075,7 +10246,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>121</v>
       </c>
@@ -10089,7 +10260,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>389</v>
       </c>
@@ -10103,7 +10274,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>86</v>
       </c>
@@ -10117,7 +10288,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>118</v>
       </c>
@@ -10137,7 +10308,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>393</v>
       </c>
@@ -10157,7 +10328,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>393</v>
       </c>
@@ -10177,7 +10348,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>393</v>
       </c>
@@ -10197,7 +10368,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>393</v>
       </c>
@@ -10217,7 +10388,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>214</v>
       </c>
@@ -10237,7 +10408,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>398</v>
       </c>
@@ -10257,7 +10428,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>401</v>
       </c>
@@ -10277,7 +10448,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>404</v>
       </c>
@@ -10297,7 +10468,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>10</v>
       </c>
@@ -10317,7 +10488,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>111</v>
       </c>
@@ -10337,7 +10508,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>221</v>
       </c>
@@ -10357,7 +10528,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>98</v>
       </c>
@@ -10377,7 +10548,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>415</v>
       </c>
@@ -10397,7 +10568,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>343</v>
       </c>
@@ -10417,7 +10588,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>307</v>
       </c>
@@ -10437,7 +10608,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>186</v>
       </c>
@@ -10457,7 +10628,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>71</v>
       </c>
@@ -10477,7 +10648,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>427</v>
       </c>
@@ -10497,7 +10668,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>430</v>
       </c>
@@ -10517,7 +10688,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>430</v>
       </c>
@@ -10537,7 +10708,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>433</v>
       </c>
@@ -10557,7 +10728,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>118</v>
       </c>
@@ -10577,7 +10748,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>65</v>
       </c>
@@ -10597,7 +10768,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>440</v>
       </c>
@@ -10617,7 +10788,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>443</v>
       </c>
@@ -10637,7 +10808,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>446</v>
       </c>
@@ -10657,7 +10828,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>307</v>
       </c>
@@ -10677,7 +10848,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>415</v>
       </c>
@@ -10697,7 +10868,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>453</v>
       </c>
@@ -10717,7 +10888,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>453</v>
       </c>
@@ -10737,7 +10908,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>456</v>
       </c>
@@ -10757,7 +10928,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>459</v>
       </c>
@@ -10777,7 +10948,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>462</v>
       </c>
@@ -10797,7 +10968,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>221</v>
       </c>
@@ -10817,7 +10988,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>467</v>
       </c>
@@ -10837,7 +11008,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>470</v>
       </c>
@@ -10857,7 +11028,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>135</v>
       </c>
@@ -10877,7 +11048,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>475</v>
       </c>
@@ -10897,7 +11068,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>478</v>
       </c>
@@ -10917,7 +11088,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>480</v>
       </c>
@@ -10937,7 +11108,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>483</v>
       </c>
@@ -10957,7 +11128,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>389</v>
       </c>
@@ -10977,7 +11148,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>488</v>
       </c>
@@ -10997,7 +11168,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>343</v>
       </c>
@@ -11017,7 +11188,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>493</v>
       </c>
@@ -11037,7 +11208,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>496</v>
       </c>
@@ -11057,7 +11228,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>307</v>
       </c>
@@ -11077,7 +11248,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>501</v>
       </c>
@@ -11097,7 +11268,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>504</v>
       </c>
@@ -11117,7 +11288,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>63</v>
       </c>
@@ -11137,7 +11308,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>83</v>
       </c>
@@ -11157,7 +11328,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>26</v>
       </c>
@@ -11177,7 +11348,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>511</v>
       </c>
@@ -11197,7 +11368,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>514</v>
       </c>
@@ -11217,7 +11388,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>186</v>
       </c>
@@ -11237,7 +11408,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>519</v>
       </c>
@@ -11257,7 +11428,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>522</v>
       </c>
@@ -11277,7 +11448,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>119</v>
       </c>
@@ -11297,7 +11468,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>470</v>
       </c>
@@ -11317,7 +11488,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>30</v>
       </c>
@@ -11337,7 +11508,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>33</v>
       </c>
@@ -11357,7 +11528,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>531</v>
       </c>
@@ -11377,7 +11548,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>534</v>
       </c>
@@ -11397,7 +11568,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>535</v>
       </c>
@@ -11417,7 +11588,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>538</v>
       </c>
@@ -11437,7 +11608,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>541</v>
       </c>
@@ -11457,7 +11628,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -11477,7 +11648,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>546</v>
       </c>
@@ -11497,7 +11668,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>186</v>
       </c>
@@ -11515,6 +11686,486 @@
       </c>
       <c r="F646" t="s">
         <v>550</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A647" t="s">
+        <v>443</v>
+      </c>
+      <c r="B647" t="s">
+        <v>8</v>
+      </c>
+      <c r="C647" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D647" t="s">
+        <v>360</v>
+      </c>
+      <c r="E647" t="s">
+        <v>561</v>
+      </c>
+      <c r="F647" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A648" t="s">
+        <v>551</v>
+      </c>
+      <c r="B648" t="s">
+        <v>13</v>
+      </c>
+      <c r="C648" s="1">
+        <v>46094</v>
+      </c>
+      <c r="D648" t="s">
+        <v>355</v>
+      </c>
+      <c r="E648" t="s">
+        <v>563</v>
+      </c>
+      <c r="F648" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A649" t="s">
+        <v>552</v>
+      </c>
+      <c r="B649" t="s">
+        <v>11</v>
+      </c>
+      <c r="C649" s="1">
+        <v>46090</v>
+      </c>
+      <c r="D649" t="s">
+        <v>390</v>
+      </c>
+      <c r="E649" t="s">
+        <v>565</v>
+      </c>
+      <c r="F649" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>111</v>
+      </c>
+      <c r="B650" t="s">
+        <v>13</v>
+      </c>
+      <c r="C650" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D650" t="s">
+        <v>362</v>
+      </c>
+      <c r="E650" t="s">
+        <v>567</v>
+      </c>
+      <c r="F650" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>427</v>
+      </c>
+      <c r="B651" t="s">
+        <v>19</v>
+      </c>
+      <c r="C651" s="1">
+        <v>46097</v>
+      </c>
+      <c r="D651" t="s">
+        <v>355</v>
+      </c>
+      <c r="E651" t="s">
+        <v>569</v>
+      </c>
+      <c r="F651" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>120</v>
+      </c>
+      <c r="B652" t="s">
+        <v>15</v>
+      </c>
+      <c r="C652" s="1">
+        <v>46090</v>
+      </c>
+      <c r="D652" t="s">
+        <v>364</v>
+      </c>
+      <c r="E652" t="s">
+        <v>571</v>
+      </c>
+      <c r="F652" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>553</v>
+      </c>
+      <c r="B653" t="s">
+        <v>5</v>
+      </c>
+      <c r="C653" s="1">
+        <v>46092</v>
+      </c>
+      <c r="D653" t="s">
+        <v>360</v>
+      </c>
+      <c r="E653" t="s">
+        <v>573</v>
+      </c>
+      <c r="F653" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>496</v>
+      </c>
+      <c r="B654" t="s">
+        <v>5</v>
+      </c>
+      <c r="C654" s="1">
+        <v>46098</v>
+      </c>
+      <c r="D654" t="s">
+        <v>362</v>
+      </c>
+      <c r="E654" t="s">
+        <v>575</v>
+      </c>
+      <c r="F654" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>66</v>
+      </c>
+      <c r="B655" t="s">
+        <v>13</v>
+      </c>
+      <c r="C655" s="1">
+        <v>46083</v>
+      </c>
+      <c r="D655" t="s">
+        <v>390</v>
+      </c>
+      <c r="E655" t="s">
+        <v>577</v>
+      </c>
+      <c r="F655" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>98</v>
+      </c>
+      <c r="B656" t="s">
+        <v>19</v>
+      </c>
+      <c r="C656" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D656" t="s">
+        <v>355</v>
+      </c>
+      <c r="E656" t="s">
+        <v>579</v>
+      </c>
+      <c r="F656" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>453</v>
+      </c>
+      <c r="B657" t="s">
+        <v>13</v>
+      </c>
+      <c r="C657" s="1">
+        <v>46107</v>
+      </c>
+      <c r="D657" t="s">
+        <v>353</v>
+      </c>
+      <c r="E657" t="s">
+        <v>580</v>
+      </c>
+      <c r="F657" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A658" t="s">
+        <v>453</v>
+      </c>
+      <c r="B658" t="s">
+        <v>13</v>
+      </c>
+      <c r="C658" s="1">
+        <v>46106</v>
+      </c>
+      <c r="D658" t="s">
+        <v>360</v>
+      </c>
+      <c r="E658" t="s">
+        <v>582</v>
+      </c>
+      <c r="F658" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A659" t="s">
+        <v>415</v>
+      </c>
+      <c r="B659" t="s">
+        <v>11</v>
+      </c>
+      <c r="C659" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D659" t="s">
+        <v>355</v>
+      </c>
+      <c r="E659" t="s">
+        <v>584</v>
+      </c>
+      <c r="F659" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A660" t="s">
+        <v>554</v>
+      </c>
+      <c r="B660" t="s">
+        <v>13</v>
+      </c>
+      <c r="C660" s="1">
+        <v>46098</v>
+      </c>
+      <c r="D660" t="s">
+        <v>355</v>
+      </c>
+      <c r="E660" t="s">
+        <v>586</v>
+      </c>
+      <c r="F660" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>554</v>
+      </c>
+      <c r="B661" t="s">
+        <v>13</v>
+      </c>
+      <c r="C661" s="1">
+        <v>46091</v>
+      </c>
+      <c r="D661" t="s">
+        <v>588</v>
+      </c>
+      <c r="E661" t="s">
+        <v>589</v>
+      </c>
+      <c r="F661" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>103</v>
+      </c>
+      <c r="B662" t="s">
+        <v>19</v>
+      </c>
+      <c r="C662" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D662" t="s">
+        <v>355</v>
+      </c>
+      <c r="E662" t="s">
+        <v>591</v>
+      </c>
+      <c r="F662" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A663" t="s">
+        <v>555</v>
+      </c>
+      <c r="B663" t="s">
+        <v>8</v>
+      </c>
+      <c r="C663" s="1">
+        <v>46104</v>
+      </c>
+      <c r="D663" t="s">
+        <v>355</v>
+      </c>
+      <c r="E663" t="s">
+        <v>593</v>
+      </c>
+      <c r="F663" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A664" t="s">
+        <v>555</v>
+      </c>
+      <c r="B664" t="s">
+        <v>8</v>
+      </c>
+      <c r="C664" s="1">
+        <v>46097</v>
+      </c>
+      <c r="D664" t="s">
+        <v>355</v>
+      </c>
+      <c r="E664" t="s">
+        <v>349</v>
+      </c>
+      <c r="F664" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="665" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A665" t="s">
+        <v>556</v>
+      </c>
+      <c r="B665" t="s">
+        <v>192</v>
+      </c>
+      <c r="C665" s="1">
+        <v>46106</v>
+      </c>
+      <c r="D665" t="s">
+        <v>355</v>
+      </c>
+      <c r="E665" t="s">
+        <v>596</v>
+      </c>
+      <c r="F665" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="666" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A666" t="s">
+        <v>557</v>
+      </c>
+      <c r="B666" t="s">
+        <v>8</v>
+      </c>
+      <c r="C666" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D666" t="s">
+        <v>362</v>
+      </c>
+      <c r="E666" t="s">
+        <v>598</v>
+      </c>
+      <c r="F666" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="667" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A667" t="s">
+        <v>558</v>
+      </c>
+      <c r="B667" t="s">
+        <v>8</v>
+      </c>
+      <c r="C667" s="1">
+        <v>46106</v>
+      </c>
+      <c r="D667" t="s">
+        <v>355</v>
+      </c>
+      <c r="E667" t="s">
+        <v>600</v>
+      </c>
+      <c r="F667" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A668" t="s">
+        <v>559</v>
+      </c>
+      <c r="B668" t="s">
+        <v>5</v>
+      </c>
+      <c r="C668" s="1">
+        <v>46090</v>
+      </c>
+      <c r="D668" t="s">
+        <v>353</v>
+      </c>
+      <c r="E668" t="s">
+        <v>602</v>
+      </c>
+      <c r="F668" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A669" t="s">
+        <v>560</v>
+      </c>
+      <c r="B669" t="s">
+        <v>19</v>
+      </c>
+      <c r="C669" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D669" t="s">
+        <v>355</v>
+      </c>
+      <c r="E669" t="s">
+        <v>604</v>
+      </c>
+      <c r="F669" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A670" t="s">
+        <v>82</v>
+      </c>
+      <c r="B670" t="s">
+        <v>13</v>
+      </c>
+      <c r="C670" s="1">
+        <v>46106</v>
+      </c>
+      <c r="D670" t="s">
+        <v>353</v>
+      </c>
+      <c r="E670" t="s">
+        <v>606</v>
+      </c>
+      <c r="F670" t="s">
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/data/Desvios de DTOs.xlsx
+++ b/data/Desvios de DTOs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D42C445-F05E-473A-B7E5-247F07B90C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5328DEF-9911-48E4-9346-EADF20681965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="642">
   <si>
     <t>Colaborador</t>
   </si>
@@ -1863,6 +1863,108 @@
   </si>
   <si>
     <t>Motorista chegou as 15:19 e não acompanhou a Blitz Ajudante chegou as 15:26 e não acompanhou.Produtos da Companhia ( Caixaria ) sendo colocado no chão para a conferência ( orientar ajudante e Conferente a sempre colocar os produtos sobre os PBRs, conforme descrito no padrão)Manuseio incorreto, pegada inicial de algumas caixas sendo feita apenas por uma das mãos( orientação sobre Manuseio correto)Ajudante rasgou o strech e deixou no chão na área de passagem dele mesmo para realização da Blitz, risco de tropeçar ( Reforçar a importância e o dever do 5S)Atualizar no padrão o uso da presilha nos fitilhos Colocar o padrão impresso nas áreas.</t>
+  </si>
+  <si>
+    <t>Não segregou a área de amarração durante a atividade</t>
+  </si>
+  <si>
+    <t>Ver e agirRelato ato inseguro</t>
+  </si>
+  <si>
+    <t>Chave solta no caminhão</t>
+  </si>
+  <si>
+    <t>Em conversa com manobra observamos algumas oportunidades no controle de chave dentro do armazém que vou levar para reunião de segurança para discutir sobre o assunto.</t>
+  </si>
+  <si>
+    <t>CARLOS DE ARRUDA NETO</t>
+  </si>
+  <si>
+    <t>Passei as informações sobre o ato inseguro, para poder evitar puxar a paleteira.</t>
+  </si>
+  <si>
+    <t>Utilizando correntinha durante a atividade</t>
+  </si>
+  <si>
+    <t>GEOVANI PICH ROSSIN</t>
+  </si>
+  <si>
+    <t>Ver e agir, com o colaborador sobre manuseio de paleteira</t>
+  </si>
+  <si>
+    <t>Colaborador estava puxando a paleteira ao invés de empurrar</t>
+  </si>
+  <si>
+    <t>Ver e agir, Realizado o treinamento com o colaborador sobre o manuseio correto de paleteiras.</t>
+  </si>
+  <si>
+    <t>Não executou check do trava quedas.</t>
+  </si>
+  <si>
+    <t>Ver e agir, orientado no fim do DTO realizar check list do trava quedas para se ancorar e subir no caminhão pra enlonar.</t>
+  </si>
+  <si>
+    <t>Não realizou a segregação do local conforme o padrão</t>
+  </si>
+  <si>
+    <t>Realizar reciclagem com o funcionário José Benedito referente ao uso de segregação correta da área conforme o padrão durante as atividades.</t>
+  </si>
+  <si>
+    <t>Colaborador não realizou o checklist dos equipamentos de amarração, realizado somente a inspeção física.</t>
+  </si>
+  <si>
+    <t>Colaborador não realizou o checklist dos equipamentos de amarração, realizado somente a inspeção física.Colaborador Orientado a realizar também o checklist digital, gerando histórico da Atividade e qualidade do equipamento.</t>
+  </si>
+  <si>
+    <t>Area não foi segregada, porém alegou que é por conta de não ter movimentacao e o 5S da area não estava feito antes de iniciar a atividade</t>
+  </si>
+  <si>
+    <t>Reforçar a importância da segregacao, mesmo que não tenha movimentacao.Reforçar onde consular o padrao</t>
+  </si>
+  <si>
+    <t>Não utilização de luva</t>
+  </si>
+  <si>
+    <t>Time de frota reforçou em troca de turno a necessidade da utilização de todos os epi</t>
+  </si>
+  <si>
+    <t>RODRIGO MELO RIBEIRO</t>
+  </si>
+  <si>
+    <t>Colaborador estava manuseando de forma incorreta.</t>
+  </si>
+  <si>
+    <t>Colaborador foi orientado sobre a posição ergonômica ao manusear a caixaria na área que estava separando os resíduos para o 5s.</t>
+  </si>
+  <si>
+    <t>SIDNEI SILVA DE LIMA</t>
+  </si>
+  <si>
+    <t>Colaborador ao descarregar está conduzindo o palete de frente</t>
+  </si>
+  <si>
+    <t>Realizar treinamento com o colaborador sobre descarregamento de forma segura, orientado sobre a importância de andar de ré com o veículo carregado, também como é novo de casa foi orientado verbalmente porém está ciente que em caso de recorrências pode gerar medida.</t>
+  </si>
+  <si>
+    <t>Carregando paletes com empilhadeira de frente</t>
+  </si>
+  <si>
+    <t>Treinamento com o colaborador sobre a forma correta de conduzir a empilhadeira quando estiver carregada, e advertência verbal pois é novo de operação, caso ocorra novamente após o treinamento está ciente das medidas.</t>
+  </si>
+  <si>
+    <t>VICTOR HENRIQUE PEREIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>Colaborador fez checklist de uma paleteira, porém na execução do Dto ele utilizava outra paleteira que viu mais perto.</t>
+  </si>
+  <si>
+    <t>Colaborador foi orientado a deixar na segregação a paleteira e pegar a paleteira correta que foi feita o checklist e foi falado sobre a importância da inspeção pre-uso.</t>
+  </si>
+  <si>
+    <t>Está utilizando correntinha no pescoço</t>
+  </si>
+  <si>
+    <t>Ver e agir Relato ato inseguro</t>
   </si>
 </sst>
 </file>
@@ -2215,7 +2317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}">
-  <dimension ref="A1:F670"/>
+  <dimension ref="A1:F686"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
@@ -12168,6 +12270,326 @@
         <v>607</v>
       </c>
     </row>
+    <row r="671" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A671" t="s">
+        <v>343</v>
+      </c>
+      <c r="B671" t="s">
+        <v>8</v>
+      </c>
+      <c r="C671" s="1">
+        <v>46114</v>
+      </c>
+      <c r="D671" t="s">
+        <v>360</v>
+      </c>
+      <c r="E671" t="s">
+        <v>608</v>
+      </c>
+      <c r="F671" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="672" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A672" t="s">
+        <v>221</v>
+      </c>
+      <c r="B672" t="s">
+        <v>192</v>
+      </c>
+      <c r="C672" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D672" t="s">
+        <v>355</v>
+      </c>
+      <c r="E672" t="s">
+        <v>610</v>
+      </c>
+      <c r="F672" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A673" t="s">
+        <v>612</v>
+      </c>
+      <c r="B673" t="s">
+        <v>5</v>
+      </c>
+      <c r="C673" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D673" t="s">
+        <v>362</v>
+      </c>
+      <c r="E673" t="s">
+        <v>497</v>
+      </c>
+      <c r="F673" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>307</v>
+      </c>
+      <c r="B674" t="s">
+        <v>8</v>
+      </c>
+      <c r="C674" s="1">
+        <v>46114</v>
+      </c>
+      <c r="D674" t="s">
+        <v>357</v>
+      </c>
+      <c r="E674" t="s">
+        <v>614</v>
+      </c>
+      <c r="F674" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
+        <v>615</v>
+      </c>
+      <c r="B675" t="s">
+        <v>11</v>
+      </c>
+      <c r="C675" s="1">
+        <v>46128</v>
+      </c>
+      <c r="D675" t="s">
+        <v>362</v>
+      </c>
+      <c r="E675" t="s">
+        <v>575</v>
+      </c>
+      <c r="F675" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>615</v>
+      </c>
+      <c r="B676" t="s">
+        <v>11</v>
+      </c>
+      <c r="C676" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D676" t="s">
+        <v>362</v>
+      </c>
+      <c r="E676" t="s">
+        <v>617</v>
+      </c>
+      <c r="F676" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>339</v>
+      </c>
+      <c r="B677" t="s">
+        <v>11</v>
+      </c>
+      <c r="C677" s="1">
+        <v>46139</v>
+      </c>
+      <c r="D677" t="s">
+        <v>386</v>
+      </c>
+      <c r="E677" t="s">
+        <v>619</v>
+      </c>
+      <c r="F677" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>52</v>
+      </c>
+      <c r="B678" t="s">
+        <v>8</v>
+      </c>
+      <c r="C678" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D678" t="s">
+        <v>360</v>
+      </c>
+      <c r="E678" t="s">
+        <v>621</v>
+      </c>
+      <c r="F678" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>158</v>
+      </c>
+      <c r="B679" t="s">
+        <v>13</v>
+      </c>
+      <c r="C679" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D679" t="s">
+        <v>386</v>
+      </c>
+      <c r="E679" t="s">
+        <v>623</v>
+      </c>
+      <c r="F679" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>158</v>
+      </c>
+      <c r="B680" t="s">
+        <v>13</v>
+      </c>
+      <c r="C680" s="1">
+        <v>46125</v>
+      </c>
+      <c r="D680" t="s">
+        <v>360</v>
+      </c>
+      <c r="E680" t="s">
+        <v>625</v>
+      </c>
+      <c r="F680" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>559</v>
+      </c>
+      <c r="B681" t="s">
+        <v>5</v>
+      </c>
+      <c r="C681" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D681" t="s">
+        <v>357</v>
+      </c>
+      <c r="E681" t="s">
+        <v>627</v>
+      </c>
+      <c r="F681" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>629</v>
+      </c>
+      <c r="B682" t="s">
+        <v>13</v>
+      </c>
+      <c r="C682" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D682" t="s">
+        <v>353</v>
+      </c>
+      <c r="E682" t="s">
+        <v>630</v>
+      </c>
+      <c r="F682" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>632</v>
+      </c>
+      <c r="B683" t="s">
+        <v>11</v>
+      </c>
+      <c r="C683" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D683" t="s">
+        <v>378</v>
+      </c>
+      <c r="E683" t="s">
+        <v>633</v>
+      </c>
+      <c r="F683" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A684" t="s">
+        <v>632</v>
+      </c>
+      <c r="B684" t="s">
+        <v>11</v>
+      </c>
+      <c r="C684" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D684" t="s">
+        <v>390</v>
+      </c>
+      <c r="E684" t="s">
+        <v>635</v>
+      </c>
+      <c r="F684" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>637</v>
+      </c>
+      <c r="B685" t="s">
+        <v>13</v>
+      </c>
+      <c r="C685" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D685" t="s">
+        <v>357</v>
+      </c>
+      <c r="E685" t="s">
+        <v>638</v>
+      </c>
+      <c r="F685" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>305</v>
+      </c>
+      <c r="B686" t="s">
+        <v>8</v>
+      </c>
+      <c r="C686" s="1">
+        <v>46114</v>
+      </c>
+      <c r="D686" t="s">
+        <v>357</v>
+      </c>
+      <c r="E686" t="s">
+        <v>640</v>
+      </c>
+      <c r="F686" t="s">
+        <v>641</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D576" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D576">

--- a/data/Desvios de DTOs.xlsx
+++ b/data/Desvios de DTOs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5328DEF-9911-48E4-9346-EADF20681965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C4AB6D-013A-4ED7-AE33-484D7448B886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2389" uniqueCount="699">
   <si>
     <t>Colaborador</t>
   </si>
@@ -1965,6 +1965,177 @@
   </si>
   <si>
     <t>Ver e agir Relato ato inseguro</t>
+  </si>
+  <si>
+    <t>colaborador pegando duas caixas de longe NECK ao mesmo tempo,</t>
+  </si>
+  <si>
+    <t>colaborador foi orientado sobre os riscos de executar o manuseio manual incorreto</t>
+  </si>
+  <si>
+    <t>ALEX DE OLIVEIRA MOURA</t>
+  </si>
+  <si>
+    <t>CD ARACAJU</t>
+  </si>
+  <si>
+    <t>Colaborador acabou puxando a paleteira invés de empurrar. Foi orientado de imediato</t>
+  </si>
+  <si>
+    <t>Reciclagem do colaborador sobre o procedimento de manuseio de paleteira + orientação inloco</t>
+  </si>
+  <si>
+    <t>estava puxando paleteira pesada durante deslocamento no picking</t>
+  </si>
+  <si>
+    <t>feed back sobre manuseio de paleteiras adequado</t>
+  </si>
+  <si>
+    <t>uso de celular  em quanto caminha</t>
+  </si>
+  <si>
+    <t>ver e agir com manobra em uso de celular enquanto caminha</t>
+  </si>
+  <si>
+    <t>ANDREY FERREIRA GONZAGA</t>
+  </si>
+  <si>
+    <t>ajudante puxa paleteira</t>
+  </si>
+  <si>
+    <t>orientado no momento do feed back sobre manuseio correto de paleteira (empurrar)</t>
+  </si>
+  <si>
+    <t>velocidade acima do estabelecido no plano de tráfego</t>
+  </si>
+  <si>
+    <t>repassar vídeo sobre o plano de tráfego</t>
+  </si>
+  <si>
+    <t>operador não estava usando o Boné com proteção</t>
+  </si>
+  <si>
+    <t>realizado ver e agir</t>
+  </si>
+  <si>
+    <t>Execução Segura de Abastecimento de GLP</t>
+  </si>
+  <si>
+    <t>A empilhadeira Yale foi estacionada do lado incorreto e fora do padrão, pois o cilindro de gás foi instalado do lado oposto, o que  inviabilizou o abastecimento correto e a descida do colaborador da empilhadeira sem que o mesmo precisasse pular a mureta de segregação. Na posição correta da empilhadeira a mangueira do abastecimento não alcança o local de encaixe do cilíndro. Além disso a viseira do capacete do colaborar está com a visibilidade comprometida por conter diversas ranhuras e que a luva de proteção não fornece a flexibilidade e acessibilidade necessária para realizar a tarefa e que o tamanho da bota não está adequado.</t>
+  </si>
+  <si>
+    <t>Verificar a possibilidade de ajustar a instalação dos cilindros para o lado correto de abastecimento nas empilhadeiras Yale e, também, a troca da viseira do capacete de proteção, assim como fornecer uma bota de tamanho adequado para o colaborador. Solicitar também ao financeiro que seja cortada a grama ao redores do local de abastecimento.</t>
+  </si>
+  <si>
+    <t>operador não colocou a chave na caixinha de bloqueios, guardou no bolso.</t>
+  </si>
+  <si>
+    <t>Realizar treinamento com o colaborador sobre bloqueio de energia e uso de segregação do motorista carreteiro, o qual não estava na área de espera, feito ver e agir.</t>
+  </si>
+  <si>
+    <t>IZAIAS MARCELO FERREIRA</t>
+  </si>
+  <si>
+    <t>ajudante no momento precisou girar o palet e acabou puxando ao invés de empurrar.</t>
+  </si>
+  <si>
+    <t>treinar ajudante no passo a passo correto do manuseio com a paleteira</t>
+  </si>
+  <si>
+    <t>JESSER MENEZES GONCALVES</t>
+  </si>
+  <si>
+    <t>utilização de celular com máquina em movimento</t>
+  </si>
+  <si>
+    <t>ver e agir colaborador tratado</t>
+  </si>
+  <si>
+    <t>Execução Segura de atividades em níveis diferentes</t>
+  </si>
+  <si>
+    <t>Utilização dos 3 pontos de apoio corretamente</t>
+  </si>
+  <si>
+    <t>Reforçar e treinar o colaborador na atividade.</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS PATINO ANDRADEZ</t>
+  </si>
+  <si>
+    <t>não realizou checklist da paleteiras.</t>
+  </si>
+  <si>
+    <t>realizado ver e agir.</t>
+  </si>
+  <si>
+    <t>LUCAS ALVES DA SILVA</t>
+  </si>
+  <si>
+    <t>colaborador pegando pela lateral dos plástico dos P.A Lata 350ml, pegando duas caixas por vez, sendo uma em cada mão.</t>
+  </si>
+  <si>
+    <t>colaborador Orientado na hora sobre Manuseio incorreto de pega pela aste lateral da embalagem do produto e sim e sim por debaixo com as duas mãos.</t>
+  </si>
+  <si>
+    <t>LUCIANO NASCIMENTO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Colaborador acabou jogando a cinta para o ajudante da amarração, invés de passar o item em mãos</t>
+  </si>
+  <si>
+    <t>Instrução para os colocadores sobre o desvio de segurança cometido e explicação sobre os riscos envolvidos Verificar disponibilidade de padrão de amarração na área do retorno de rota</t>
+  </si>
+  <si>
+    <t>Estava puxando a paleteira e pegando 2 caixas de lata por vezes.</t>
+  </si>
+  <si>
+    <t>Ver e agir sobre o padrão de utilização da paleteira. Treinamento de qualidade.</t>
+  </si>
+  <si>
+    <t>PATRICK WILLIAM DE SOUZA SILVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execução segura de controle de chave</t>
+  </si>
+  <si>
+    <t>Não utilizou o trava rodas durante a descarga, e aparentemente o freteiro João estava com as chaves do caminhão em seu bolso.</t>
+  </si>
+  <si>
+    <t>Colaborador Patrick, conferente Jaqueline e Freteiro orientados no ato da descarga.</t>
+  </si>
+  <si>
+    <t>PAULO VITOR DE ARAUJO</t>
+  </si>
+  <si>
+    <t>Colaborador puxando a paleteira ao invés de empurrar.</t>
+  </si>
+  <si>
+    <t>realizar reciclagem no treinamento de forma correta de abastecimento do marketing place</t>
+  </si>
+  <si>
+    <t>REINALDO LOPES CAVADAS</t>
+  </si>
+  <si>
+    <t>distância homem máquina. ajudante se aproximou da máquina com ela ligada em movimento.</t>
+  </si>
+  <si>
+    <t>tratar operador sobre o processo</t>
+  </si>
+  <si>
+    <t>utilização da segregação</t>
+  </si>
+  <si>
+    <t>ver e agir, orientação sobre o uso correto da segregação</t>
+  </si>
+  <si>
+    <t>ROQUE SANDRO ALMEIDA MAXIMO</t>
+  </si>
+  <si>
+    <t>mecânico não retirou a chave do contato.</t>
+  </si>
+  <si>
+    <t>Reorientação. Ao términar o serviço a chave precisa ser guardada na caixinha e a caixinha fechada.</t>
   </si>
 </sst>
 </file>
@@ -2317,16 +2488,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}">
-  <dimension ref="A1:F686"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F708"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="139.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="139.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2340,7 +2511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2354,7 +2525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2368,7 +2539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2382,7 +2553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2396,7 +2567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2410,7 +2581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2424,7 +2595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2438,7 +2609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -2452,7 +2623,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2466,7 +2637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2480,7 +2651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2494,7 +2665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2508,7 +2679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2522,7 +2693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2536,7 +2707,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -2550,7 +2721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2564,7 +2735,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -2578,7 +2749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -2592,7 +2763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2606,7 +2777,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2620,7 +2791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -2634,7 +2805,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2648,7 +2819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -2662,7 +2833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2676,7 +2847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -2690,7 +2861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -2704,7 +2875,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -2718,7 +2889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -2732,7 +2903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -2746,7 +2917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -2760,7 +2931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -2774,7 +2945,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -2788,7 +2959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2802,7 +2973,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2816,7 +2987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2830,7 +3001,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2844,7 +3015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2858,7 +3029,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -2872,7 +3043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -2886,7 +3057,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2900,7 +3071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2914,7 +3085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2928,7 +3099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2942,7 +3113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -2956,7 +3127,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -2970,7 +3141,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -2984,7 +3155,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -2998,7 +3169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -3012,7 +3183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -3026,7 +3197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -3040,7 +3211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -3054,7 +3225,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -3068,7 +3239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -3082,7 +3253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -3096,7 +3267,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -3110,7 +3281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -3124,7 +3295,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -3138,7 +3309,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -3152,7 +3323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>32</v>
       </c>
@@ -3166,7 +3337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -3180,7 +3351,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -3194,7 +3365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -3208,7 +3379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -3222,7 +3393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -3236,7 +3407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -3250,7 +3421,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -3264,7 +3435,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -3278,7 +3449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -3292,7 +3463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -3306,7 +3477,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -3320,7 +3491,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -3334,7 +3505,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -3348,7 +3519,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>45</v>
       </c>
@@ -3362,7 +3533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -3376,7 +3547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -3390,7 +3561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -3404,7 +3575,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -3418,7 +3589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -3432,7 +3603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -3446,7 +3617,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>78</v>
       </c>
@@ -3460,7 +3631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>79</v>
       </c>
@@ -3474,7 +3645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>80</v>
       </c>
@@ -3488,7 +3659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>81</v>
       </c>
@@ -3502,7 +3673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -3516,7 +3687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>82</v>
       </c>
@@ -3530,7 +3701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3544,7 +3715,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>84</v>
       </c>
@@ -3558,7 +3729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>85</v>
       </c>
@@ -3572,7 +3743,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>86</v>
       </c>
@@ -3586,7 +3757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -3600,7 +3771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>87</v>
       </c>
@@ -3614,7 +3785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>55</v>
       </c>
@@ -3628,7 +3799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>63</v>
       </c>
@@ -3642,7 +3813,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>63</v>
       </c>
@@ -3656,7 +3827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>63</v>
       </c>
@@ -3670,7 +3841,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>63</v>
       </c>
@@ -3684,7 +3855,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>63</v>
       </c>
@@ -3698,7 +3869,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>89</v>
       </c>
@@ -3712,7 +3883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>89</v>
       </c>
@@ -3726,7 +3897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>90</v>
       </c>
@@ -3740,7 +3911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>90</v>
       </c>
@@ -3754,7 +3925,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -3768,7 +3939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>91</v>
       </c>
@@ -3782,7 +3953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>92</v>
       </c>
@@ -3796,7 +3967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>64</v>
       </c>
@@ -3810,7 +3981,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>37</v>
       </c>
@@ -3824,7 +3995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>93</v>
       </c>
@@ -3838,7 +4009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>31</v>
       </c>
@@ -3852,7 +4023,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>94</v>
       </c>
@@ -3866,7 +4037,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>95</v>
       </c>
@@ -3880,7 +4051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>96</v>
       </c>
@@ -3894,7 +4065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -3908,7 +4079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>98</v>
       </c>
@@ -3922,7 +4093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -3936,7 +4107,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>52</v>
       </c>
@@ -3950,7 +4121,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>99</v>
       </c>
@@ -3964,7 +4135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>100</v>
       </c>
@@ -3978,7 +4149,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>100</v>
       </c>
@@ -3992,7 +4163,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>101</v>
       </c>
@@ -4006,7 +4177,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>101</v>
       </c>
@@ -4020,7 +4191,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>100</v>
       </c>
@@ -4034,7 +4205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>100</v>
       </c>
@@ -4048,7 +4219,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>100</v>
       </c>
@@ -4062,7 +4233,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>36</v>
       </c>
@@ -4076,7 +4247,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>102</v>
       </c>
@@ -4090,7 +4261,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>103</v>
       </c>
@@ -4104,7 +4275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>104</v>
       </c>
@@ -4118,7 +4289,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>105</v>
       </c>
@@ -4132,7 +4303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>106</v>
       </c>
@@ -4146,7 +4317,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>107</v>
       </c>
@@ -4160,7 +4331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>108</v>
       </c>
@@ -4174,7 +4345,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>109</v>
       </c>
@@ -4188,7 +4359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>110</v>
       </c>
@@ -4202,7 +4373,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>36</v>
       </c>
@@ -4216,7 +4387,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>111</v>
       </c>
@@ -4230,7 +4401,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>112</v>
       </c>
@@ -4244,7 +4415,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>113</v>
       </c>
@@ -4258,7 +4429,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>12</v>
       </c>
@@ -4272,7 +4443,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>114</v>
       </c>
@@ -4286,7 +4457,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>115</v>
       </c>
@@ -4300,7 +4471,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>116</v>
       </c>
@@ -4314,7 +4485,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>117</v>
       </c>
@@ -4328,7 +4499,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>118</v>
       </c>
@@ -4342,7 +4513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>118</v>
       </c>
@@ -4356,7 +4527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>118</v>
       </c>
@@ -4370,7 +4541,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>118</v>
       </c>
@@ -4384,7 +4555,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>115</v>
       </c>
@@ -4398,7 +4569,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>119</v>
       </c>
@@ -4412,7 +4583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>120</v>
       </c>
@@ -4426,7 +4597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>121</v>
       </c>
@@ -4440,7 +4611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>121</v>
       </c>
@@ -4454,7 +4625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>121</v>
       </c>
@@ -4468,7 +4639,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>122</v>
       </c>
@@ -4482,7 +4653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>55</v>
       </c>
@@ -4496,7 +4667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>80</v>
       </c>
@@ -4510,7 +4681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>80</v>
       </c>
@@ -4524,7 +4695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>80</v>
       </c>
@@ -4538,7 +4709,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>123</v>
       </c>
@@ -4552,7 +4723,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>123</v>
       </c>
@@ -4566,7 +4737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -4580,7 +4751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -4594,7 +4765,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>124</v>
       </c>
@@ -4608,7 +4779,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -4622,7 +4793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>125</v>
       </c>
@@ -4636,7 +4807,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>126</v>
       </c>
@@ -4650,7 +4821,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>127</v>
       </c>
@@ -4664,7 +4835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>128</v>
       </c>
@@ -4678,7 +4849,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>129</v>
       </c>
@@ -4692,7 +4863,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>73</v>
       </c>
@@ -4706,7 +4877,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>130</v>
       </c>
@@ -4720,7 +4891,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>131</v>
       </c>
@@ -4734,7 +4905,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>132</v>
       </c>
@@ -4748,7 +4919,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>133</v>
       </c>
@@ -4762,7 +4933,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>134</v>
       </c>
@@ -4776,7 +4947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>134</v>
       </c>
@@ -4790,7 +4961,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>135</v>
       </c>
@@ -4804,7 +4975,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>93</v>
       </c>
@@ -4818,7 +4989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>93</v>
       </c>
@@ -4832,7 +5003,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>134</v>
       </c>
@@ -4846,7 +5017,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>125</v>
       </c>
@@ -4860,7 +5031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>136</v>
       </c>
@@ -4874,7 +5045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>137</v>
       </c>
@@ -4888,7 +5059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>138</v>
       </c>
@@ -4902,7 +5073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>139</v>
       </c>
@@ -4916,7 +5087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>139</v>
       </c>
@@ -4930,7 +5101,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>137</v>
       </c>
@@ -4944,7 +5115,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>137</v>
       </c>
@@ -4958,7 +5129,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>137</v>
       </c>
@@ -4972,7 +5143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>137</v>
       </c>
@@ -4986,7 +5157,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>140</v>
       </c>
@@ -5000,7 +5171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>140</v>
       </c>
@@ -5014,7 +5185,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>141</v>
       </c>
@@ -5028,7 +5199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>142</v>
       </c>
@@ -5042,7 +5213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>143</v>
       </c>
@@ -5056,7 +5227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>143</v>
       </c>
@@ -5070,7 +5241,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>144</v>
       </c>
@@ -5084,7 +5255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>145</v>
       </c>
@@ -5098,7 +5269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>135</v>
       </c>
@@ -5112,7 +5283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>146</v>
       </c>
@@ -5126,7 +5297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>147</v>
       </c>
@@ -5140,7 +5311,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>148</v>
       </c>
@@ -5154,7 +5325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>148</v>
       </c>
@@ -5168,7 +5339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>149</v>
       </c>
@@ -5182,7 +5353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>149</v>
       </c>
@@ -5196,7 +5367,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>150</v>
       </c>
@@ -5210,7 +5381,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>39</v>
       </c>
@@ -5224,7 +5395,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>151</v>
       </c>
@@ -5238,7 +5409,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>151</v>
       </c>
@@ -5252,7 +5423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>152</v>
       </c>
@@ -5266,7 +5437,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>153</v>
       </c>
@@ -5280,7 +5451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>153</v>
       </c>
@@ -5294,7 +5465,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>153</v>
       </c>
@@ -5308,7 +5479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>154</v>
       </c>
@@ -5322,7 +5493,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>155</v>
       </c>
@@ -5336,7 +5507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>155</v>
       </c>
@@ -5350,7 +5521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>155</v>
       </c>
@@ -5364,7 +5535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>156</v>
       </c>
@@ -5378,7 +5549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>156</v>
       </c>
@@ -5392,7 +5563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>107</v>
       </c>
@@ -5406,7 +5577,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>127</v>
       </c>
@@ -5420,7 +5591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>157</v>
       </c>
@@ -5434,7 +5605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>67</v>
       </c>
@@ -5448,7 +5619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>158</v>
       </c>
@@ -5462,7 +5633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>158</v>
       </c>
@@ -5476,7 +5647,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>159</v>
       </c>
@@ -5490,7 +5661,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>160</v>
       </c>
@@ -5504,7 +5675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>161</v>
       </c>
@@ -5518,7 +5689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>161</v>
       </c>
@@ -5532,7 +5703,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>162</v>
       </c>
@@ -5546,7 +5717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>162</v>
       </c>
@@ -5560,7 +5731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>163</v>
       </c>
@@ -5574,7 +5745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>163</v>
       </c>
@@ -5588,7 +5759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>164</v>
       </c>
@@ -5602,7 +5773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>164</v>
       </c>
@@ -5616,7 +5787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>165</v>
       </c>
@@ -5630,7 +5801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>165</v>
       </c>
@@ -5644,7 +5815,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>12</v>
       </c>
@@ -5658,7 +5829,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>139</v>
       </c>
@@ -5672,7 +5843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>127</v>
       </c>
@@ -5686,7 +5857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>163</v>
       </c>
@@ -5700,7 +5871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>166</v>
       </c>
@@ -5714,7 +5885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>166</v>
       </c>
@@ -5728,7 +5899,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>167</v>
       </c>
@@ -5742,7 +5913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>167</v>
       </c>
@@ -5756,7 +5927,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>168</v>
       </c>
@@ -5770,7 +5941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>155</v>
       </c>
@@ -5784,7 +5955,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>169</v>
       </c>
@@ -5798,7 +5969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>170</v>
       </c>
@@ -5812,7 +5983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>171</v>
       </c>
@@ -5826,7 +5997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>172</v>
       </c>
@@ -5840,7 +6011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>153</v>
       </c>
@@ -5854,7 +6025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>122</v>
       </c>
@@ -5868,7 +6039,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>173</v>
       </c>
@@ -5882,7 +6053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>173</v>
       </c>
@@ -5896,7 +6067,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>174</v>
       </c>
@@ -5910,7 +6081,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>174</v>
       </c>
@@ -5924,7 +6095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>52</v>
       </c>
@@ -5938,7 +6109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>83</v>
       </c>
@@ -5952,7 +6123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>175</v>
       </c>
@@ -5966,7 +6137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>175</v>
       </c>
@@ -5980,7 +6151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>176</v>
       </c>
@@ -5994,7 +6165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>118</v>
       </c>
@@ -6008,7 +6179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>177</v>
       </c>
@@ -6022,7 +6193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>96</v>
       </c>
@@ -6036,7 +6207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>178</v>
       </c>
@@ -6050,7 +6221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>10</v>
       </c>
@@ -6064,7 +6235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>10</v>
       </c>
@@ -6078,7 +6249,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>136</v>
       </c>
@@ -6092,7 +6263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>84</v>
       </c>
@@ -6106,7 +6277,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>179</v>
       </c>
@@ -6120,7 +6291,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>97</v>
       </c>
@@ -6134,7 +6305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>180</v>
       </c>
@@ -6148,7 +6319,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>181</v>
       </c>
@@ -6162,7 +6333,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>181</v>
       </c>
@@ -6176,7 +6347,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>182</v>
       </c>
@@ -6190,7 +6361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>183</v>
       </c>
@@ -6204,7 +6375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>183</v>
       </c>
@@ -6218,7 +6389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>183</v>
       </c>
@@ -6232,7 +6403,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>184</v>
       </c>
@@ -6246,7 +6417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>153</v>
       </c>
@@ -6260,7 +6431,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>185</v>
       </c>
@@ -6274,7 +6445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>185</v>
       </c>
@@ -6288,7 +6459,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>123</v>
       </c>
@@ -6302,7 +6473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>186</v>
       </c>
@@ -6316,7 +6487,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>186</v>
       </c>
@@ -6330,7 +6501,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>187</v>
       </c>
@@ -6344,7 +6515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>7</v>
       </c>
@@ -6358,7 +6529,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>7</v>
       </c>
@@ -6372,7 +6543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>188</v>
       </c>
@@ -6386,7 +6557,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>127</v>
       </c>
@@ -6400,7 +6571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>189</v>
       </c>
@@ -6414,7 +6585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>123</v>
       </c>
@@ -6428,7 +6599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>55</v>
       </c>
@@ -6442,7 +6613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>120</v>
       </c>
@@ -6456,7 +6627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>45</v>
       </c>
@@ -6470,7 +6641,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>190</v>
       </c>
@@ -6484,7 +6655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>113</v>
       </c>
@@ -6498,7 +6669,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>191</v>
       </c>
@@ -6512,7 +6683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>193</v>
       </c>
@@ -6526,7 +6697,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>194</v>
       </c>
@@ -6540,7 +6711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>195</v>
       </c>
@@ -6554,7 +6725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>196</v>
       </c>
@@ -6568,7 +6739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>197</v>
       </c>
@@ -6582,7 +6753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>197</v>
       </c>
@@ -6596,7 +6767,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>198</v>
       </c>
@@ -6610,7 +6781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>198</v>
       </c>
@@ -6624,7 +6795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>199</v>
       </c>
@@ -6638,7 +6809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>199</v>
       </c>
@@ -6652,7 +6823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>58</v>
       </c>
@@ -6666,7 +6837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>200</v>
       </c>
@@ -6680,7 +6851,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>201</v>
       </c>
@@ -6694,7 +6865,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>202</v>
       </c>
@@ -6708,7 +6879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>203</v>
       </c>
@@ -6722,7 +6893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>204</v>
       </c>
@@ -6736,7 +6907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>205</v>
       </c>
@@ -6750,7 +6921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>121</v>
       </c>
@@ -6764,7 +6935,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>121</v>
       </c>
@@ -6778,7 +6949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>206</v>
       </c>
@@ -6792,7 +6963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>207</v>
       </c>
@@ -6806,7 +6977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>208</v>
       </c>
@@ -6820,7 +6991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>209</v>
       </c>
@@ -6834,7 +7005,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>210</v>
       </c>
@@ -6848,7 +7019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>116</v>
       </c>
@@ -6862,7 +7033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>116</v>
       </c>
@@ -6876,7 +7047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>116</v>
       </c>
@@ -6890,7 +7061,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>116</v>
       </c>
@@ -6904,7 +7075,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>63</v>
       </c>
@@ -6918,7 +7089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>63</v>
       </c>
@@ -6932,7 +7103,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>124</v>
       </c>
@@ -6946,7 +7117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>96</v>
       </c>
@@ -6960,7 +7131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>96</v>
       </c>
@@ -6974,7 +7145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>211</v>
       </c>
@@ -6988,7 +7159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>212</v>
       </c>
@@ -7002,7 +7173,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>213</v>
       </c>
@@ -7016,7 +7187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>214</v>
       </c>
@@ -7030,7 +7201,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>215</v>
       </c>
@@ -7044,7 +7215,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>216</v>
       </c>
@@ -7058,7 +7229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>217</v>
       </c>
@@ -7072,7 +7243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>198</v>
       </c>
@@ -7086,7 +7257,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>195</v>
       </c>
@@ -7100,7 +7271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>218</v>
       </c>
@@ -7114,7 +7285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>219</v>
       </c>
@@ -7128,7 +7299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>83</v>
       </c>
@@ -7142,7 +7313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>196</v>
       </c>
@@ -7156,7 +7327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>220</v>
       </c>
@@ -7170,7 +7341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>221</v>
       </c>
@@ -7184,7 +7355,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>222</v>
       </c>
@@ -7198,7 +7369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>204</v>
       </c>
@@ -7212,7 +7383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>223</v>
       </c>
@@ -7226,7 +7397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>157</v>
       </c>
@@ -7240,7 +7411,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>76</v>
       </c>
@@ -7254,7 +7425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>224</v>
       </c>
@@ -7268,7 +7439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>225</v>
       </c>
@@ -7282,7 +7453,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>196</v>
       </c>
@@ -7296,7 +7467,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>105</v>
       </c>
@@ -7310,7 +7481,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>228</v>
       </c>
@@ -7324,7 +7495,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>230</v>
       </c>
@@ -7338,7 +7509,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>204</v>
       </c>
@@ -7352,7 +7523,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>205</v>
       </c>
@@ -7366,7 +7537,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>234</v>
       </c>
@@ -7380,7 +7551,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>236</v>
       </c>
@@ -7394,7 +7565,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>238</v>
       </c>
@@ -7408,7 +7579,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>195</v>
       </c>
@@ -7422,7 +7593,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>59</v>
       </c>
@@ -7436,7 +7607,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>242</v>
       </c>
@@ -7450,7 +7621,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>62</v>
       </c>
@@ -7464,7 +7635,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>245</v>
       </c>
@@ -7478,7 +7649,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>247</v>
       </c>
@@ -7492,7 +7663,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>57</v>
       </c>
@@ -7506,7 +7677,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>60</v>
       </c>
@@ -7520,7 +7691,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>236</v>
       </c>
@@ -7534,7 +7705,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>18</v>
       </c>
@@ -7548,7 +7719,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>121</v>
       </c>
@@ -7562,7 +7733,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>253</v>
       </c>
@@ -7576,7 +7747,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>255</v>
       </c>
@@ -7590,7 +7761,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>204</v>
       </c>
@@ -7604,7 +7775,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>62</v>
       </c>
@@ -7618,7 +7789,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>60</v>
       </c>
@@ -7632,7 +7803,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>260</v>
       </c>
@@ -7646,7 +7817,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>262</v>
       </c>
@@ -7660,7 +7831,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>264</v>
       </c>
@@ -7674,7 +7845,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>220</v>
       </c>
@@ -7688,7 +7859,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>266</v>
       </c>
@@ -7702,7 +7873,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>268</v>
       </c>
@@ -7716,7 +7887,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>107</v>
       </c>
@@ -7730,7 +7901,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>270</v>
       </c>
@@ -7744,7 +7915,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>202</v>
       </c>
@@ -7758,7 +7929,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>272</v>
       </c>
@@ -7772,7 +7943,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>274</v>
       </c>
@@ -7786,7 +7957,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>276</v>
       </c>
@@ -7800,7 +7971,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>242</v>
       </c>
@@ -7814,7 +7985,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>278</v>
       </c>
@@ -7828,7 +7999,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>23</v>
       </c>
@@ -7842,7 +8013,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>62</v>
       </c>
@@ -7856,7 +8027,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>60</v>
       </c>
@@ -7870,7 +8041,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>245</v>
       </c>
@@ -7884,7 +8055,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>281</v>
       </c>
@@ -7898,7 +8069,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>282</v>
       </c>
@@ -7912,7 +8083,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>283</v>
       </c>
@@ -7926,7 +8097,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>284</v>
       </c>
@@ -7940,7 +8111,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>207</v>
       </c>
@@ -7954,7 +8125,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>76</v>
       </c>
@@ -7968,7 +8139,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>285</v>
       </c>
@@ -7982,7 +8153,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>262</v>
       </c>
@@ -7996,7 +8167,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>286</v>
       </c>
@@ -8010,7 +8181,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>287</v>
       </c>
@@ -8024,7 +8195,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>135</v>
       </c>
@@ -8038,7 +8209,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>57</v>
       </c>
@@ -8052,7 +8223,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>289</v>
       </c>
@@ -8066,7 +8237,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>268</v>
       </c>
@@ -8080,7 +8251,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>290</v>
       </c>
@@ -8094,7 +8265,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>107</v>
       </c>
@@ -8108,7 +8279,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>255</v>
       </c>
@@ -8122,7 +8293,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>202</v>
       </c>
@@ -8136,7 +8307,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>291</v>
       </c>
@@ -8150,7 +8321,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>228</v>
       </c>
@@ -8164,7 +8335,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>292</v>
       </c>
@@ -8178,7 +8349,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>293</v>
       </c>
@@ -8192,7 +8363,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>274</v>
       </c>
@@ -8206,7 +8377,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>294</v>
       </c>
@@ -8220,7 +8391,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>276</v>
       </c>
@@ -8234,7 +8405,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>296</v>
       </c>
@@ -8248,7 +8419,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>297</v>
       </c>
@@ -8262,7 +8433,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>23</v>
       </c>
@@ -8276,7 +8447,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>281</v>
       </c>
@@ -8290,7 +8461,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>298</v>
       </c>
@@ -8304,7 +8475,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>236</v>
       </c>
@@ -8318,7 +8489,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>300</v>
       </c>
@@ -8332,7 +8503,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>286</v>
       </c>
@@ -8346,7 +8517,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>303</v>
       </c>
@@ -8360,7 +8531,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>289</v>
       </c>
@@ -8374,7 +8545,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>304</v>
       </c>
@@ -8388,7 +8559,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>305</v>
       </c>
@@ -8402,7 +8573,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>196</v>
       </c>
@@ -8416,7 +8587,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>107</v>
       </c>
@@ -8430,7 +8601,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>255</v>
       </c>
@@ -8444,7 +8615,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>228</v>
       </c>
@@ -8458,7 +8629,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>307</v>
       </c>
@@ -8472,7 +8643,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>293</v>
       </c>
@@ -8486,7 +8657,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>296</v>
       </c>
@@ -8500,7 +8671,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>309</v>
       </c>
@@ -8514,7 +8685,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>242</v>
       </c>
@@ -8528,7 +8699,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>205</v>
       </c>
@@ -8542,7 +8713,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>62</v>
       </c>
@@ -8556,7 +8727,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>245</v>
       </c>
@@ -8570,7 +8741,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>311</v>
       </c>
@@ -8584,7 +8755,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>283</v>
       </c>
@@ -8598,7 +8769,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>236</v>
       </c>
@@ -8612,7 +8783,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>262</v>
       </c>
@@ -8626,7 +8797,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>208</v>
       </c>
@@ -8640,7 +8811,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>286</v>
       </c>
@@ -8654,7 +8825,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>253</v>
       </c>
@@ -8668,7 +8839,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>304</v>
       </c>
@@ -8682,7 +8853,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>38</v>
       </c>
@@ -8696,7 +8867,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>126</v>
       </c>
@@ -8710,7 +8881,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>316</v>
       </c>
@@ -8724,7 +8895,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>196</v>
       </c>
@@ -8738,7 +8909,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>107</v>
       </c>
@@ -8752,7 +8923,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>318</v>
       </c>
@@ -8766,7 +8937,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>159</v>
       </c>
@@ -8780,7 +8951,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>228</v>
       </c>
@@ -8794,7 +8965,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>293</v>
       </c>
@@ -8808,7 +8979,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>296</v>
       </c>
@@ -8822,7 +8993,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>309</v>
       </c>
@@ -8836,7 +9007,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>242</v>
       </c>
@@ -8850,7 +9021,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>12</v>
       </c>
@@ -8864,7 +9035,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>62</v>
       </c>
@@ -8878,7 +9049,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>245</v>
       </c>
@@ -8892,7 +9063,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>283</v>
       </c>
@@ -8906,7 +9077,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>121</v>
       </c>
@@ -8920,7 +9091,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>286</v>
       </c>
@@ -8934,7 +9105,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>324</v>
       </c>
@@ -8948,7 +9119,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>38</v>
       </c>
@@ -8962,7 +9133,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>196</v>
       </c>
@@ -8976,7 +9147,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>327</v>
       </c>
@@ -8990,7 +9161,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>293</v>
       </c>
@@ -9004,7 +9175,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>296</v>
       </c>
@@ -9018,7 +9189,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>309</v>
       </c>
@@ -9032,7 +9203,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>62</v>
       </c>
@@ -9046,7 +9217,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>245</v>
       </c>
@@ -9060,7 +9231,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>330</v>
       </c>
@@ -9074,7 +9245,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>42</v>
       </c>
@@ -9088,7 +9259,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>286</v>
       </c>
@@ -9102,7 +9273,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>196</v>
       </c>
@@ -9116,7 +9287,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>333</v>
       </c>
@@ -9130,7 +9301,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>296</v>
       </c>
@@ -9144,7 +9315,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>309</v>
       </c>
@@ -9158,7 +9329,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>62</v>
       </c>
@@ -9172,7 +9343,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>152</v>
       </c>
@@ -9186,7 +9357,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>196</v>
       </c>
@@ -9200,7 +9371,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>242</v>
       </c>
@@ -9214,7 +9385,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>62</v>
       </c>
@@ -9228,7 +9399,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>152</v>
       </c>
@@ -9242,7 +9413,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>76</v>
       </c>
@@ -9256,7 +9427,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>126</v>
       </c>
@@ -9270,7 +9441,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>196</v>
       </c>
@@ -9284,7 +9455,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>107</v>
       </c>
@@ -9298,7 +9469,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>339</v>
       </c>
@@ -9312,7 +9483,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>341</v>
       </c>
@@ -9326,7 +9497,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>341</v>
       </c>
@@ -9340,7 +9511,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>341</v>
       </c>
@@ -9354,7 +9525,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>196</v>
       </c>
@@ -9368,7 +9539,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>343</v>
       </c>
@@ -9382,7 +9553,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>345</v>
       </c>
@@ -9396,7 +9567,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>345</v>
       </c>
@@ -9410,7 +9581,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>62</v>
       </c>
@@ -9424,7 +9595,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>260</v>
       </c>
@@ -9438,7 +9609,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>236</v>
       </c>
@@ -9452,7 +9623,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>348</v>
       </c>
@@ -9466,7 +9637,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>350</v>
       </c>
@@ -9480,7 +9651,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>72</v>
       </c>
@@ -9494,7 +9665,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>247</v>
       </c>
@@ -9508,7 +9679,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>354</v>
       </c>
@@ -9522,7 +9693,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>356</v>
       </c>
@@ -9536,7 +9707,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>358</v>
       </c>
@@ -9550,7 +9721,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>359</v>
       </c>
@@ -9564,7 +9735,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>361</v>
       </c>
@@ -9578,7 +9749,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>177</v>
       </c>
@@ -9592,7 +9763,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>361</v>
       </c>
@@ -9606,7 +9777,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>363</v>
       </c>
@@ -9620,7 +9791,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>190</v>
       </c>
@@ -9634,7 +9805,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>365</v>
       </c>
@@ -9648,7 +9819,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>366</v>
       </c>
@@ -9662,7 +9833,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>79</v>
       </c>
@@ -9676,7 +9847,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>361</v>
       </c>
@@ -9690,7 +9861,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>324</v>
       </c>
@@ -9704,7 +9875,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>367</v>
       </c>
@@ -9718,7 +9889,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>36</v>
       </c>
@@ -9732,7 +9903,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>36</v>
       </c>
@@ -9746,7 +9917,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>369</v>
       </c>
@@ -9760,7 +9931,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>196</v>
       </c>
@@ -9774,7 +9945,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>370</v>
       </c>
@@ -9788,7 +9959,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>290</v>
       </c>
@@ -9802,7 +9973,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>107</v>
       </c>
@@ -9816,7 +9987,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>371</v>
       </c>
@@ -9830,7 +10001,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>291</v>
       </c>
@@ -9844,7 +10015,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>228</v>
       </c>
@@ -9858,7 +10029,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>272</v>
       </c>
@@ -9872,7 +10043,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>296</v>
       </c>
@@ -9886,7 +10057,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>242</v>
       </c>
@@ -9900,7 +10071,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>62</v>
       </c>
@@ -9914,7 +10085,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>372</v>
       </c>
@@ -9928,7 +10099,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>282</v>
       </c>
@@ -9942,7 +10113,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>373</v>
       </c>
@@ -9956,7 +10127,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>236</v>
       </c>
@@ -9970,7 +10141,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>217</v>
       </c>
@@ -9984,7 +10155,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>374</v>
       </c>
@@ -9998,7 +10169,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>375</v>
       </c>
@@ -10012,7 +10183,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>376</v>
       </c>
@@ -10026,7 +10197,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>377</v>
       </c>
@@ -10040,7 +10211,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>379</v>
       </c>
@@ -10054,7 +10225,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>272</v>
       </c>
@@ -10068,7 +10239,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>296</v>
       </c>
@@ -10082,7 +10253,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>242</v>
       </c>
@@ -10096,7 +10267,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>373</v>
       </c>
@@ -10110,7 +10281,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>236</v>
       </c>
@@ -10124,7 +10295,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>380</v>
       </c>
@@ -10138,7 +10309,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>361</v>
       </c>
@@ -10152,7 +10323,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>381</v>
       </c>
@@ -10166,7 +10337,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>382</v>
       </c>
@@ -10180,7 +10351,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>126</v>
       </c>
@@ -10194,7 +10365,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>348</v>
       </c>
@@ -10208,7 +10379,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>132</v>
       </c>
@@ -10222,7 +10393,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>383</v>
       </c>
@@ -10236,7 +10407,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>384</v>
       </c>
@@ -10250,7 +10421,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>12</v>
       </c>
@@ -10264,7 +10435,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>385</v>
       </c>
@@ -10278,7 +10449,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>115</v>
       </c>
@@ -10292,7 +10463,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>115</v>
       </c>
@@ -10306,7 +10477,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>72</v>
       </c>
@@ -10320,7 +10491,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>72</v>
       </c>
@@ -10334,7 +10505,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>121</v>
       </c>
@@ -10348,7 +10519,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>121</v>
       </c>
@@ -10362,7 +10533,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>389</v>
       </c>
@@ -10376,7 +10547,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>86</v>
       </c>
@@ -10390,7 +10561,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>118</v>
       </c>
@@ -10410,7 +10581,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>393</v>
       </c>
@@ -10430,7 +10601,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>393</v>
       </c>
@@ -10450,7 +10621,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>393</v>
       </c>
@@ -10470,7 +10641,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>393</v>
       </c>
@@ -10490,7 +10661,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>214</v>
       </c>
@@ -10510,7 +10681,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>398</v>
       </c>
@@ -10530,7 +10701,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>401</v>
       </c>
@@ -10550,7 +10721,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>404</v>
       </c>
@@ -10570,7 +10741,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>10</v>
       </c>
@@ -10590,7 +10761,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>111</v>
       </c>
@@ -10610,7 +10781,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>221</v>
       </c>
@@ -10630,7 +10801,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>98</v>
       </c>
@@ -10650,7 +10821,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>415</v>
       </c>
@@ -10670,7 +10841,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>343</v>
       </c>
@@ -10690,7 +10861,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>307</v>
       </c>
@@ -10710,7 +10881,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>186</v>
       </c>
@@ -10730,7 +10901,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>71</v>
       </c>
@@ -10750,7 +10921,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>427</v>
       </c>
@@ -10770,7 +10941,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>430</v>
       </c>
@@ -10790,7 +10961,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>430</v>
       </c>
@@ -10810,7 +10981,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>433</v>
       </c>
@@ -10830,7 +11001,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>118</v>
       </c>
@@ -10850,7 +11021,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>65</v>
       </c>
@@ -10870,7 +11041,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>440</v>
       </c>
@@ -10890,7 +11061,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>443</v>
       </c>
@@ -10910,7 +11081,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>446</v>
       </c>
@@ -10930,7 +11101,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>307</v>
       </c>
@@ -10950,7 +11121,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>415</v>
       </c>
@@ -10970,7 +11141,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>453</v>
       </c>
@@ -10990,7 +11161,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>453</v>
       </c>
@@ -11010,7 +11181,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>456</v>
       </c>
@@ -11030,7 +11201,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>459</v>
       </c>
@@ -11050,7 +11221,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>462</v>
       </c>
@@ -11070,7 +11241,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>221</v>
       </c>
@@ -11090,7 +11261,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>467</v>
       </c>
@@ -11110,7 +11281,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>470</v>
       </c>
@@ -11130,7 +11301,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>135</v>
       </c>
@@ -11150,7 +11321,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>475</v>
       </c>
@@ -11170,7 +11341,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>478</v>
       </c>
@@ -11190,7 +11361,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>480</v>
       </c>
@@ -11210,7 +11381,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>483</v>
       </c>
@@ -11230,7 +11401,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>389</v>
       </c>
@@ -11250,7 +11421,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>488</v>
       </c>
@@ -11270,7 +11441,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>343</v>
       </c>
@@ -11290,7 +11461,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>493</v>
       </c>
@@ -11310,7 +11481,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>496</v>
       </c>
@@ -11330,7 +11501,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>307</v>
       </c>
@@ -11350,7 +11521,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>501</v>
       </c>
@@ -11370,7 +11541,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>504</v>
       </c>
@@ -11390,7 +11561,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>63</v>
       </c>
@@ -11410,7 +11581,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>83</v>
       </c>
@@ -11430,7 +11601,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>26</v>
       </c>
@@ -11450,7 +11621,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>511</v>
       </c>
@@ -11470,7 +11641,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>514</v>
       </c>
@@ -11490,7 +11661,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>186</v>
       </c>
@@ -11510,7 +11681,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>519</v>
       </c>
@@ -11530,7 +11701,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>522</v>
       </c>
@@ -11550,7 +11721,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>119</v>
       </c>
@@ -11570,7 +11741,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>470</v>
       </c>
@@ -11590,7 +11761,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>30</v>
       </c>
@@ -11610,7 +11781,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>33</v>
       </c>
@@ -11630,7 +11801,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>531</v>
       </c>
@@ -11650,7 +11821,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>534</v>
       </c>
@@ -11670,7 +11841,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>535</v>
       </c>
@@ -11690,7 +11861,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>538</v>
       </c>
@@ -11710,7 +11881,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>541</v>
       </c>
@@ -11730,7 +11901,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -11750,7 +11921,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>546</v>
       </c>
@@ -11770,7 +11941,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>186</v>
       </c>
@@ -11790,7 +11961,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>443</v>
       </c>
@@ -11810,7 +11981,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>551</v>
       </c>
@@ -11830,7 +12001,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>552</v>
       </c>
@@ -11850,7 +12021,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>111</v>
       </c>
@@ -11870,7 +12041,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>427</v>
       </c>
@@ -11890,7 +12061,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>120</v>
       </c>
@@ -11910,7 +12081,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>553</v>
       </c>
@@ -11930,7 +12101,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>496</v>
       </c>
@@ -11950,7 +12121,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>66</v>
       </c>
@@ -11970,7 +12141,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>98</v>
       </c>
@@ -11990,7 +12161,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>453</v>
       </c>
@@ -12010,7 +12181,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>453</v>
       </c>
@@ -12030,7 +12201,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>415</v>
       </c>
@@ -12050,7 +12221,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>554</v>
       </c>
@@ -12070,7 +12241,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>554</v>
       </c>
@@ -12090,7 +12261,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>103</v>
       </c>
@@ -12110,7 +12281,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>555</v>
       </c>
@@ -12130,7 +12301,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>555</v>
       </c>
@@ -12150,7 +12321,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>556</v>
       </c>
@@ -12170,7 +12341,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>557</v>
       </c>
@@ -12190,7 +12361,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>558</v>
       </c>
@@ -12210,7 +12381,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>559</v>
       </c>
@@ -12230,7 +12401,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>560</v>
       </c>
@@ -12250,7 +12421,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>82</v>
       </c>
@@ -12270,7 +12441,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>343</v>
       </c>
@@ -12290,7 +12461,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>221</v>
       </c>
@@ -12310,7 +12481,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>612</v>
       </c>
@@ -12330,7 +12501,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>307</v>
       </c>
@@ -12350,7 +12521,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>615</v>
       </c>
@@ -12370,7 +12541,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>615</v>
       </c>
@@ -12390,7 +12561,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>339</v>
       </c>
@@ -12410,7 +12581,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>52</v>
       </c>
@@ -12430,7 +12601,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>158</v>
       </c>
@@ -12450,7 +12621,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>158</v>
       </c>
@@ -12470,7 +12641,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>559</v>
       </c>
@@ -12490,7 +12661,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>629</v>
       </c>
@@ -12510,7 +12681,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>632</v>
       </c>
@@ -12530,7 +12701,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>632</v>
       </c>
@@ -12550,7 +12721,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>637</v>
       </c>
@@ -12570,7 +12741,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>305</v>
       </c>
@@ -12588,6 +12759,446 @@
       </c>
       <c r="F686" t="s">
         <v>641</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>70</v>
+      </c>
+      <c r="B687" t="s">
+        <v>54</v>
+      </c>
+      <c r="C687" s="1">
+        <v>46151</v>
+      </c>
+      <c r="D687" t="s">
+        <v>353</v>
+      </c>
+      <c r="E687" t="s">
+        <v>642</v>
+      </c>
+      <c r="F687" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>644</v>
+      </c>
+      <c r="B688" t="s">
+        <v>645</v>
+      </c>
+      <c r="C688" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D688" t="s">
+        <v>362</v>
+      </c>
+      <c r="E688" t="s">
+        <v>646</v>
+      </c>
+      <c r="F688" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>63</v>
+      </c>
+      <c r="B689" t="s">
+        <v>11</v>
+      </c>
+      <c r="C689" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D689" t="s">
+        <v>362</v>
+      </c>
+      <c r="E689" t="s">
+        <v>648</v>
+      </c>
+      <c r="F689" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>221</v>
+      </c>
+      <c r="B690" t="s">
+        <v>192</v>
+      </c>
+      <c r="C690" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D690" t="s">
+        <v>368</v>
+      </c>
+      <c r="E690" t="s">
+        <v>650</v>
+      </c>
+      <c r="F690" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>652</v>
+      </c>
+      <c r="B691" t="s">
+        <v>11</v>
+      </c>
+      <c r="C691" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D691" t="s">
+        <v>362</v>
+      </c>
+      <c r="E691" t="s">
+        <v>653</v>
+      </c>
+      <c r="F691" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>427</v>
+      </c>
+      <c r="B692" t="s">
+        <v>19</v>
+      </c>
+      <c r="C692" s="1">
+        <v>46153</v>
+      </c>
+      <c r="D692" t="s">
+        <v>357</v>
+      </c>
+      <c r="E692" t="s">
+        <v>655</v>
+      </c>
+      <c r="F692" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>98</v>
+      </c>
+      <c r="B693" t="s">
+        <v>19</v>
+      </c>
+      <c r="C693" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D693" t="s">
+        <v>357</v>
+      </c>
+      <c r="E693" t="s">
+        <v>657</v>
+      </c>
+      <c r="F693" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>16</v>
+      </c>
+      <c r="B694" t="s">
+        <v>8</v>
+      </c>
+      <c r="C694" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D694" t="s">
+        <v>659</v>
+      </c>
+      <c r="E694" t="s">
+        <v>660</v>
+      </c>
+      <c r="F694" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>103</v>
+      </c>
+      <c r="B695" t="s">
+        <v>19</v>
+      </c>
+      <c r="C695" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D695" t="s">
+        <v>355</v>
+      </c>
+      <c r="E695" t="s">
+        <v>662</v>
+      </c>
+      <c r="F695" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>664</v>
+      </c>
+      <c r="B696" t="s">
+        <v>192</v>
+      </c>
+      <c r="C696" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D696" t="s">
+        <v>362</v>
+      </c>
+      <c r="E696" t="s">
+        <v>665</v>
+      </c>
+      <c r="F696" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>667</v>
+      </c>
+      <c r="B697" t="s">
+        <v>5</v>
+      </c>
+      <c r="C697" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D697" t="s">
+        <v>390</v>
+      </c>
+      <c r="E697" t="s">
+        <v>668</v>
+      </c>
+      <c r="F697" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>144</v>
+      </c>
+      <c r="B698" t="s">
+        <v>15</v>
+      </c>
+      <c r="C698" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D698" t="s">
+        <v>670</v>
+      </c>
+      <c r="E698" t="s">
+        <v>671</v>
+      </c>
+      <c r="F698" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>673</v>
+      </c>
+      <c r="B699" t="s">
+        <v>19</v>
+      </c>
+      <c r="C699" s="1">
+        <v>46153</v>
+      </c>
+      <c r="D699" t="s">
+        <v>357</v>
+      </c>
+      <c r="E699" t="s">
+        <v>674</v>
+      </c>
+      <c r="F699" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>676</v>
+      </c>
+      <c r="B700" t="s">
+        <v>13</v>
+      </c>
+      <c r="C700" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D700" t="s">
+        <v>353</v>
+      </c>
+      <c r="E700" t="s">
+        <v>677</v>
+      </c>
+      <c r="F700" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>679</v>
+      </c>
+      <c r="B701" t="s">
+        <v>645</v>
+      </c>
+      <c r="C701" s="1">
+        <v>46156</v>
+      </c>
+      <c r="D701" t="s">
+        <v>387</v>
+      </c>
+      <c r="E701" t="s">
+        <v>680</v>
+      </c>
+      <c r="F701" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>118</v>
+      </c>
+      <c r="B702" t="s">
+        <v>11</v>
+      </c>
+      <c r="C702" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D702" t="s">
+        <v>353</v>
+      </c>
+      <c r="E702" t="s">
+        <v>682</v>
+      </c>
+      <c r="F702" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>684</v>
+      </c>
+      <c r="B703" t="s">
+        <v>54</v>
+      </c>
+      <c r="C703" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D703" t="s">
+        <v>685</v>
+      </c>
+      <c r="E703" t="s">
+        <v>686</v>
+      </c>
+      <c r="F703" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>684</v>
+      </c>
+      <c r="B704" t="s">
+        <v>54</v>
+      </c>
+      <c r="C704" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D704" t="s">
+        <v>388</v>
+      </c>
+      <c r="E704" t="s">
+        <v>686</v>
+      </c>
+      <c r="F704" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>688</v>
+      </c>
+      <c r="B705" t="s">
+        <v>192</v>
+      </c>
+      <c r="C705" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D705" t="s">
+        <v>362</v>
+      </c>
+      <c r="E705" t="s">
+        <v>689</v>
+      </c>
+      <c r="F705" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>691</v>
+      </c>
+      <c r="B706" t="s">
+        <v>192</v>
+      </c>
+      <c r="C706" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D706" t="s">
+        <v>378</v>
+      </c>
+      <c r="E706" t="s">
+        <v>692</v>
+      </c>
+      <c r="F706" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>82</v>
+      </c>
+      <c r="B707" t="s">
+        <v>13</v>
+      </c>
+      <c r="C707" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D707" t="s">
+        <v>360</v>
+      </c>
+      <c r="E707" t="s">
+        <v>694</v>
+      </c>
+      <c r="F707" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>696</v>
+      </c>
+      <c r="B708" t="s">
+        <v>13</v>
+      </c>
+      <c r="C708" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D708" t="s">
+        <v>355</v>
+      </c>
+      <c r="E708" t="s">
+        <v>697</v>
+      </c>
+      <c r="F708" t="s">
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/data/Desvios de DTOs.xlsx
+++ b/data/Desvios de DTOs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C4AB6D-013A-4ED7-AE33-484D7448B886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8918ED41-23C3-49B9-AB5D-B0534A130D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2389" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="776">
   <si>
     <t>Colaborador</t>
   </si>
@@ -2136,6 +2136,237 @@
   </si>
   <si>
     <t>Reorientação. Ao términar o serviço a chave precisa ser guardada na caixinha e a caixinha fechada.</t>
+  </si>
+  <si>
+    <t>não uso de EPI cinto lombar e luvas inadequadas além de uso proibido de correntes</t>
+  </si>
+  <si>
+    <t>Tratativa do desvio e pontuação no prontuário.</t>
+  </si>
+  <si>
+    <t>ALISON ROGER CRUZ</t>
+  </si>
+  <si>
+    <t>Feito ver e agir.</t>
+  </si>
+  <si>
+    <t>Nao utilizounplano de trafego corretamente</t>
+  </si>
+  <si>
+    <t>foi feito feedback com colaborador para que utilize as faixas do plano de tráfego corretamente.</t>
+  </si>
+  <si>
+    <t>falta de correntes nos P20</t>
+  </si>
+  <si>
+    <t>ver e agir com passagem de corrente nos P20</t>
+  </si>
+  <si>
+    <t>Execução Segura de Armazenamento e Transporte de Cilindro de Gás Comprimido</t>
+  </si>
+  <si>
+    <t>p20 nao estava com corrente em todas as botijas</t>
+  </si>
+  <si>
+    <t>colocação imadiata da corrente nas botijas vazias e retreino do operador</t>
+  </si>
+  <si>
+    <t>DANIEL MARQUES DA CUNHA</t>
+  </si>
+  <si>
+    <t>motorista acessou o armazém fora do local correto</t>
+  </si>
+  <si>
+    <t>fazer treinamento sobre o plano de tráfego no dia 12/06</t>
+  </si>
+  <si>
+    <t>EDMIR NASCIMENTO DA SILVA</t>
+  </si>
+  <si>
+    <t>Não uso de trata roda, mas já fiz abordagem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedi para usar o trava roda, e observei de perto. Outras atividades está indo muito bem </t>
+  </si>
+  <si>
+    <t>EVANDRO FELIPE DE ARAUJO DA SILVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execução segura de uso de segregação</t>
+  </si>
+  <si>
+    <t>Não utilizava o trava roda, é entrando na segregação.</t>
+  </si>
+  <si>
+    <t>Não utilizava trava roda, fiz uma abordagem é ensinei o processo correto é respeita segregação.</t>
+  </si>
+  <si>
+    <t>Segregação: Não foi utilizado cones de sinalização ao executar a tarefa. No momento em que o operador estava realizando a tarefa o manobra passou próximo a empilhadeira com risco de acidente. Trava-Rodas: O operador não utilizou o trava-rodas ao executar a tarefa. Controle Chaces: Não validou de a chave estava bloqueada na caixinha.</t>
+  </si>
+  <si>
+    <t>O mesmo foi orientado no início da tarefa sobre o uso de trava-rodas e logo após a finalização da tarefa foi repassado todos os desvios de segurança encontrados. Solicitado pro supervisor Bruno revisar o padrão e reforçar em geral sobre segurança.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execução Segura de Trava rodas (Ideal Empilhadeiras)</t>
+  </si>
+  <si>
+    <t>caminhão se. trava rodas no ato da troca de pneus</t>
+  </si>
+  <si>
+    <t>treinar mecânico no passo a passo da atividade. possui duvidas</t>
+  </si>
+  <si>
+    <t>JOSE DE ARIMAR TOUTA</t>
+  </si>
+  <si>
+    <t>descarregou AG com a pilha acima de 5 cxs desamarrado</t>
+  </si>
+  <si>
+    <t>Operador orientado a pedir ao ajudante para amarrar quando AG estiver desamarrado.</t>
+  </si>
+  <si>
+    <t>Colaborador não colocou as correntes de segregação. Feito ver e agir.</t>
+  </si>
+  <si>
+    <t>feito DTO de retrabalho. Precisa colocar o padrão fixado e disponível na área de retrabalho, não tem.</t>
+  </si>
+  <si>
+    <t>realizando atividade fora da área segregada</t>
+  </si>
+  <si>
+    <t>realizar treinamento de areas segregadas ao colaborador</t>
+  </si>
+  <si>
+    <t>LUCIANO CRUZ DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> caminhão e van).</t>
+  </si>
+  <si>
+    <t>Foi encontrada a deficiência de realizações do check pré uso.</t>
+  </si>
+  <si>
+    <t>Retreinar à equipe de frota com foco nos processos e sops.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> maquina de limpeza</t>
+  </si>
+  <si>
+    <t>Não realizao da inspeção de pré  uso.</t>
+  </si>
+  <si>
+    <t>Realizar treinamento com todo time.</t>
+  </si>
+  <si>
+    <t>Execução segura de Inspeção Pré-Uso de Equipamentos Motorizados (empilhadeira, maquina de limpeza...)</t>
+  </si>
+  <si>
+    <t>não identificação das anomalias no check list e problemas de PTL</t>
+  </si>
+  <si>
+    <t>reciclagem em todos os pontos de checklist e identificação de problemas no PTL</t>
+  </si>
+  <si>
+    <t>MARCELO NUNES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Nao realizou inspeção</t>
+  </si>
+  <si>
+    <t>Reforçar treinamento com todo time com foco na inspeção equipamentos</t>
+  </si>
+  <si>
+    <t>Ao pegar as quantidades solicitadas de 600 do palate, deixou em coluna. Não retirando 100% em lastro.</t>
+  </si>
+  <si>
+    <t>Colaborador foi orientado ao final do DTO sobre a percepção de risco e realização do manuseio conforme padrão.</t>
+  </si>
+  <si>
+    <t>RAFAEL COSMANN PEREIRA</t>
+  </si>
+  <si>
+    <t>Sem desvio</t>
+  </si>
+  <si>
+    <t>Sem ação</t>
+  </si>
+  <si>
+    <t>Chave na ignição</t>
+  </si>
+  <si>
+    <t>RENAN DE OLIVEIRA DE SOUZA FERREIRA DIAS</t>
+  </si>
+  <si>
+    <t>ajudante utilizou a paleteira de forma incorreta, puxando ao invés de empurrar</t>
+  </si>
+  <si>
+    <t>treinamento sobre a utilização de equipamentos não motorizados em 30/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execução Segura de Prevenção da Violência</t>
+  </si>
+  <si>
+    <t>trava rodas damiani não colocada</t>
+  </si>
+  <si>
+    <t>ver e agir, orientação quanto ao uso e a importância de utilizar o trava rodas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execução Segura na direção (caminhões e Vans)</t>
+  </si>
+  <si>
+    <t>SANDOVAL GALIZA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>CDL CAMAÇARI</t>
+  </si>
+  <si>
+    <t>Não uso do trava rodas</t>
+  </si>
+  <si>
+    <t>Solicitar compra do trava rodas para área de manutenção.</t>
+  </si>
+  <si>
+    <t>TAYNARA DA SILVA LACERDA</t>
+  </si>
+  <si>
+    <t>CD SALVADOR</t>
+  </si>
+  <si>
+    <t>Colaborador utilizando luva, porém não é a fornecida pela empresa.</t>
+  </si>
+  <si>
+    <t>Colaboradora foi instruida no ato sobre a utilização do EPI correto e foi levantado o ponto de adequação de luva para operadores de empilhadeira.</t>
+  </si>
+  <si>
+    <t>colaborador realizando movimentação de produtos utilizando Adorno ( Corrente )</t>
+  </si>
+  <si>
+    <t>seguir com Fluxo e Pontuação em seu prontuário por desvio de segurança.</t>
+  </si>
+  <si>
+    <t>Ergonomia</t>
+  </si>
+  <si>
+    <t>Orientação verbal sobre ergonomia.</t>
+  </si>
+  <si>
+    <t>WILSON DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execução segura de manuseio de paleteiras</t>
+  </si>
+  <si>
+    <t>Colaborador não executou o checklist da paleteira de forma adequada. O mesmo ao ser abordado relatou que acreditava que o checklist só poderia ser feito no início do turno e quando lembrou não viu a necessidade de realizar posteriormente.</t>
+  </si>
+  <si>
+    <t>Reciclagem sobre o checklist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execução segura de manuseio manual</t>
+  </si>
+  <si>
+    <t>Execução Segura de Equipamento de Elevação</t>
   </si>
 </sst>
 </file>
@@ -2488,16 +2719,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}">
-  <dimension ref="A1:F708"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F766"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="139.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="139.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2511,7 +2742,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2525,7 +2756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2539,7 +2770,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2553,7 +2784,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2567,7 +2798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2581,7 +2812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2595,7 +2826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2609,7 +2840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -2623,7 +2854,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2637,7 +2868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2651,7 +2882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2665,7 +2896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2679,7 +2910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2693,7 +2924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2707,7 +2938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -2721,7 +2952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2735,7 +2966,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -2749,7 +2980,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -2763,7 +2994,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2777,7 +3008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2791,7 +3022,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -2805,7 +3036,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2819,7 +3050,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -2833,7 +3064,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2847,7 +3078,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -2861,7 +3092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -2875,7 +3106,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -2889,7 +3120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -2903,7 +3134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -2917,7 +3148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -2931,7 +3162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -2945,7 +3176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -2959,7 +3190,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2973,7 +3204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2987,7 +3218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -3001,7 +3232,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -3015,7 +3246,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -3029,7 +3260,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -3043,7 +3274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -3057,7 +3288,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -3071,7 +3302,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -3085,7 +3316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -3099,7 +3330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -3113,7 +3344,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3127,7 +3358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -3141,7 +3372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -3155,7 +3386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3169,7 +3400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -3183,7 +3414,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -3197,7 +3428,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -3211,7 +3442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -3225,7 +3456,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -3239,7 +3470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -3253,7 +3484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -3267,7 +3498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -3281,7 +3512,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -3295,7 +3526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -3309,7 +3540,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -3323,7 +3554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>32</v>
       </c>
@@ -3337,7 +3568,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -3351,7 +3582,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -3365,7 +3596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -3379,7 +3610,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -3393,7 +3624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -3407,7 +3638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -3421,7 +3652,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -3435,7 +3666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -3449,7 +3680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -3463,7 +3694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -3477,7 +3708,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -3491,7 +3722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -3505,7 +3736,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -3519,7 +3750,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>45</v>
       </c>
@@ -3533,7 +3764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -3547,7 +3778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -3561,7 +3792,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -3575,7 +3806,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -3589,7 +3820,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -3603,7 +3834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -3617,7 +3848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>78</v>
       </c>
@@ -3631,7 +3862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>79</v>
       </c>
@@ -3645,7 +3876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>80</v>
       </c>
@@ -3659,7 +3890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>81</v>
       </c>
@@ -3673,7 +3904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -3687,7 +3918,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>82</v>
       </c>
@@ -3701,7 +3932,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3715,7 +3946,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>84</v>
       </c>
@@ -3729,7 +3960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>85</v>
       </c>
@@ -3743,7 +3974,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>86</v>
       </c>
@@ -3757,7 +3988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -3771,7 +4002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>87</v>
       </c>
@@ -3785,7 +4016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>55</v>
       </c>
@@ -3799,7 +4030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>63</v>
       </c>
@@ -3813,7 +4044,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>63</v>
       </c>
@@ -3827,7 +4058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>63</v>
       </c>
@@ -3841,7 +4072,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>63</v>
       </c>
@@ -3855,7 +4086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>63</v>
       </c>
@@ -3869,7 +4100,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>89</v>
       </c>
@@ -3883,7 +4114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>89</v>
       </c>
@@ -3897,7 +4128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>90</v>
       </c>
@@ -3911,7 +4142,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>90</v>
       </c>
@@ -3925,7 +4156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -3939,7 +4170,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>91</v>
       </c>
@@ -3953,7 +4184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>92</v>
       </c>
@@ -3967,7 +4198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>64</v>
       </c>
@@ -3981,7 +4212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>37</v>
       </c>
@@ -3995,7 +4226,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>93</v>
       </c>
@@ -4009,7 +4240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>31</v>
       </c>
@@ -4023,7 +4254,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>94</v>
       </c>
@@ -4037,7 +4268,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>95</v>
       </c>
@@ -4051,7 +4282,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>96</v>
       </c>
@@ -4065,7 +4296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -4079,7 +4310,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>98</v>
       </c>
@@ -4093,7 +4324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -4107,7 +4338,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>52</v>
       </c>
@@ -4121,7 +4352,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>99</v>
       </c>
@@ -4135,7 +4366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>100</v>
       </c>
@@ -4149,7 +4380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>100</v>
       </c>
@@ -4163,7 +4394,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>101</v>
       </c>
@@ -4177,7 +4408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>101</v>
       </c>
@@ -4191,7 +4422,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>100</v>
       </c>
@@ -4205,7 +4436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>100</v>
       </c>
@@ -4219,7 +4450,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>100</v>
       </c>
@@ -4233,7 +4464,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>36</v>
       </c>
@@ -4247,7 +4478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>102</v>
       </c>
@@ -4261,7 +4492,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>103</v>
       </c>
@@ -4275,7 +4506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>104</v>
       </c>
@@ -4289,7 +4520,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>105</v>
       </c>
@@ -4303,7 +4534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>106</v>
       </c>
@@ -4317,7 +4548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>107</v>
       </c>
@@ -4331,7 +4562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>108</v>
       </c>
@@ -4345,7 +4576,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>109</v>
       </c>
@@ -4359,7 +4590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>110</v>
       </c>
@@ -4373,7 +4604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>36</v>
       </c>
@@ -4387,7 +4618,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>111</v>
       </c>
@@ -4401,7 +4632,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>112</v>
       </c>
@@ -4415,7 +4646,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>113</v>
       </c>
@@ -4429,7 +4660,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>12</v>
       </c>
@@ -4443,7 +4674,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>114</v>
       </c>
@@ -4457,7 +4688,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>115</v>
       </c>
@@ -4471,7 +4702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>116</v>
       </c>
@@ -4485,7 +4716,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>117</v>
       </c>
@@ -4499,7 +4730,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>118</v>
       </c>
@@ -4513,7 +4744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>118</v>
       </c>
@@ -4527,7 +4758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>118</v>
       </c>
@@ -4541,7 +4772,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>118</v>
       </c>
@@ -4555,7 +4786,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>115</v>
       </c>
@@ -4569,7 +4800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>119</v>
       </c>
@@ -4583,7 +4814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>120</v>
       </c>
@@ -4597,7 +4828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>121</v>
       </c>
@@ -4611,7 +4842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>121</v>
       </c>
@@ -4625,7 +4856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>121</v>
       </c>
@@ -4639,7 +4870,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>122</v>
       </c>
@@ -4653,7 +4884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>55</v>
       </c>
@@ -4667,7 +4898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>80</v>
       </c>
@@ -4681,7 +4912,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>80</v>
       </c>
@@ -4695,7 +4926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>80</v>
       </c>
@@ -4709,7 +4940,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>123</v>
       </c>
@@ -4723,7 +4954,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>123</v>
       </c>
@@ -4737,7 +4968,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -4751,7 +4982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -4765,7 +4996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>124</v>
       </c>
@@ -4779,7 +5010,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -4793,7 +5024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>125</v>
       </c>
@@ -4807,7 +5038,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>126</v>
       </c>
@@ -4821,7 +5052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>127</v>
       </c>
@@ -4835,7 +5066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>128</v>
       </c>
@@ -4849,7 +5080,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>129</v>
       </c>
@@ -4863,7 +5094,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>73</v>
       </c>
@@ -4877,7 +5108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>130</v>
       </c>
@@ -4891,7 +5122,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>131</v>
       </c>
@@ -4905,7 +5136,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>132</v>
       </c>
@@ -4919,7 +5150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>133</v>
       </c>
@@ -4933,7 +5164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>134</v>
       </c>
@@ -4947,7 +5178,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>134</v>
       </c>
@@ -4961,7 +5192,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>135</v>
       </c>
@@ -4975,7 +5206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>93</v>
       </c>
@@ -4989,7 +5220,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>93</v>
       </c>
@@ -5003,7 +5234,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>134</v>
       </c>
@@ -5017,7 +5248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>125</v>
       </c>
@@ -5031,7 +5262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>136</v>
       </c>
@@ -5045,7 +5276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>137</v>
       </c>
@@ -5059,7 +5290,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>138</v>
       </c>
@@ -5073,7 +5304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>139</v>
       </c>
@@ -5087,7 +5318,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>139</v>
       </c>
@@ -5101,7 +5332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>137</v>
       </c>
@@ -5115,7 +5346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>137</v>
       </c>
@@ -5129,7 +5360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>137</v>
       </c>
@@ -5143,7 +5374,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>137</v>
       </c>
@@ -5157,7 +5388,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>140</v>
       </c>
@@ -5171,7 +5402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>140</v>
       </c>
@@ -5185,7 +5416,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>141</v>
       </c>
@@ -5199,7 +5430,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>142</v>
       </c>
@@ -5213,7 +5444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>143</v>
       </c>
@@ -5227,7 +5458,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>143</v>
       </c>
@@ -5241,7 +5472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>144</v>
       </c>
@@ -5255,7 +5486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>145</v>
       </c>
@@ -5269,7 +5500,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>135</v>
       </c>
@@ -5283,7 +5514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>146</v>
       </c>
@@ -5297,7 +5528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>147</v>
       </c>
@@ -5311,7 +5542,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>148</v>
       </c>
@@ -5325,7 +5556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>148</v>
       </c>
@@ -5339,7 +5570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>149</v>
       </c>
@@ -5353,7 +5584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>149</v>
       </c>
@@ -5367,7 +5598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>150</v>
       </c>
@@ -5381,7 +5612,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>39</v>
       </c>
@@ -5395,7 +5626,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>151</v>
       </c>
@@ -5409,7 +5640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>151</v>
       </c>
@@ -5423,7 +5654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>152</v>
       </c>
@@ -5437,7 +5668,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>153</v>
       </c>
@@ -5451,7 +5682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>153</v>
       </c>
@@ -5465,7 +5696,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>153</v>
       </c>
@@ -5479,7 +5710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>154</v>
       </c>
@@ -5493,7 +5724,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>155</v>
       </c>
@@ -5507,7 +5738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>155</v>
       </c>
@@ -5521,7 +5752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>155</v>
       </c>
@@ -5535,7 +5766,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>156</v>
       </c>
@@ -5549,7 +5780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>156</v>
       </c>
@@ -5563,7 +5794,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>107</v>
       </c>
@@ -5577,7 +5808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>127</v>
       </c>
@@ -5591,7 +5822,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>157</v>
       </c>
@@ -5605,7 +5836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>67</v>
       </c>
@@ -5619,7 +5850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>158</v>
       </c>
@@ -5633,7 +5864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>158</v>
       </c>
@@ -5647,7 +5878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>159</v>
       </c>
@@ -5661,7 +5892,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>160</v>
       </c>
@@ -5675,7 +5906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>161</v>
       </c>
@@ -5689,7 +5920,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>161</v>
       </c>
@@ -5703,7 +5934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>162</v>
       </c>
@@ -5717,7 +5948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>162</v>
       </c>
@@ -5731,7 +5962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>163</v>
       </c>
@@ -5745,7 +5976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>163</v>
       </c>
@@ -5759,7 +5990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>164</v>
       </c>
@@ -5773,7 +6004,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>164</v>
       </c>
@@ -5787,7 +6018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>165</v>
       </c>
@@ -5801,7 +6032,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>165</v>
       </c>
@@ -5815,7 +6046,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>12</v>
       </c>
@@ -5829,7 +6060,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>139</v>
       </c>
@@ -5843,7 +6074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>127</v>
       </c>
@@ -5857,7 +6088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>163</v>
       </c>
@@ -5871,7 +6102,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>166</v>
       </c>
@@ -5885,7 +6116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>166</v>
       </c>
@@ -5899,7 +6130,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>167</v>
       </c>
@@ -5913,7 +6144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>167</v>
       </c>
@@ -5927,7 +6158,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>168</v>
       </c>
@@ -5941,7 +6172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>155</v>
       </c>
@@ -5955,7 +6186,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>169</v>
       </c>
@@ -5969,7 +6200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>170</v>
       </c>
@@ -5983,7 +6214,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>171</v>
       </c>
@@ -5997,7 +6228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>172</v>
       </c>
@@ -6011,7 +6242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>153</v>
       </c>
@@ -6025,7 +6256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>122</v>
       </c>
@@ -6039,7 +6270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>173</v>
       </c>
@@ -6053,7 +6284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>173</v>
       </c>
@@ -6067,7 +6298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>174</v>
       </c>
@@ -6081,7 +6312,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>174</v>
       </c>
@@ -6095,7 +6326,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>52</v>
       </c>
@@ -6109,7 +6340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>83</v>
       </c>
@@ -6123,7 +6354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>175</v>
       </c>
@@ -6137,7 +6368,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>175</v>
       </c>
@@ -6151,7 +6382,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>176</v>
       </c>
@@ -6165,7 +6396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>118</v>
       </c>
@@ -6179,7 +6410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>177</v>
       </c>
@@ -6193,7 +6424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>96</v>
       </c>
@@ -6207,7 +6438,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>178</v>
       </c>
@@ -6221,7 +6452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>10</v>
       </c>
@@ -6235,7 +6466,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>10</v>
       </c>
@@ -6249,7 +6480,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>136</v>
       </c>
@@ -6263,7 +6494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>84</v>
       </c>
@@ -6277,7 +6508,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>179</v>
       </c>
@@ -6291,7 +6522,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>97</v>
       </c>
@@ -6305,7 +6536,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>180</v>
       </c>
@@ -6319,7 +6550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>181</v>
       </c>
@@ -6333,7 +6564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>181</v>
       </c>
@@ -6347,7 +6578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>182</v>
       </c>
@@ -6361,7 +6592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>183</v>
       </c>
@@ -6375,7 +6606,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>183</v>
       </c>
@@ -6389,7 +6620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>183</v>
       </c>
@@ -6403,7 +6634,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>184</v>
       </c>
@@ -6417,7 +6648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>153</v>
       </c>
@@ -6431,7 +6662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>185</v>
       </c>
@@ -6445,7 +6676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>185</v>
       </c>
@@ -6459,7 +6690,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>123</v>
       </c>
@@ -6473,7 +6704,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>186</v>
       </c>
@@ -6487,7 +6718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>186</v>
       </c>
@@ -6501,7 +6732,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>187</v>
       </c>
@@ -6515,7 +6746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>7</v>
       </c>
@@ -6529,7 +6760,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>7</v>
       </c>
@@ -6543,7 +6774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>188</v>
       </c>
@@ -6557,7 +6788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>127</v>
       </c>
@@ -6571,7 +6802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>189</v>
       </c>
@@ -6585,7 +6816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>123</v>
       </c>
@@ -6599,7 +6830,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>55</v>
       </c>
@@ -6613,7 +6844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>120</v>
       </c>
@@ -6627,7 +6858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>45</v>
       </c>
@@ -6641,7 +6872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>190</v>
       </c>
@@ -6655,7 +6886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>113</v>
       </c>
@@ -6669,7 +6900,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>191</v>
       </c>
@@ -6683,7 +6914,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>193</v>
       </c>
@@ -6697,7 +6928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>194</v>
       </c>
@@ -6711,7 +6942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>195</v>
       </c>
@@ -6725,7 +6956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>196</v>
       </c>
@@ -6739,7 +6970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>197</v>
       </c>
@@ -6753,7 +6984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>197</v>
       </c>
@@ -6767,7 +6998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>198</v>
       </c>
@@ -6781,7 +7012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>198</v>
       </c>
@@ -6795,7 +7026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>199</v>
       </c>
@@ -6809,7 +7040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>199</v>
       </c>
@@ -6823,7 +7054,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>58</v>
       </c>
@@ -6837,7 +7068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>200</v>
       </c>
@@ -6851,7 +7082,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>201</v>
       </c>
@@ -6865,7 +7096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>202</v>
       </c>
@@ -6879,7 +7110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>203</v>
       </c>
@@ -6893,7 +7124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>204</v>
       </c>
@@ -6907,7 +7138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>205</v>
       </c>
@@ -6921,7 +7152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>121</v>
       </c>
@@ -6935,7 +7166,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>121</v>
       </c>
@@ -6949,7 +7180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>206</v>
       </c>
@@ -6963,7 +7194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>207</v>
       </c>
@@ -6977,7 +7208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>208</v>
       </c>
@@ -6991,7 +7222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>209</v>
       </c>
@@ -7005,7 +7236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>210</v>
       </c>
@@ -7019,7 +7250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>116</v>
       </c>
@@ -7033,7 +7264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>116</v>
       </c>
@@ -7047,7 +7278,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>116</v>
       </c>
@@ -7061,7 +7292,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>116</v>
       </c>
@@ -7075,7 +7306,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>63</v>
       </c>
@@ -7089,7 +7320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>63</v>
       </c>
@@ -7103,7 +7334,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>124</v>
       </c>
@@ -7117,7 +7348,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>96</v>
       </c>
@@ -7131,7 +7362,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>96</v>
       </c>
@@ -7145,7 +7376,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>211</v>
       </c>
@@ -7159,7 +7390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>212</v>
       </c>
@@ -7173,7 +7404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>213</v>
       </c>
@@ -7187,7 +7418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>214</v>
       </c>
@@ -7201,7 +7432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>215</v>
       </c>
@@ -7215,7 +7446,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>216</v>
       </c>
@@ -7229,7 +7460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>217</v>
       </c>
@@ -7243,7 +7474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>198</v>
       </c>
@@ -7257,7 +7488,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>195</v>
       </c>
@@ -7271,7 +7502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>218</v>
       </c>
@@ -7285,7 +7516,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>219</v>
       </c>
@@ -7299,7 +7530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>83</v>
       </c>
@@ -7313,7 +7544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>196</v>
       </c>
@@ -7327,7 +7558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>220</v>
       </c>
@@ -7341,7 +7572,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>221</v>
       </c>
@@ -7355,7 +7586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>222</v>
       </c>
@@ -7369,7 +7600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>204</v>
       </c>
@@ -7383,7 +7614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>223</v>
       </c>
@@ -7397,7 +7628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>157</v>
       </c>
@@ -7411,7 +7642,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>76</v>
       </c>
@@ -7425,7 +7656,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>224</v>
       </c>
@@ -7439,7 +7670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>225</v>
       </c>
@@ -7453,7 +7684,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>196</v>
       </c>
@@ -7467,7 +7698,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>105</v>
       </c>
@@ -7481,7 +7712,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>228</v>
       </c>
@@ -7495,7 +7726,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>230</v>
       </c>
@@ -7509,7 +7740,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>204</v>
       </c>
@@ -7523,7 +7754,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>205</v>
       </c>
@@ -7537,7 +7768,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>234</v>
       </c>
@@ -7551,7 +7782,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>236</v>
       </c>
@@ -7565,7 +7796,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>238</v>
       </c>
@@ -7579,7 +7810,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>195</v>
       </c>
@@ -7593,7 +7824,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>59</v>
       </c>
@@ -7607,7 +7838,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>242</v>
       </c>
@@ -7621,7 +7852,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>62</v>
       </c>
@@ -7635,7 +7866,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>245</v>
       </c>
@@ -7649,7 +7880,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>247</v>
       </c>
@@ -7663,7 +7894,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>57</v>
       </c>
@@ -7677,7 +7908,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>60</v>
       </c>
@@ -7691,7 +7922,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>236</v>
       </c>
@@ -7705,7 +7936,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>18</v>
       </c>
@@ -7719,7 +7950,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>121</v>
       </c>
@@ -7733,7 +7964,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>253</v>
       </c>
@@ -7747,7 +7978,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>255</v>
       </c>
@@ -7761,7 +7992,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>204</v>
       </c>
@@ -7775,7 +8006,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>62</v>
       </c>
@@ -7789,7 +8020,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>60</v>
       </c>
@@ -7803,7 +8034,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>260</v>
       </c>
@@ -7817,7 +8048,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>262</v>
       </c>
@@ -7831,7 +8062,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>264</v>
       </c>
@@ -7845,7 +8076,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>220</v>
       </c>
@@ -7859,7 +8090,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>266</v>
       </c>
@@ -7873,7 +8104,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>268</v>
       </c>
@@ -7887,7 +8118,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>107</v>
       </c>
@@ -7901,7 +8132,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>270</v>
       </c>
@@ -7915,7 +8146,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>202</v>
       </c>
@@ -7929,7 +8160,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>272</v>
       </c>
@@ -7943,7 +8174,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>274</v>
       </c>
@@ -7957,7 +8188,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>276</v>
       </c>
@@ -7971,7 +8202,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>242</v>
       </c>
@@ -7985,7 +8216,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>278</v>
       </c>
@@ -7999,7 +8230,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>23</v>
       </c>
@@ -8013,7 +8244,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>62</v>
       </c>
@@ -8027,7 +8258,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>60</v>
       </c>
@@ -8041,7 +8272,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>245</v>
       </c>
@@ -8055,7 +8286,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>281</v>
       </c>
@@ -8069,7 +8300,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>282</v>
       </c>
@@ -8083,7 +8314,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>283</v>
       </c>
@@ -8097,7 +8328,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>284</v>
       </c>
@@ -8111,7 +8342,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>207</v>
       </c>
@@ -8125,7 +8356,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>76</v>
       </c>
@@ -8139,7 +8370,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>285</v>
       </c>
@@ -8153,7 +8384,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>262</v>
       </c>
@@ -8167,7 +8398,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>286</v>
       </c>
@@ -8181,7 +8412,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>287</v>
       </c>
@@ -8195,7 +8426,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>135</v>
       </c>
@@ -8209,7 +8440,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>57</v>
       </c>
@@ -8223,7 +8454,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>289</v>
       </c>
@@ -8237,7 +8468,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>268</v>
       </c>
@@ -8251,7 +8482,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>290</v>
       </c>
@@ -8265,7 +8496,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>107</v>
       </c>
@@ -8279,7 +8510,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>255</v>
       </c>
@@ -8293,7 +8524,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>202</v>
       </c>
@@ -8307,7 +8538,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>291</v>
       </c>
@@ -8321,7 +8552,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>228</v>
       </c>
@@ -8335,7 +8566,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>292</v>
       </c>
@@ -8349,7 +8580,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>293</v>
       </c>
@@ -8363,7 +8594,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>274</v>
       </c>
@@ -8377,7 +8608,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>294</v>
       </c>
@@ -8391,7 +8622,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>276</v>
       </c>
@@ -8405,7 +8636,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>296</v>
       </c>
@@ -8419,7 +8650,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>297</v>
       </c>
@@ -8433,7 +8664,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>23</v>
       </c>
@@ -8447,7 +8678,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>281</v>
       </c>
@@ -8461,7 +8692,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>298</v>
       </c>
@@ -8475,7 +8706,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>236</v>
       </c>
@@ -8489,7 +8720,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>300</v>
       </c>
@@ -8503,7 +8734,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>286</v>
       </c>
@@ -8517,7 +8748,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>303</v>
       </c>
@@ -8531,7 +8762,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>289</v>
       </c>
@@ -8545,7 +8776,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>304</v>
       </c>
@@ -8559,7 +8790,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>305</v>
       </c>
@@ -8573,7 +8804,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>196</v>
       </c>
@@ -8587,7 +8818,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>107</v>
       </c>
@@ -8601,7 +8832,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>255</v>
       </c>
@@ -8615,7 +8846,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>228</v>
       </c>
@@ -8629,7 +8860,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>307</v>
       </c>
@@ -8643,7 +8874,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>293</v>
       </c>
@@ -8657,7 +8888,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>296</v>
       </c>
@@ -8671,7 +8902,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>309</v>
       </c>
@@ -8685,7 +8916,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>242</v>
       </c>
@@ -8699,7 +8930,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>205</v>
       </c>
@@ -8713,7 +8944,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>62</v>
       </c>
@@ -8727,7 +8958,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>245</v>
       </c>
@@ -8741,7 +8972,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>311</v>
       </c>
@@ -8755,7 +8986,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>283</v>
       </c>
@@ -8769,7 +9000,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>236</v>
       </c>
@@ -8783,7 +9014,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>262</v>
       </c>
@@ -8797,7 +9028,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>208</v>
       </c>
@@ -8811,7 +9042,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>286</v>
       </c>
@@ -8825,7 +9056,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>253</v>
       </c>
@@ -8839,7 +9070,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>304</v>
       </c>
@@ -8853,7 +9084,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>38</v>
       </c>
@@ -8867,7 +9098,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>126</v>
       </c>
@@ -8881,7 +9112,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>316</v>
       </c>
@@ -8895,7 +9126,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>196</v>
       </c>
@@ -8909,7 +9140,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>107</v>
       </c>
@@ -8923,7 +9154,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>318</v>
       </c>
@@ -8937,7 +9168,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>159</v>
       </c>
@@ -8951,7 +9182,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>228</v>
       </c>
@@ -8965,7 +9196,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>293</v>
       </c>
@@ -8979,7 +9210,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>296</v>
       </c>
@@ -8993,7 +9224,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>309</v>
       </c>
@@ -9007,7 +9238,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>242</v>
       </c>
@@ -9021,7 +9252,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>12</v>
       </c>
@@ -9035,7 +9266,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>62</v>
       </c>
@@ -9049,7 +9280,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>245</v>
       </c>
@@ -9063,7 +9294,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>283</v>
       </c>
@@ -9077,7 +9308,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>121</v>
       </c>
@@ -9091,7 +9322,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>286</v>
       </c>
@@ -9105,7 +9336,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>324</v>
       </c>
@@ -9119,7 +9350,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>38</v>
       </c>
@@ -9133,7 +9364,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>196</v>
       </c>
@@ -9147,7 +9378,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>327</v>
       </c>
@@ -9161,7 +9392,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>293</v>
       </c>
@@ -9175,7 +9406,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>296</v>
       </c>
@@ -9189,7 +9420,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>309</v>
       </c>
@@ -9203,7 +9434,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>62</v>
       </c>
@@ -9217,7 +9448,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>245</v>
       </c>
@@ -9231,7 +9462,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>330</v>
       </c>
@@ -9245,7 +9476,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>42</v>
       </c>
@@ -9259,7 +9490,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>286</v>
       </c>
@@ -9273,7 +9504,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>196</v>
       </c>
@@ -9287,7 +9518,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>333</v>
       </c>
@@ -9301,7 +9532,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>296</v>
       </c>
@@ -9315,7 +9546,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>309</v>
       </c>
@@ -9329,7 +9560,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>62</v>
       </c>
@@ -9343,7 +9574,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>152</v>
       </c>
@@ -9357,7 +9588,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>196</v>
       </c>
@@ -9371,7 +9602,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>242</v>
       </c>
@@ -9385,7 +9616,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>62</v>
       </c>
@@ -9399,7 +9630,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>152</v>
       </c>
@@ -9413,7 +9644,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>76</v>
       </c>
@@ -9427,7 +9658,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>126</v>
       </c>
@@ -9441,7 +9672,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>196</v>
       </c>
@@ -9455,7 +9686,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>107</v>
       </c>
@@ -9469,7 +9700,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>339</v>
       </c>
@@ -9483,7 +9714,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>341</v>
       </c>
@@ -9497,7 +9728,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>341</v>
       </c>
@@ -9511,7 +9742,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>341</v>
       </c>
@@ -9525,7 +9756,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>196</v>
       </c>
@@ -9539,7 +9770,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>343</v>
       </c>
@@ -9553,7 +9784,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>345</v>
       </c>
@@ -9567,7 +9798,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>345</v>
       </c>
@@ -9581,7 +9812,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>62</v>
       </c>
@@ -9595,7 +9826,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>260</v>
       </c>
@@ -9609,7 +9840,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>236</v>
       </c>
@@ -9623,7 +9854,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>348</v>
       </c>
@@ -9637,7 +9868,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>350</v>
       </c>
@@ -9651,7 +9882,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>72</v>
       </c>
@@ -9665,7 +9896,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>247</v>
       </c>
@@ -9679,7 +9910,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>354</v>
       </c>
@@ -9693,7 +9924,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>356</v>
       </c>
@@ -9707,7 +9938,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>358</v>
       </c>
@@ -9721,7 +9952,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>359</v>
       </c>
@@ -9735,7 +9966,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>361</v>
       </c>
@@ -9749,7 +9980,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>177</v>
       </c>
@@ -9763,7 +9994,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>361</v>
       </c>
@@ -9777,7 +10008,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>363</v>
       </c>
@@ -9791,7 +10022,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>190</v>
       </c>
@@ -9805,7 +10036,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>365</v>
       </c>
@@ -9819,7 +10050,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>366</v>
       </c>
@@ -9833,7 +10064,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>79</v>
       </c>
@@ -9847,7 +10078,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>361</v>
       </c>
@@ -9861,7 +10092,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>324</v>
       </c>
@@ -9875,7 +10106,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>367</v>
       </c>
@@ -9889,7 +10120,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>36</v>
       </c>
@@ -9903,7 +10134,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>36</v>
       </c>
@@ -9917,7 +10148,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>369</v>
       </c>
@@ -9931,7 +10162,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>196</v>
       </c>
@@ -9945,7 +10176,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>370</v>
       </c>
@@ -9959,7 +10190,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>290</v>
       </c>
@@ -9973,7 +10204,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>107</v>
       </c>
@@ -9987,7 +10218,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>371</v>
       </c>
@@ -10001,7 +10232,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>291</v>
       </c>
@@ -10015,7 +10246,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>228</v>
       </c>
@@ -10029,7 +10260,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>272</v>
       </c>
@@ -10043,7 +10274,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>296</v>
       </c>
@@ -10057,7 +10288,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>242</v>
       </c>
@@ -10071,7 +10302,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>62</v>
       </c>
@@ -10085,7 +10316,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>372</v>
       </c>
@@ -10099,7 +10330,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>282</v>
       </c>
@@ -10113,7 +10344,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>373</v>
       </c>
@@ -10127,7 +10358,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>236</v>
       </c>
@@ -10141,7 +10372,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>217</v>
       </c>
@@ -10155,7 +10386,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>374</v>
       </c>
@@ -10169,7 +10400,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>375</v>
       </c>
@@ -10183,7 +10414,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>376</v>
       </c>
@@ -10197,7 +10428,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>377</v>
       </c>
@@ -10211,7 +10442,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>379</v>
       </c>
@@ -10225,7 +10456,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>272</v>
       </c>
@@ -10239,7 +10470,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>296</v>
       </c>
@@ -10253,7 +10484,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>242</v>
       </c>
@@ -10267,7 +10498,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>373</v>
       </c>
@@ -10281,7 +10512,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>236</v>
       </c>
@@ -10295,7 +10526,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>380</v>
       </c>
@@ -10309,7 +10540,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>361</v>
       </c>
@@ -10323,7 +10554,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>381</v>
       </c>
@@ -10337,7 +10568,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>382</v>
       </c>
@@ -10351,7 +10582,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>126</v>
       </c>
@@ -10365,7 +10596,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>348</v>
       </c>
@@ -10379,7 +10610,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>132</v>
       </c>
@@ -10393,7 +10624,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>383</v>
       </c>
@@ -10407,7 +10638,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>384</v>
       </c>
@@ -10421,7 +10652,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>12</v>
       </c>
@@ -10435,7 +10666,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>385</v>
       </c>
@@ -10449,7 +10680,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>115</v>
       </c>
@@ -10463,7 +10694,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>115</v>
       </c>
@@ -10477,7 +10708,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>72</v>
       </c>
@@ -10491,7 +10722,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>72</v>
       </c>
@@ -10505,7 +10736,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>121</v>
       </c>
@@ -10519,7 +10750,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>121</v>
       </c>
@@ -10533,7 +10764,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>389</v>
       </c>
@@ -10547,7 +10778,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>86</v>
       </c>
@@ -10561,7 +10792,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>118</v>
       </c>
@@ -10581,7 +10812,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>393</v>
       </c>
@@ -10601,7 +10832,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>393</v>
       </c>
@@ -10621,7 +10852,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>393</v>
       </c>
@@ -10641,7 +10872,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>393</v>
       </c>
@@ -10661,7 +10892,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>214</v>
       </c>
@@ -10681,7 +10912,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>398</v>
       </c>
@@ -10701,7 +10932,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>401</v>
       </c>
@@ -10721,7 +10952,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>404</v>
       </c>
@@ -10741,7 +10972,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>10</v>
       </c>
@@ -10761,7 +10992,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>111</v>
       </c>
@@ -10781,7 +11012,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>221</v>
       </c>
@@ -10801,7 +11032,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>98</v>
       </c>
@@ -10821,7 +11052,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>415</v>
       </c>
@@ -10841,7 +11072,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>343</v>
       </c>
@@ -10861,7 +11092,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>307</v>
       </c>
@@ -10881,7 +11112,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>186</v>
       </c>
@@ -10901,7 +11132,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>71</v>
       </c>
@@ -10921,7 +11152,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>427</v>
       </c>
@@ -10941,7 +11172,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>430</v>
       </c>
@@ -10961,7 +11192,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>430</v>
       </c>
@@ -10981,7 +11212,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>433</v>
       </c>
@@ -11001,7 +11232,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>118</v>
       </c>
@@ -11021,7 +11252,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>65</v>
       </c>
@@ -11041,7 +11272,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>440</v>
       </c>
@@ -11061,7 +11292,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>443</v>
       </c>
@@ -11081,7 +11312,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>446</v>
       </c>
@@ -11101,7 +11332,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>307</v>
       </c>
@@ -11121,7 +11352,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>415</v>
       </c>
@@ -11141,7 +11372,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>453</v>
       </c>
@@ -11161,7 +11392,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>453</v>
       </c>
@@ -11181,7 +11412,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>456</v>
       </c>
@@ -11201,7 +11432,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>459</v>
       </c>
@@ -11221,7 +11452,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>462</v>
       </c>
@@ -11241,7 +11472,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>221</v>
       </c>
@@ -11261,7 +11492,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>467</v>
       </c>
@@ -11281,7 +11512,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>470</v>
       </c>
@@ -11301,7 +11532,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>135</v>
       </c>
@@ -11321,7 +11552,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>475</v>
       </c>
@@ -11341,7 +11572,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>478</v>
       </c>
@@ -11361,7 +11592,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>480</v>
       </c>
@@ -11381,7 +11612,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>483</v>
       </c>
@@ -11401,7 +11632,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>389</v>
       </c>
@@ -11421,7 +11652,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>488</v>
       </c>
@@ -11441,7 +11672,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>343</v>
       </c>
@@ -11461,7 +11692,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>493</v>
       </c>
@@ -11481,7 +11712,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>496</v>
       </c>
@@ -11501,7 +11732,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>307</v>
       </c>
@@ -11521,7 +11752,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>501</v>
       </c>
@@ -11541,7 +11772,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>504</v>
       </c>
@@ -11561,7 +11792,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>63</v>
       </c>
@@ -11581,7 +11812,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>83</v>
       </c>
@@ -11601,7 +11832,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>26</v>
       </c>
@@ -11621,7 +11852,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>511</v>
       </c>
@@ -11641,7 +11872,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>514</v>
       </c>
@@ -11661,7 +11892,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>186</v>
       </c>
@@ -11681,7 +11912,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>519</v>
       </c>
@@ -11701,7 +11932,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>522</v>
       </c>
@@ -11721,7 +11952,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>119</v>
       </c>
@@ -11741,7 +11972,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>470</v>
       </c>
@@ -11761,7 +11992,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>30</v>
       </c>
@@ -11781,7 +12012,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>33</v>
       </c>
@@ -11801,7 +12032,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>531</v>
       </c>
@@ -11821,7 +12052,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>534</v>
       </c>
@@ -11841,7 +12072,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>535</v>
       </c>
@@ -11861,7 +12092,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>538</v>
       </c>
@@ -11881,7 +12112,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>541</v>
       </c>
@@ -11901,7 +12132,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -11921,7 +12152,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>546</v>
       </c>
@@ -11941,7 +12172,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>186</v>
       </c>
@@ -11961,487 +12192,487 @@
         <v>550</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>443</v>
+        <v>66</v>
       </c>
       <c r="B647" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C647" s="1">
-        <v>46108</v>
+        <v>46083</v>
       </c>
       <c r="D647" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="E647" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="F647" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B648" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C648" s="1">
-        <v>46094</v>
+        <v>46090</v>
       </c>
       <c r="D648" t="s">
-        <v>355</v>
+        <v>390</v>
       </c>
       <c r="E648" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F648" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>552</v>
+        <v>120</v>
       </c>
       <c r="B649" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C649" s="1">
         <v>46090</v>
       </c>
       <c r="D649" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="E649" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="F649" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>111</v>
+        <v>559</v>
       </c>
       <c r="B650" t="s">
+        <v>5</v>
+      </c>
+      <c r="C650" s="1">
+        <v>46090</v>
+      </c>
+      <c r="D650" t="s">
+        <v>353</v>
+      </c>
+      <c r="E650" t="s">
+        <v>602</v>
+      </c>
+      <c r="F650" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>554</v>
+      </c>
+      <c r="B651" t="s">
         <v>13</v>
       </c>
-      <c r="C650" s="1">
-        <v>46111</v>
-      </c>
-      <c r="D650" t="s">
+      <c r="C651" s="1">
+        <v>46091</v>
+      </c>
+      <c r="D651" t="s">
+        <v>588</v>
+      </c>
+      <c r="E651" t="s">
+        <v>589</v>
+      </c>
+      <c r="F651" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>553</v>
+      </c>
+      <c r="B652" t="s">
+        <v>5</v>
+      </c>
+      <c r="C652" s="1">
+        <v>46092</v>
+      </c>
+      <c r="D652" t="s">
+        <v>360</v>
+      </c>
+      <c r="E652" t="s">
+        <v>573</v>
+      </c>
+      <c r="F652" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>551</v>
+      </c>
+      <c r="B653" t="s">
+        <v>13</v>
+      </c>
+      <c r="C653" s="1">
+        <v>46094</v>
+      </c>
+      <c r="D653" t="s">
+        <v>355</v>
+      </c>
+      <c r="E653" t="s">
+        <v>563</v>
+      </c>
+      <c r="F653" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>427</v>
+      </c>
+      <c r="B654" t="s">
+        <v>19</v>
+      </c>
+      <c r="C654" s="1">
+        <v>46097</v>
+      </c>
+      <c r="D654" t="s">
+        <v>355</v>
+      </c>
+      <c r="E654" t="s">
+        <v>569</v>
+      </c>
+      <c r="F654" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>555</v>
+      </c>
+      <c r="B655" t="s">
+        <v>8</v>
+      </c>
+      <c r="C655" s="1">
+        <v>46097</v>
+      </c>
+      <c r="D655" t="s">
+        <v>355</v>
+      </c>
+      <c r="E655" t="s">
+        <v>349</v>
+      </c>
+      <c r="F655" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>496</v>
+      </c>
+      <c r="B656" t="s">
+        <v>5</v>
+      </c>
+      <c r="C656" s="1">
+        <v>46098</v>
+      </c>
+      <c r="D656" t="s">
         <v>362</v>
       </c>
-      <c r="E650" t="s">
-        <v>567</v>
-      </c>
-      <c r="F650" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A651" t="s">
-        <v>427</v>
-      </c>
-      <c r="B651" t="s">
-        <v>19</v>
-      </c>
-      <c r="C651" s="1">
-        <v>46097</v>
-      </c>
-      <c r="D651" t="s">
-        <v>355</v>
-      </c>
-      <c r="E651" t="s">
-        <v>569</v>
-      </c>
-      <c r="F651" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A652" t="s">
-        <v>120</v>
-      </c>
-      <c r="B652" t="s">
-        <v>15</v>
-      </c>
-      <c r="C652" s="1">
-        <v>46090</v>
-      </c>
-      <c r="D652" t="s">
-        <v>364</v>
-      </c>
-      <c r="E652" t="s">
-        <v>571</v>
-      </c>
-      <c r="F652" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A653" t="s">
-        <v>553</v>
-      </c>
-      <c r="B653" t="s">
-        <v>5</v>
-      </c>
-      <c r="C653" s="1">
-        <v>46092</v>
-      </c>
-      <c r="D653" t="s">
-        <v>360</v>
-      </c>
-      <c r="E653" t="s">
-        <v>573</v>
-      </c>
-      <c r="F653" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A654" t="s">
-        <v>496</v>
-      </c>
-      <c r="B654" t="s">
-        <v>5</v>
-      </c>
-      <c r="C654" s="1">
-        <v>46098</v>
-      </c>
-      <c r="D654" t="s">
-        <v>362</v>
-      </c>
-      <c r="E654" t="s">
+      <c r="E656" t="s">
         <v>575</v>
       </c>
-      <c r="F654" t="s">
+      <c r="F656" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A655" t="s">
-        <v>66</v>
-      </c>
-      <c r="B655" t="s">
-        <v>13</v>
-      </c>
-      <c r="C655" s="1">
-        <v>46083</v>
-      </c>
-      <c r="D655" t="s">
-        <v>390</v>
-      </c>
-      <c r="E655" t="s">
-        <v>577</v>
-      </c>
-      <c r="F655" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A656" t="s">
-        <v>98</v>
-      </c>
-      <c r="B656" t="s">
-        <v>19</v>
-      </c>
-      <c r="C656" s="1">
-        <v>46101</v>
-      </c>
-      <c r="D656" t="s">
-        <v>355</v>
-      </c>
-      <c r="E656" t="s">
-        <v>579</v>
-      </c>
-      <c r="F656" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>453</v>
+        <v>554</v>
       </c>
       <c r="B657" t="s">
         <v>13</v>
       </c>
       <c r="C657" s="1">
-        <v>46107</v>
+        <v>46098</v>
       </c>
       <c r="D657" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E657" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="F657" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>453</v>
+        <v>98</v>
       </c>
       <c r="B658" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C658" s="1">
-        <v>46106</v>
+        <v>46101</v>
       </c>
       <c r="D658" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E658" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F658" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>415</v>
+        <v>103</v>
       </c>
       <c r="B659" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C659" s="1">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="D659" t="s">
         <v>355</v>
       </c>
       <c r="E659" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="F659" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B660" t="s">
+        <v>8</v>
+      </c>
+      <c r="C660" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D660" t="s">
+        <v>362</v>
+      </c>
+      <c r="E660" t="s">
+        <v>598</v>
+      </c>
+      <c r="F660" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>555</v>
+      </c>
+      <c r="B661" t="s">
+        <v>8</v>
+      </c>
+      <c r="C661" s="1">
+        <v>46104</v>
+      </c>
+      <c r="D661" t="s">
+        <v>355</v>
+      </c>
+      <c r="E661" t="s">
+        <v>593</v>
+      </c>
+      <c r="F661" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>453</v>
+      </c>
+      <c r="B662" t="s">
         <v>13</v>
       </c>
-      <c r="C660" s="1">
-        <v>46098</v>
-      </c>
-      <c r="D660" t="s">
-        <v>355</v>
-      </c>
-      <c r="E660" t="s">
-        <v>586</v>
-      </c>
-      <c r="F660" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A661" t="s">
-        <v>554</v>
-      </c>
-      <c r="B661" t="s">
-        <v>13</v>
-      </c>
-      <c r="C661" s="1">
-        <v>46091</v>
-      </c>
-      <c r="D661" t="s">
-        <v>588</v>
-      </c>
-      <c r="E661" t="s">
-        <v>589</v>
-      </c>
-      <c r="F661" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A662" t="s">
-        <v>103</v>
-      </c>
-      <c r="B662" t="s">
-        <v>19</v>
-      </c>
       <c r="C662" s="1">
-        <v>46101</v>
+        <v>46106</v>
       </c>
       <c r="D662" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E662" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="F662" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B663" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="C663" s="1">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="D663" t="s">
         <v>355</v>
       </c>
       <c r="E663" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F663" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B664" t="s">
         <v>8</v>
       </c>
       <c r="C664" s="1">
-        <v>46097</v>
+        <v>46106</v>
       </c>
       <c r="D664" t="s">
         <v>355</v>
       </c>
       <c r="E664" t="s">
-        <v>349</v>
+        <v>600</v>
       </c>
       <c r="F664" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="665" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="B665" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="C665" s="1">
         <v>46106</v>
       </c>
       <c r="D665" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E665" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="F665" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="666" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>557</v>
+        <v>453</v>
       </c>
       <c r="B666" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C666" s="1">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="D666" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="E666" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="F666" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="667" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>558</v>
+        <v>443</v>
       </c>
       <c r="B667" t="s">
         <v>8</v>
       </c>
       <c r="C667" s="1">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="D667" t="s">
+        <v>360</v>
+      </c>
+      <c r="E667" t="s">
+        <v>561</v>
+      </c>
+      <c r="F667" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A668" t="s">
+        <v>415</v>
+      </c>
+      <c r="B668" t="s">
+        <v>11</v>
+      </c>
+      <c r="C668" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D668" t="s">
         <v>355</v>
       </c>
-      <c r="E667" t="s">
-        <v>600</v>
-      </c>
-      <c r="F667" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A668" t="s">
-        <v>559</v>
-      </c>
-      <c r="B668" t="s">
-        <v>5</v>
-      </c>
-      <c r="C668" s="1">
-        <v>46090</v>
-      </c>
-      <c r="D668" t="s">
-        <v>353</v>
-      </c>
       <c r="E668" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="F668" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>560</v>
+        <v>111</v>
       </c>
       <c r="B669" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C669" s="1">
         <v>46111</v>
       </c>
       <c r="D669" t="s">
+        <v>362</v>
+      </c>
+      <c r="E669" t="s">
+        <v>567</v>
+      </c>
+      <c r="F669" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A670" t="s">
+        <v>560</v>
+      </c>
+      <c r="B670" t="s">
+        <v>19</v>
+      </c>
+      <c r="C670" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D670" t="s">
         <v>355</v>
       </c>
-      <c r="E669" t="s">
+      <c r="E670" t="s">
         <v>604</v>
       </c>
-      <c r="F669" t="s">
+      <c r="F670" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A670" t="s">
-        <v>82</v>
-      </c>
-      <c r="B670" t="s">
-        <v>13</v>
-      </c>
-      <c r="C670" s="1">
-        <v>46106</v>
-      </c>
-      <c r="D670" t="s">
-        <v>353</v>
-      </c>
-      <c r="E670" t="s">
-        <v>606</v>
-      </c>
-      <c r="F670" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>343</v>
       </c>
@@ -12461,750 +12692,1910 @@
         <v>609</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>221</v>
+        <v>307</v>
       </c>
       <c r="B672" t="s">
-        <v>192</v>
+        <v>8</v>
       </c>
       <c r="C672" s="1">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="D672" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E672" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F672" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
+        <v>305</v>
+      </c>
+      <c r="B673" t="s">
+        <v>8</v>
+      </c>
+      <c r="C673" s="1">
+        <v>46114</v>
+      </c>
+      <c r="D673" t="s">
+        <v>357</v>
+      </c>
+      <c r="E673" t="s">
+        <v>640</v>
+      </c>
+      <c r="F673" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>158</v>
+      </c>
+      <c r="B674" t="s">
+        <v>13</v>
+      </c>
+      <c r="C674" s="1">
+        <v>46125</v>
+      </c>
+      <c r="D674" t="s">
+        <v>360</v>
+      </c>
+      <c r="E674" t="s">
+        <v>625</v>
+      </c>
+      <c r="F674" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
         <v>612</v>
       </c>
-      <c r="B673" t="s">
-        <v>5</v>
-      </c>
-      <c r="C673" s="1">
+      <c r="B675" t="s">
+        <v>5</v>
+      </c>
+      <c r="C675" s="1">
         <v>46126</v>
-      </c>
-      <c r="D673" t="s">
-        <v>362</v>
-      </c>
-      <c r="E673" t="s">
-        <v>497</v>
-      </c>
-      <c r="F673" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A674" t="s">
-        <v>307</v>
-      </c>
-      <c r="B674" t="s">
-        <v>8</v>
-      </c>
-      <c r="C674" s="1">
-        <v>46114</v>
-      </c>
-      <c r="D674" t="s">
-        <v>357</v>
-      </c>
-      <c r="E674" t="s">
-        <v>614</v>
-      </c>
-      <c r="F674" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A675" t="s">
-        <v>615</v>
-      </c>
-      <c r="B675" t="s">
-        <v>11</v>
-      </c>
-      <c r="C675" s="1">
-        <v>46128</v>
       </c>
       <c r="D675" t="s">
         <v>362</v>
       </c>
       <c r="E675" t="s">
+        <v>497</v>
+      </c>
+      <c r="F675" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>629</v>
+      </c>
+      <c r="B676" t="s">
+        <v>13</v>
+      </c>
+      <c r="C676" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D676" t="s">
+        <v>353</v>
+      </c>
+      <c r="E676" t="s">
+        <v>630</v>
+      </c>
+      <c r="F676" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>637</v>
+      </c>
+      <c r="B677" t="s">
+        <v>13</v>
+      </c>
+      <c r="C677" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D677" t="s">
+        <v>357</v>
+      </c>
+      <c r="E677" t="s">
+        <v>638</v>
+      </c>
+      <c r="F677" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>221</v>
+      </c>
+      <c r="B678" t="s">
+        <v>192</v>
+      </c>
+      <c r="C678" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D678" t="s">
+        <v>355</v>
+      </c>
+      <c r="E678" t="s">
+        <v>610</v>
+      </c>
+      <c r="F678" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>615</v>
+      </c>
+      <c r="B679" t="s">
+        <v>11</v>
+      </c>
+      <c r="C679" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D679" t="s">
+        <v>362</v>
+      </c>
+      <c r="E679" t="s">
+        <v>617</v>
+      </c>
+      <c r="F679" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>615</v>
+      </c>
+      <c r="B680" t="s">
+        <v>11</v>
+      </c>
+      <c r="C680" s="1">
+        <v>46128</v>
+      </c>
+      <c r="D680" t="s">
+        <v>362</v>
+      </c>
+      <c r="E680" t="s">
         <v>575</v>
       </c>
-      <c r="F675" t="s">
+      <c r="F680" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A676" t="s">
-        <v>615</v>
-      </c>
-      <c r="B676" t="s">
-        <v>11</v>
-      </c>
-      <c r="C676" s="1">
-        <v>46127</v>
-      </c>
-      <c r="D676" t="s">
-        <v>362</v>
-      </c>
-      <c r="E676" t="s">
-        <v>617</v>
-      </c>
-      <c r="F676" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A677" t="s">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>158</v>
+      </c>
+      <c r="B681" t="s">
+        <v>13</v>
+      </c>
+      <c r="C681" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D681" t="s">
+        <v>386</v>
+      </c>
+      <c r="E681" t="s">
+        <v>623</v>
+      </c>
+      <c r="F681" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>559</v>
+      </c>
+      <c r="B682" t="s">
+        <v>5</v>
+      </c>
+      <c r="C682" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D682" t="s">
+        <v>357</v>
+      </c>
+      <c r="E682" t="s">
+        <v>627</v>
+      </c>
+      <c r="F682" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
         <v>339</v>
-      </c>
-      <c r="B677" t="s">
-        <v>11</v>
-      </c>
-      <c r="C677" s="1">
-        <v>46139</v>
-      </c>
-      <c r="D677" t="s">
-        <v>386</v>
-      </c>
-      <c r="E677" t="s">
-        <v>619</v>
-      </c>
-      <c r="F677" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A678" t="s">
-        <v>52</v>
-      </c>
-      <c r="B678" t="s">
-        <v>8</v>
-      </c>
-      <c r="C678" s="1">
-        <v>46140</v>
-      </c>
-      <c r="D678" t="s">
-        <v>360</v>
-      </c>
-      <c r="E678" t="s">
-        <v>621</v>
-      </c>
-      <c r="F678" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A679" t="s">
-        <v>158</v>
-      </c>
-      <c r="B679" t="s">
-        <v>13</v>
-      </c>
-      <c r="C679" s="1">
-        <v>46134</v>
-      </c>
-      <c r="D679" t="s">
-        <v>386</v>
-      </c>
-      <c r="E679" t="s">
-        <v>623</v>
-      </c>
-      <c r="F679" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A680" t="s">
-        <v>158</v>
-      </c>
-      <c r="B680" t="s">
-        <v>13</v>
-      </c>
-      <c r="C680" s="1">
-        <v>46125</v>
-      </c>
-      <c r="D680" t="s">
-        <v>360</v>
-      </c>
-      <c r="E680" t="s">
-        <v>625</v>
-      </c>
-      <c r="F680" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A681" t="s">
-        <v>559</v>
-      </c>
-      <c r="B681" t="s">
-        <v>5</v>
-      </c>
-      <c r="C681" s="1">
-        <v>46135</v>
-      </c>
-      <c r="D681" t="s">
-        <v>357</v>
-      </c>
-      <c r="E681" t="s">
-        <v>627</v>
-      </c>
-      <c r="F681" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A682" t="s">
-        <v>629</v>
-      </c>
-      <c r="B682" t="s">
-        <v>13</v>
-      </c>
-      <c r="C682" s="1">
-        <v>46126</v>
-      </c>
-      <c r="D682" t="s">
-        <v>353</v>
-      </c>
-      <c r="E682" t="s">
-        <v>630</v>
-      </c>
-      <c r="F682" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A683" t="s">
-        <v>632</v>
       </c>
       <c r="B683" t="s">
         <v>11</v>
       </c>
       <c r="C683" s="1">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="D683" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E683" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="F683" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>632</v>
+        <v>52</v>
       </c>
       <c r="B684" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C684" s="1">
         <v>46140</v>
       </c>
       <c r="D684" t="s">
+        <v>360</v>
+      </c>
+      <c r="E684" t="s">
+        <v>621</v>
+      </c>
+      <c r="F684" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>632</v>
+      </c>
+      <c r="B685" t="s">
+        <v>11</v>
+      </c>
+      <c r="C685" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D685" t="s">
+        <v>378</v>
+      </c>
+      <c r="E685" t="s">
+        <v>633</v>
+      </c>
+      <c r="F685" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>632</v>
+      </c>
+      <c r="B686" t="s">
+        <v>11</v>
+      </c>
+      <c r="C686" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D686" t="s">
         <v>390</v>
       </c>
-      <c r="E684" t="s">
+      <c r="E686" t="s">
         <v>635</v>
       </c>
-      <c r="F684" t="s">
+      <c r="F686" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A685" t="s">
-        <v>637</v>
-      </c>
-      <c r="B685" t="s">
+    <row r="687" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>644</v>
+      </c>
+      <c r="B687" t="s">
+        <v>645</v>
+      </c>
+      <c r="C687" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D687" t="s">
+        <v>362</v>
+      </c>
+      <c r="E687" t="s">
+        <v>646</v>
+      </c>
+      <c r="F687" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A688" t="s">
+        <v>70</v>
+      </c>
+      <c r="B688" t="s">
+        <v>54</v>
+      </c>
+      <c r="C688" s="1">
+        <v>46151</v>
+      </c>
+      <c r="D688" t="s">
+        <v>353</v>
+      </c>
+      <c r="E688" t="s">
+        <v>642</v>
+      </c>
+      <c r="F688" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>427</v>
+      </c>
+      <c r="B689" t="s">
+        <v>19</v>
+      </c>
+      <c r="C689" s="1">
+        <v>46153</v>
+      </c>
+      <c r="D689" t="s">
+        <v>357</v>
+      </c>
+      <c r="E689" t="s">
+        <v>655</v>
+      </c>
+      <c r="F689" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>673</v>
+      </c>
+      <c r="B690" t="s">
+        <v>19</v>
+      </c>
+      <c r="C690" s="1">
+        <v>46153</v>
+      </c>
+      <c r="D690" t="s">
+        <v>357</v>
+      </c>
+      <c r="E690" t="s">
+        <v>674</v>
+      </c>
+      <c r="F690" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A691" t="s">
+        <v>679</v>
+      </c>
+      <c r="B691" t="s">
+        <v>645</v>
+      </c>
+      <c r="C691" s="1">
+        <v>46156</v>
+      </c>
+      <c r="D691" t="s">
+        <v>387</v>
+      </c>
+      <c r="E691" t="s">
+        <v>680</v>
+      </c>
+      <c r="F691" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A692" t="s">
+        <v>696</v>
+      </c>
+      <c r="B692" t="s">
         <v>13</v>
       </c>
-      <c r="C685" s="1">
-        <v>46126</v>
-      </c>
-      <c r="D685" t="s">
-        <v>357</v>
-      </c>
-      <c r="E685" t="s">
-        <v>638</v>
-      </c>
-      <c r="F685" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A686" t="s">
-        <v>305</v>
-      </c>
-      <c r="B686" t="s">
-        <v>8</v>
-      </c>
-      <c r="C686" s="1">
-        <v>46114</v>
-      </c>
-      <c r="D686" t="s">
-        <v>357</v>
-      </c>
-      <c r="E686" t="s">
-        <v>640</v>
-      </c>
-      <c r="F686" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A687" t="s">
-        <v>70</v>
-      </c>
-      <c r="B687" t="s">
-        <v>54</v>
-      </c>
-      <c r="C687" s="1">
-        <v>46151</v>
-      </c>
-      <c r="D687" t="s">
+      <c r="C692" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D692" t="s">
+        <v>355</v>
+      </c>
+      <c r="E692" t="s">
+        <v>697</v>
+      </c>
+      <c r="F692" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>667</v>
+      </c>
+      <c r="B693" t="s">
+        <v>5</v>
+      </c>
+      <c r="C693" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D693" t="s">
+        <v>390</v>
+      </c>
+      <c r="E693" t="s">
+        <v>668</v>
+      </c>
+      <c r="F693" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A694" t="s">
+        <v>676</v>
+      </c>
+      <c r="B694" t="s">
+        <v>13</v>
+      </c>
+      <c r="C694" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D694" t="s">
         <v>353</v>
       </c>
-      <c r="E687" t="s">
-        <v>642</v>
-      </c>
-      <c r="F687" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A688" t="s">
-        <v>644</v>
-      </c>
-      <c r="B688" t="s">
-        <v>645</v>
-      </c>
-      <c r="C688" s="1">
-        <v>46150</v>
-      </c>
-      <c r="D688" t="s">
+      <c r="E694" t="s">
+        <v>677</v>
+      </c>
+      <c r="F694" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>82</v>
+      </c>
+      <c r="B695" t="s">
+        <v>13</v>
+      </c>
+      <c r="C695" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D695" t="s">
+        <v>360</v>
+      </c>
+      <c r="E695" t="s">
+        <v>694</v>
+      </c>
+      <c r="F695" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A696" t="s">
+        <v>118</v>
+      </c>
+      <c r="B696" t="s">
+        <v>11</v>
+      </c>
+      <c r="C696" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D696" t="s">
+        <v>353</v>
+      </c>
+      <c r="E696" t="s">
+        <v>682</v>
+      </c>
+      <c r="F696" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A697" t="s">
+        <v>63</v>
+      </c>
+      <c r="B697" t="s">
+        <v>11</v>
+      </c>
+      <c r="C697" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D697" t="s">
         <v>362</v>
       </c>
-      <c r="E688" t="s">
-        <v>646</v>
-      </c>
-      <c r="F688" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A689" t="s">
-        <v>63</v>
-      </c>
-      <c r="B689" t="s">
+      <c r="E697" t="s">
+        <v>648</v>
+      </c>
+      <c r="F697" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A698" t="s">
+        <v>652</v>
+      </c>
+      <c r="B698" t="s">
         <v>11</v>
-      </c>
-      <c r="C689" s="1">
-        <v>46163</v>
-      </c>
-      <c r="D689" t="s">
-        <v>362</v>
-      </c>
-      <c r="E689" t="s">
-        <v>648</v>
-      </c>
-      <c r="F689" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A690" t="s">
-        <v>221</v>
-      </c>
-      <c r="B690" t="s">
-        <v>192</v>
-      </c>
-      <c r="C690" s="1">
-        <v>46171</v>
-      </c>
-      <c r="D690" t="s">
-        <v>368</v>
-      </c>
-      <c r="E690" t="s">
-        <v>650</v>
-      </c>
-      <c r="F690" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A691" t="s">
-        <v>652</v>
-      </c>
-      <c r="B691" t="s">
-        <v>11</v>
-      </c>
-      <c r="C691" s="1">
-        <v>46163</v>
-      </c>
-      <c r="D691" t="s">
-        <v>362</v>
-      </c>
-      <c r="E691" t="s">
-        <v>653</v>
-      </c>
-      <c r="F691" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A692" t="s">
-        <v>427</v>
-      </c>
-      <c r="B692" t="s">
-        <v>19</v>
-      </c>
-      <c r="C692" s="1">
-        <v>46153</v>
-      </c>
-      <c r="D692" t="s">
-        <v>357</v>
-      </c>
-      <c r="E692" t="s">
-        <v>655</v>
-      </c>
-      <c r="F692" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A693" t="s">
-        <v>98</v>
-      </c>
-      <c r="B693" t="s">
-        <v>19</v>
-      </c>
-      <c r="C693" s="1">
-        <v>46171</v>
-      </c>
-      <c r="D693" t="s">
-        <v>357</v>
-      </c>
-      <c r="E693" t="s">
-        <v>657</v>
-      </c>
-      <c r="F693" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A694" t="s">
-        <v>16</v>
-      </c>
-      <c r="B694" t="s">
-        <v>8</v>
-      </c>
-      <c r="C694" s="1">
-        <v>46172</v>
-      </c>
-      <c r="D694" t="s">
-        <v>659</v>
-      </c>
-      <c r="E694" t="s">
-        <v>660</v>
-      </c>
-      <c r="F694" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A695" t="s">
-        <v>103</v>
-      </c>
-      <c r="B695" t="s">
-        <v>19</v>
-      </c>
-      <c r="C695" s="1">
-        <v>46172</v>
-      </c>
-      <c r="D695" t="s">
-        <v>355</v>
-      </c>
-      <c r="E695" t="s">
-        <v>662</v>
-      </c>
-      <c r="F695" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A696" t="s">
-        <v>664</v>
-      </c>
-      <c r="B696" t="s">
-        <v>192</v>
-      </c>
-      <c r="C696" s="1">
-        <v>46164</v>
-      </c>
-      <c r="D696" t="s">
-        <v>362</v>
-      </c>
-      <c r="E696" t="s">
-        <v>665</v>
-      </c>
-      <c r="F696" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A697" t="s">
-        <v>667</v>
-      </c>
-      <c r="B697" t="s">
-        <v>5</v>
-      </c>
-      <c r="C697" s="1">
-        <v>46161</v>
-      </c>
-      <c r="D697" t="s">
-        <v>390</v>
-      </c>
-      <c r="E697" t="s">
-        <v>668</v>
-      </c>
-      <c r="F697" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A698" t="s">
-        <v>144</v>
-      </c>
-      <c r="B698" t="s">
-        <v>15</v>
       </c>
       <c r="C698" s="1">
         <v>46163</v>
       </c>
       <c r="D698" t="s">
+        <v>362</v>
+      </c>
+      <c r="E698" t="s">
+        <v>653</v>
+      </c>
+      <c r="F698" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>144</v>
+      </c>
+      <c r="B699" t="s">
+        <v>15</v>
+      </c>
+      <c r="C699" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D699" t="s">
         <v>670</v>
       </c>
-      <c r="E698" t="s">
+      <c r="E699" t="s">
         <v>671</v>
       </c>
-      <c r="F698" t="s">
+      <c r="F699" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A699" t="s">
-        <v>673</v>
-      </c>
-      <c r="B699" t="s">
-        <v>19</v>
-      </c>
-      <c r="C699" s="1">
-        <v>46153</v>
-      </c>
-      <c r="D699" t="s">
-        <v>357</v>
-      </c>
-      <c r="E699" t="s">
-        <v>674</v>
-      </c>
-      <c r="F699" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="B700" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C700" s="1">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="D700" t="s">
-        <v>353</v>
+        <v>685</v>
       </c>
       <c r="E700" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="F700" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="B701" t="s">
-        <v>645</v>
+        <v>54</v>
       </c>
       <c r="C701" s="1">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="D701" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E701" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="F701" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>118</v>
+        <v>691</v>
       </c>
       <c r="B702" t="s">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="C702" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D702" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="E702" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="F702" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>684</v>
+        <v>664</v>
       </c>
       <c r="B703" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="C703" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D703" t="s">
-        <v>685</v>
+        <v>362</v>
       </c>
       <c r="E703" t="s">
-        <v>686</v>
+        <v>665</v>
       </c>
       <c r="F703" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B704" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="C704" s="1">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="D704" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="E704" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F704" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>688</v>
+        <v>221</v>
       </c>
       <c r="B705" t="s">
         <v>192</v>
       </c>
       <c r="C705" s="1">
-        <v>46167</v>
+        <v>46171</v>
       </c>
       <c r="D705" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E705" t="s">
-        <v>689</v>
+        <v>650</v>
       </c>
       <c r="F705" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>691</v>
+        <v>98</v>
       </c>
       <c r="B706" t="s">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="C706" s="1">
-        <v>46163</v>
+        <v>46171</v>
       </c>
       <c r="D706" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="E706" t="s">
-        <v>692</v>
+        <v>657</v>
       </c>
       <c r="F706" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="B707" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C707" s="1">
-        <v>46161</v>
+        <v>46172</v>
       </c>
       <c r="D707" t="s">
-        <v>360</v>
+        <v>659</v>
       </c>
       <c r="E707" t="s">
-        <v>694</v>
+        <v>660</v>
       </c>
       <c r="F707" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>696</v>
+        <v>103</v>
       </c>
       <c r="B708" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C708" s="1">
-        <v>46157</v>
+        <v>46172</v>
       </c>
       <c r="D708" t="s">
         <v>355</v>
       </c>
       <c r="E708" t="s">
+        <v>662</v>
+      </c>
+      <c r="F708" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A709" t="s">
+        <v>70</v>
+      </c>
+      <c r="B709" t="s">
+        <v>54</v>
+      </c>
+      <c r="C709" s="1">
+        <v>46151</v>
+      </c>
+      <c r="D709" t="s">
+        <v>353</v>
+      </c>
+      <c r="E709" t="s">
+        <v>642</v>
+      </c>
+      <c r="F709" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A710" t="s">
+        <v>644</v>
+      </c>
+      <c r="B710" t="s">
+        <v>645</v>
+      </c>
+      <c r="C710" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D710" t="s">
+        <v>362</v>
+      </c>
+      <c r="E710" t="s">
+        <v>646</v>
+      </c>
+      <c r="F710" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>63</v>
+      </c>
+      <c r="B711" t="s">
+        <v>11</v>
+      </c>
+      <c r="C711" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D711" t="s">
+        <v>362</v>
+      </c>
+      <c r="E711" t="s">
+        <v>648</v>
+      </c>
+      <c r="F711" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A712" t="s">
+        <v>63</v>
+      </c>
+      <c r="B712" t="s">
+        <v>11</v>
+      </c>
+      <c r="C712" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D712" t="s">
+        <v>353</v>
+      </c>
+      <c r="E712" t="s">
+        <v>699</v>
+      </c>
+      <c r="F712" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>221</v>
+      </c>
+      <c r="B713" t="s">
+        <v>192</v>
+      </c>
+      <c r="C713" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D713" t="s">
+        <v>368</v>
+      </c>
+      <c r="E713" t="s">
+        <v>650</v>
+      </c>
+      <c r="F713" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A714" t="s">
+        <v>701</v>
+      </c>
+      <c r="B714" t="s">
+        <v>11</v>
+      </c>
+      <c r="C714" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D714" t="s">
+        <v>362</v>
+      </c>
+      <c r="E714" t="s">
+        <v>340</v>
+      </c>
+      <c r="F714" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A715" t="s">
+        <v>427</v>
+      </c>
+      <c r="B715" t="s">
+        <v>19</v>
+      </c>
+      <c r="C715" s="1">
+        <v>46153</v>
+      </c>
+      <c r="D715" t="s">
+        <v>357</v>
+      </c>
+      <c r="E715" t="s">
+        <v>655</v>
+      </c>
+      <c r="F715" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A716" t="s">
+        <v>142</v>
+      </c>
+      <c r="B716" t="s">
+        <v>15</v>
+      </c>
+      <c r="C716" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D716" t="s">
+        <v>368</v>
+      </c>
+      <c r="E716" t="s">
+        <v>703</v>
+      </c>
+      <c r="F716" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A717" t="s">
+        <v>201</v>
+      </c>
+      <c r="B717" t="s">
+        <v>192</v>
+      </c>
+      <c r="C717" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D717" t="s">
+        <v>360</v>
+      </c>
+      <c r="E717" t="s">
+        <v>705</v>
+      </c>
+      <c r="F717" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A718" t="s">
+        <v>201</v>
+      </c>
+      <c r="B718" t="s">
+        <v>192</v>
+      </c>
+      <c r="C718" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D718" t="s">
+        <v>707</v>
+      </c>
+      <c r="E718" t="s">
+        <v>708</v>
+      </c>
+      <c r="F718" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A719" t="s">
+        <v>710</v>
+      </c>
+      <c r="B719" t="s">
+        <v>192</v>
+      </c>
+      <c r="C719" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D719" t="s">
+        <v>368</v>
+      </c>
+      <c r="E719" t="s">
+        <v>711</v>
+      </c>
+      <c r="F719" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A720" t="s">
+        <v>713</v>
+      </c>
+      <c r="B720" t="s">
+        <v>8</v>
+      </c>
+      <c r="C720" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D720" t="s">
+        <v>388</v>
+      </c>
+      <c r="E720" t="s">
+        <v>714</v>
+      </c>
+      <c r="F720" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A721" t="s">
+        <v>98</v>
+      </c>
+      <c r="B721" t="s">
+        <v>19</v>
+      </c>
+      <c r="C721" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D721" t="s">
+        <v>357</v>
+      </c>
+      <c r="E721" t="s">
+        <v>657</v>
+      </c>
+      <c r="F721" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A722" t="s">
+        <v>716</v>
+      </c>
+      <c r="B722" t="s">
+        <v>8</v>
+      </c>
+      <c r="C722" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D722" t="s">
+        <v>717</v>
+      </c>
+      <c r="E722" t="s">
+        <v>718</v>
+      </c>
+      <c r="F722" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A723" t="s">
+        <v>716</v>
+      </c>
+      <c r="B723" t="s">
+        <v>8</v>
+      </c>
+      <c r="C723" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D723" t="s">
+        <v>378</v>
+      </c>
+      <c r="E723" t="s">
+        <v>718</v>
+      </c>
+      <c r="F723" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A724" t="s">
+        <v>716</v>
+      </c>
+      <c r="B724" t="s">
+        <v>8</v>
+      </c>
+      <c r="C724" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D724" t="s">
+        <v>685</v>
+      </c>
+      <c r="E724" t="s">
+        <v>720</v>
+      </c>
+      <c r="F724" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A725" t="s">
+        <v>716</v>
+      </c>
+      <c r="B725" t="s">
+        <v>8</v>
+      </c>
+      <c r="C725" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D725" t="s">
+        <v>722</v>
+      </c>
+      <c r="E725" t="s">
+        <v>720</v>
+      </c>
+      <c r="F725" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A726" t="s">
+        <v>716</v>
+      </c>
+      <c r="B726" t="s">
+        <v>8</v>
+      </c>
+      <c r="C726" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D726" t="s">
+        <v>360</v>
+      </c>
+      <c r="E726" t="s">
+        <v>720</v>
+      </c>
+      <c r="F726" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A727" t="s">
+        <v>16</v>
+      </c>
+      <c r="B727" t="s">
+        <v>8</v>
+      </c>
+      <c r="C727" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D727" t="s">
+        <v>659</v>
+      </c>
+      <c r="E727" t="s">
+        <v>660</v>
+      </c>
+      <c r="F727" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A728" t="s">
+        <v>103</v>
+      </c>
+      <c r="B728" t="s">
+        <v>19</v>
+      </c>
+      <c r="C728" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D728" t="s">
+        <v>355</v>
+      </c>
+      <c r="E728" t="s">
+        <v>662</v>
+      </c>
+      <c r="F728" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A729" t="s">
+        <v>664</v>
+      </c>
+      <c r="B729" t="s">
+        <v>192</v>
+      </c>
+      <c r="C729" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D729" t="s">
+        <v>362</v>
+      </c>
+      <c r="E729" t="s">
+        <v>665</v>
+      </c>
+      <c r="F729" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A730" t="s">
+        <v>144</v>
+      </c>
+      <c r="B730" t="s">
+        <v>15</v>
+      </c>
+      <c r="C730" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D730" t="s">
+        <v>670</v>
+      </c>
+      <c r="E730" t="s">
+        <v>671</v>
+      </c>
+      <c r="F730" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>483</v>
+      </c>
+      <c r="B731" t="s">
+        <v>192</v>
+      </c>
+      <c r="C731" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D731" t="s">
+        <v>388</v>
+      </c>
+      <c r="E731" t="s">
+        <v>723</v>
+      </c>
+      <c r="F731" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A732" t="s">
+        <v>725</v>
+      </c>
+      <c r="B732" t="s">
+        <v>5</v>
+      </c>
+      <c r="C732" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D732" t="s">
+        <v>378</v>
+      </c>
+      <c r="E732" t="s">
+        <v>726</v>
+      </c>
+      <c r="F732" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A733" t="s">
+        <v>673</v>
+      </c>
+      <c r="B733" t="s">
+        <v>19</v>
+      </c>
+      <c r="C733" s="1">
+        <v>46153</v>
+      </c>
+      <c r="D733" t="s">
+        <v>357</v>
+      </c>
+      <c r="E733" t="s">
+        <v>674</v>
+      </c>
+      <c r="F733" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A734" t="s">
+        <v>75</v>
+      </c>
+      <c r="B734" t="s">
+        <v>19</v>
+      </c>
+      <c r="C734" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D734" t="s">
+        <v>360</v>
+      </c>
+      <c r="E734" t="s">
+        <v>728</v>
+      </c>
+      <c r="F734" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>676</v>
+      </c>
+      <c r="B735" t="s">
+        <v>13</v>
+      </c>
+      <c r="C735" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D735" t="s">
+        <v>353</v>
+      </c>
+      <c r="E735" t="s">
+        <v>677</v>
+      </c>
+      <c r="F735" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A736" t="s">
+        <v>383</v>
+      </c>
+      <c r="B736" t="s">
+        <v>192</v>
+      </c>
+      <c r="C736" s="1">
+        <v>46192</v>
+      </c>
+      <c r="D736" t="s">
+        <v>360</v>
+      </c>
+      <c r="E736" t="s">
+        <v>730</v>
+      </c>
+      <c r="F736" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>732</v>
+      </c>
+      <c r="B737" t="s">
+        <v>15</v>
+      </c>
+      <c r="C737" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D737" t="s">
+        <v>733</v>
+      </c>
+      <c r="E737" t="s">
+        <v>734</v>
+      </c>
+      <c r="F737" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A738" t="s">
+        <v>732</v>
+      </c>
+      <c r="B738" t="s">
+        <v>15</v>
+      </c>
+      <c r="C738" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D738" t="s">
+        <v>736</v>
+      </c>
+      <c r="E738" t="s">
+        <v>734</v>
+      </c>
+      <c r="F738" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A739" t="s">
+        <v>732</v>
+      </c>
+      <c r="B739" t="s">
+        <v>15</v>
+      </c>
+      <c r="C739" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D739" t="s">
+        <v>386</v>
+      </c>
+      <c r="E739" t="s">
+        <v>737</v>
+      </c>
+      <c r="F739" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A740" t="s">
+        <v>732</v>
+      </c>
+      <c r="B740" t="s">
+        <v>15</v>
+      </c>
+      <c r="C740" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D740" t="s">
+        <v>739</v>
+      </c>
+      <c r="E740" t="s">
+        <v>734</v>
+      </c>
+      <c r="F740" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A741" t="s">
+        <v>679</v>
+      </c>
+      <c r="B741" t="s">
+        <v>645</v>
+      </c>
+      <c r="C741" s="1">
+        <v>46156</v>
+      </c>
+      <c r="D741" t="s">
+        <v>387</v>
+      </c>
+      <c r="E741" t="s">
+        <v>680</v>
+      </c>
+      <c r="F741" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A742" t="s">
+        <v>133</v>
+      </c>
+      <c r="B742" t="s">
+        <v>13</v>
+      </c>
+      <c r="C742" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D742" t="s">
+        <v>733</v>
+      </c>
+      <c r="E742" t="s">
+        <v>740</v>
+      </c>
+      <c r="F742" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A743" t="s">
+        <v>133</v>
+      </c>
+      <c r="B743" t="s">
+        <v>13</v>
+      </c>
+      <c r="C743" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D743" t="s">
+        <v>736</v>
+      </c>
+      <c r="E743" t="s">
+        <v>740</v>
+      </c>
+      <c r="F743" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A744" t="s">
+        <v>133</v>
+      </c>
+      <c r="B744" t="s">
+        <v>13</v>
+      </c>
+      <c r="C744" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D744" t="s">
+        <v>739</v>
+      </c>
+      <c r="E744" t="s">
+        <v>740</v>
+      </c>
+      <c r="F744" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A745" t="s">
+        <v>742</v>
+      </c>
+      <c r="B745" t="s">
+        <v>15</v>
+      </c>
+      <c r="C745" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D745" t="s">
+        <v>386</v>
+      </c>
+      <c r="E745" t="s">
+        <v>743</v>
+      </c>
+      <c r="F745" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A746" t="s">
+        <v>359</v>
+      </c>
+      <c r="B746" t="s">
+        <v>13</v>
+      </c>
+      <c r="C746" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D746" t="s">
+        <v>353</v>
+      </c>
+      <c r="E746" t="s">
+        <v>745</v>
+      </c>
+      <c r="F746" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A747" t="s">
+        <v>118</v>
+      </c>
+      <c r="B747" t="s">
+        <v>11</v>
+      </c>
+      <c r="C747" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D747" t="s">
+        <v>353</v>
+      </c>
+      <c r="E747" t="s">
+        <v>682</v>
+      </c>
+      <c r="F747" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A748" t="s">
+        <v>684</v>
+      </c>
+      <c r="B748" t="s">
+        <v>54</v>
+      </c>
+      <c r="C748" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D748" t="s">
+        <v>685</v>
+      </c>
+      <c r="E748" t="s">
+        <v>686</v>
+      </c>
+      <c r="F748" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>684</v>
+      </c>
+      <c r="B749" t="s">
+        <v>54</v>
+      </c>
+      <c r="C749" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D749" t="s">
+        <v>388</v>
+      </c>
+      <c r="E749" t="s">
+        <v>686</v>
+      </c>
+      <c r="F749" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A750" t="s">
+        <v>688</v>
+      </c>
+      <c r="B750" t="s">
+        <v>192</v>
+      </c>
+      <c r="C750" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D750" t="s">
+        <v>362</v>
+      </c>
+      <c r="E750" t="s">
+        <v>689</v>
+      </c>
+      <c r="F750" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A751" t="s">
+        <v>747</v>
+      </c>
+      <c r="B751" t="s">
+        <v>54</v>
+      </c>
+      <c r="C751" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D751" t="s">
+        <v>357</v>
+      </c>
+      <c r="E751" t="s">
+        <v>748</v>
+      </c>
+      <c r="F751" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A752" t="s">
+        <v>247</v>
+      </c>
+      <c r="B752" t="s">
+        <v>192</v>
+      </c>
+      <c r="C752" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D752" t="s">
+        <v>355</v>
+      </c>
+      <c r="E752" t="s">
+        <v>750</v>
+      </c>
+      <c r="F752" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>691</v>
+      </c>
+      <c r="B753" t="s">
+        <v>192</v>
+      </c>
+      <c r="C753" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D753" t="s">
+        <v>378</v>
+      </c>
+      <c r="E753" t="s">
+        <v>692</v>
+      </c>
+      <c r="F753" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A754" t="s">
+        <v>751</v>
+      </c>
+      <c r="B754" t="s">
+        <v>192</v>
+      </c>
+      <c r="C754" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D754" t="s">
+        <v>362</v>
+      </c>
+      <c r="E754" t="s">
+        <v>752</v>
+      </c>
+      <c r="F754" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>560</v>
+      </c>
+      <c r="B755" t="s">
+        <v>19</v>
+      </c>
+      <c r="C755" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D755" t="s">
+        <v>754</v>
+      </c>
+      <c r="E755" t="s">
+        <v>755</v>
+      </c>
+      <c r="F755" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A756" t="s">
+        <v>560</v>
+      </c>
+      <c r="B756" t="s">
+        <v>19</v>
+      </c>
+      <c r="C756" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D756" t="s">
+        <v>757</v>
+      </c>
+      <c r="E756" t="s">
+        <v>755</v>
+      </c>
+      <c r="F756" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A757" t="s">
+        <v>560</v>
+      </c>
+      <c r="B757" t="s">
+        <v>19</v>
+      </c>
+      <c r="C757" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D757" t="s">
+        <v>388</v>
+      </c>
+      <c r="E757" t="s">
+        <v>755</v>
+      </c>
+      <c r="F757" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A758" t="s">
+        <v>82</v>
+      </c>
+      <c r="B758" t="s">
+        <v>13</v>
+      </c>
+      <c r="C758" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D758" t="s">
+        <v>360</v>
+      </c>
+      <c r="E758" t="s">
+        <v>694</v>
+      </c>
+      <c r="F758" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A759" t="s">
+        <v>696</v>
+      </c>
+      <c r="B759" t="s">
+        <v>13</v>
+      </c>
+      <c r="C759" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D759" t="s">
+        <v>355</v>
+      </c>
+      <c r="E759" t="s">
         <v>697</v>
       </c>
-      <c r="F708" t="s">
+      <c r="F759" t="s">
         <v>698</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A760" t="s">
+        <v>758</v>
+      </c>
+      <c r="B760" t="s">
+        <v>759</v>
+      </c>
+      <c r="C760" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D760" t="s">
+        <v>357</v>
+      </c>
+      <c r="E760" t="s">
+        <v>760</v>
+      </c>
+      <c r="F760" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A761" t="s">
+        <v>762</v>
+      </c>
+      <c r="B761" t="s">
+        <v>763</v>
+      </c>
+      <c r="C761" s="1">
+        <v>46185</v>
+      </c>
+      <c r="D761" t="s">
+        <v>357</v>
+      </c>
+      <c r="E761" t="s">
+        <v>764</v>
+      </c>
+      <c r="F761" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A762" t="s">
+        <v>637</v>
+      </c>
+      <c r="B762" t="s">
+        <v>13</v>
+      </c>
+      <c r="C762" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D762" t="s">
+        <v>353</v>
+      </c>
+      <c r="E762" t="s">
+        <v>766</v>
+      </c>
+      <c r="F762" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A763" t="s">
+        <v>93</v>
+      </c>
+      <c r="B763" t="s">
+        <v>54</v>
+      </c>
+      <c r="C763" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D763" t="s">
+        <v>353</v>
+      </c>
+      <c r="E763" t="s">
+        <v>768</v>
+      </c>
+      <c r="F763" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A764" t="s">
+        <v>770</v>
+      </c>
+      <c r="B764" t="s">
+        <v>645</v>
+      </c>
+      <c r="C764" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D764" t="s">
+        <v>771</v>
+      </c>
+      <c r="E764" t="s">
+        <v>772</v>
+      </c>
+      <c r="F764" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="765" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A765" t="s">
+        <v>770</v>
+      </c>
+      <c r="B765" t="s">
+        <v>645</v>
+      </c>
+      <c r="C765" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D765" t="s">
+        <v>774</v>
+      </c>
+      <c r="E765" t="s">
+        <v>772</v>
+      </c>
+      <c r="F765" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="766" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A766" t="s">
+        <v>770</v>
+      </c>
+      <c r="B766" t="s">
+        <v>645</v>
+      </c>
+      <c r="C766" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D766" t="s">
+        <v>775</v>
+      </c>
+      <c r="E766" t="s">
+        <v>772</v>
+      </c>
+      <c r="F766" t="s">
+        <v>773</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D576" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D576">
-    <sortCondition ref="C2:C576"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F708">
+    <sortCondition ref="C2:C708"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Desvios de DTOs.xlsx
+++ b/data/Desvios de DTOs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8918ED41-23C3-49B9-AB5D-B0534A130D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6574ABF0-851D-43E3-8A78-D1B571742447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$576</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$766</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -14593,7 +14593,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D576" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F708">
     <sortCondition ref="C2:C708"/>
   </sortState>

--- a/data/Desvios de DTOs.xlsx
+++ b/data/Desvios de DTOs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6574ABF0-851D-43E3-8A78-D1B571742447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FB1613-B75F-42E1-A972-F0D08972B5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66944995-7197-43F3-8900-2D516179B6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$766</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2373,13 +2373,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2399,15 +2403,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{38FC0AE9-FBA6-4E15-95C5-0B6D49AE0ABE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -13014,482 +13022,482 @@
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>70</v>
+        <v>644</v>
       </c>
       <c r="B688" t="s">
-        <v>54</v>
+        <v>645</v>
       </c>
       <c r="C688" s="1">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="D688" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="E688" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="F688" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>427</v>
+        <v>70</v>
       </c>
       <c r="B689" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C689" s="1">
-        <v>46153</v>
+        <v>46151</v>
       </c>
       <c r="D689" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E689" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="F689" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>673</v>
+        <v>70</v>
       </c>
       <c r="B690" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C690" s="1">
-        <v>46153</v>
+        <v>46151</v>
       </c>
       <c r="D690" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E690" t="s">
-        <v>674</v>
+        <v>642</v>
       </c>
       <c r="F690" t="s">
-        <v>675</v>
+        <v>643</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>679</v>
+        <v>427</v>
       </c>
       <c r="B691" t="s">
-        <v>645</v>
+        <v>19</v>
       </c>
       <c r="C691" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="D691" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="E691" t="s">
-        <v>680</v>
+        <v>655</v>
       </c>
       <c r="F691" t="s">
-        <v>681</v>
+        <v>656</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="B692" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C692" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="D692" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E692" t="s">
-        <v>697</v>
+        <v>674</v>
       </c>
       <c r="F692" t="s">
-        <v>698</v>
+        <v>675</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>667</v>
+        <v>427</v>
       </c>
       <c r="B693" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C693" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="D693" t="s">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="E693" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="F693" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B694" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C694" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="D694" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E694" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F694" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>82</v>
+        <v>679</v>
       </c>
       <c r="B695" t="s">
-        <v>13</v>
+        <v>645</v>
       </c>
       <c r="C695" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="D695" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="E695" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="F695" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>118</v>
+        <v>679</v>
       </c>
       <c r="B696" t="s">
-        <v>11</v>
+        <v>645</v>
       </c>
       <c r="C696" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="D696" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="E696" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F696" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>63</v>
+        <v>696</v>
       </c>
       <c r="B697" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C697" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="D697" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E697" t="s">
-        <v>648</v>
+        <v>697</v>
       </c>
       <c r="F697" t="s">
-        <v>649</v>
+        <v>698</v>
       </c>
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>652</v>
+        <v>696</v>
       </c>
       <c r="B698" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C698" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="D698" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E698" t="s">
-        <v>653</v>
+        <v>697</v>
       </c>
       <c r="F698" t="s">
-        <v>654</v>
+        <v>698</v>
       </c>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>144</v>
+        <v>667</v>
       </c>
       <c r="B699" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C699" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="D699" t="s">
-        <v>670</v>
+        <v>390</v>
       </c>
       <c r="E699" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F699" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="B700" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C700" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="D700" t="s">
-        <v>685</v>
+        <v>353</v>
       </c>
       <c r="E700" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="F700" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>684</v>
+        <v>82</v>
       </c>
       <c r="B701" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C701" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="D701" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="E701" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="F701" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>691</v>
+        <v>676</v>
       </c>
       <c r="B702" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="C702" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="D702" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="E702" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="F702" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>664</v>
+        <v>82</v>
       </c>
       <c r="B703" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="C703" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="D703" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E703" t="s">
-        <v>665</v>
+        <v>694</v>
       </c>
       <c r="F703" t="s">
-        <v>666</v>
+        <v>695</v>
       </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>688</v>
+        <v>118</v>
       </c>
       <c r="B704" t="s">
-        <v>192</v>
+        <v>11</v>
       </c>
       <c r="C704" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="D704" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="E704" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="F704" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
       <c r="B705" t="s">
-        <v>192</v>
+        <v>11</v>
       </c>
       <c r="C705" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="D705" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="E705" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="F705" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="B706" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C706" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="D706" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E706" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="F706" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>16</v>
+        <v>652</v>
       </c>
       <c r="B707" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C707" s="1">
-        <v>46172</v>
+        <v>46163</v>
       </c>
       <c r="D707" t="s">
-        <v>659</v>
+        <v>362</v>
       </c>
       <c r="E707" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="F707" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="B708" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C708" s="1">
-        <v>46172</v>
+        <v>46163</v>
       </c>
       <c r="D708" t="s">
-        <v>355</v>
+        <v>670</v>
       </c>
       <c r="E708" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="F708" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>70</v>
+        <v>684</v>
       </c>
       <c r="B709" t="s">
         <v>54</v>
       </c>
       <c r="C709" s="1">
-        <v>46151</v>
+        <v>46163</v>
       </c>
       <c r="D709" t="s">
-        <v>353</v>
+        <v>685</v>
       </c>
       <c r="E709" t="s">
-        <v>642</v>
+        <v>686</v>
       </c>
       <c r="F709" t="s">
-        <v>643</v>
+        <v>687</v>
       </c>
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="B710" t="s">
-        <v>645</v>
+        <v>54</v>
       </c>
       <c r="C710" s="1">
-        <v>46150</v>
+        <v>46163</v>
       </c>
       <c r="D710" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="E710" t="s">
-        <v>646</v>
+        <v>686</v>
       </c>
       <c r="F710" t="s">
-        <v>647</v>
+        <v>687</v>
       </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>63</v>
+        <v>691</v>
       </c>
       <c r="B711" t="s">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="C711" s="1">
         <v>46163</v>
       </c>
       <c r="D711" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="E711" t="s">
-        <v>648</v>
+        <v>692</v>
       </c>
       <c r="F711" t="s">
-        <v>649</v>
+        <v>693</v>
       </c>
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.3">
@@ -13500,296 +13508,296 @@
         <v>11</v>
       </c>
       <c r="C712" s="1">
-        <v>46195</v>
+        <v>46163</v>
       </c>
       <c r="D712" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="E712" t="s">
-        <v>699</v>
+        <v>648</v>
       </c>
       <c r="F712" t="s">
-        <v>700</v>
+        <v>649</v>
       </c>
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>221</v>
+        <v>144</v>
       </c>
       <c r="B713" t="s">
-        <v>192</v>
+        <v>15</v>
       </c>
       <c r="C713" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="D713" t="s">
-        <v>368</v>
+        <v>670</v>
       </c>
       <c r="E713" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="F713" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
       <c r="B714" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C714" s="1">
-        <v>46197</v>
+        <v>46163</v>
       </c>
       <c r="D714" t="s">
-        <v>362</v>
+        <v>685</v>
       </c>
       <c r="E714" t="s">
-        <v>340</v>
+        <v>686</v>
       </c>
       <c r="F714" t="s">
-        <v>702</v>
+        <v>687</v>
       </c>
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>427</v>
+        <v>684</v>
       </c>
       <c r="B715" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C715" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="D715" t="s">
-        <v>357</v>
+        <v>388</v>
       </c>
       <c r="E715" t="s">
-        <v>655</v>
+        <v>686</v>
       </c>
       <c r="F715" t="s">
-        <v>656</v>
+        <v>687</v>
       </c>
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>142</v>
+        <v>691</v>
       </c>
       <c r="B716" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="C716" s="1">
-        <v>46183</v>
+        <v>46163</v>
       </c>
       <c r="D716" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="E716" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="F716" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>201</v>
+        <v>664</v>
       </c>
       <c r="B717" t="s">
         <v>192</v>
       </c>
       <c r="C717" s="1">
-        <v>46195</v>
+        <v>46164</v>
       </c>
       <c r="D717" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E717" t="s">
-        <v>705</v>
+        <v>665</v>
       </c>
       <c r="F717" t="s">
-        <v>706</v>
+        <v>666</v>
       </c>
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>201</v>
+        <v>664</v>
       </c>
       <c r="B718" t="s">
         <v>192</v>
       </c>
       <c r="C718" s="1">
-        <v>46198</v>
+        <v>46164</v>
       </c>
       <c r="D718" t="s">
-        <v>707</v>
+        <v>362</v>
       </c>
       <c r="E718" t="s">
-        <v>708</v>
+        <v>665</v>
       </c>
       <c r="F718" t="s">
-        <v>709</v>
+        <v>666</v>
       </c>
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>710</v>
+        <v>688</v>
       </c>
       <c r="B719" t="s">
         <v>192</v>
       </c>
       <c r="C719" s="1">
-        <v>46184</v>
+        <v>46167</v>
       </c>
       <c r="D719" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E719" t="s">
-        <v>711</v>
+        <v>689</v>
       </c>
       <c r="F719" t="s">
-        <v>712</v>
+        <v>690</v>
       </c>
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>713</v>
+        <v>688</v>
       </c>
       <c r="B720" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="C720" s="1">
-        <v>46200</v>
+        <v>46167</v>
       </c>
       <c r="D720" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="E720" t="s">
-        <v>714</v>
+        <v>689</v>
       </c>
       <c r="F720" t="s">
-        <v>715</v>
+        <v>690</v>
       </c>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>98</v>
+        <v>221</v>
       </c>
       <c r="B721" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="C721" s="1">
         <v>46171</v>
       </c>
       <c r="D721" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E721" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="F721" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>716</v>
+        <v>98</v>
       </c>
       <c r="B722" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C722" s="1">
-        <v>46196</v>
+        <v>46171</v>
       </c>
       <c r="D722" t="s">
-        <v>717</v>
+        <v>357</v>
       </c>
       <c r="E722" t="s">
-        <v>718</v>
+        <v>657</v>
       </c>
       <c r="F722" t="s">
-        <v>719</v>
+        <v>658</v>
       </c>
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>716</v>
+        <v>221</v>
       </c>
       <c r="B723" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="C723" s="1">
-        <v>46196</v>
+        <v>46171</v>
       </c>
       <c r="D723" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E723" t="s">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="F723" t="s">
-        <v>719</v>
+        <v>651</v>
       </c>
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>716</v>
+        <v>98</v>
       </c>
       <c r="B724" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C724" s="1">
-        <v>46197</v>
+        <v>46171</v>
       </c>
       <c r="D724" t="s">
-        <v>685</v>
+        <v>357</v>
       </c>
       <c r="E724" t="s">
-        <v>720</v>
+        <v>657</v>
       </c>
       <c r="F724" t="s">
-        <v>721</v>
+        <v>658</v>
       </c>
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>716</v>
+        <v>16</v>
       </c>
       <c r="B725" t="s">
         <v>8</v>
       </c>
       <c r="C725" s="1">
-        <v>46197</v>
+        <v>46172</v>
       </c>
       <c r="D725" t="s">
-        <v>722</v>
+        <v>659</v>
       </c>
       <c r="E725" t="s">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="F725" t="s">
-        <v>721</v>
+        <v>661</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>716</v>
+        <v>103</v>
       </c>
       <c r="B726" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C726" s="1">
-        <v>46197</v>
+        <v>46172</v>
       </c>
       <c r="D726" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E726" t="s">
-        <v>720</v>
+        <v>662</v>
       </c>
       <c r="F726" t="s">
-        <v>721</v>
+        <v>663</v>
       </c>
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.3">
@@ -13833,766 +13841,771 @@
       </c>
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A729" t="s">
-        <v>664</v>
-      </c>
-      <c r="B729" t="s">
+      <c r="A729" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C729" s="3">
+        <v>46195</v>
+      </c>
+      <c r="D729" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E729" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="F729" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A730" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C730" s="3">
+        <v>46197</v>
+      </c>
+      <c r="D730" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E730" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F730" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A731" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C731" s="3">
+        <v>46183</v>
+      </c>
+      <c r="D731" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E731" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="F731" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A732" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B732" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C729" s="1">
-        <v>46164</v>
-      </c>
-      <c r="D729" t="s">
+      <c r="C732" s="3">
+        <v>46195</v>
+      </c>
+      <c r="D732" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E732" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F732" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A733" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C733" s="3">
+        <v>46198</v>
+      </c>
+      <c r="D733" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E733" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F733" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A734" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C734" s="3">
+        <v>46184</v>
+      </c>
+      <c r="D734" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E734" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="F734" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A735" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C735" s="3">
+        <v>46200</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E735" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="F735" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A736" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C736" s="3">
+        <v>46196</v>
+      </c>
+      <c r="D736" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E736" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="F736" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A737" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C737" s="3">
+        <v>46196</v>
+      </c>
+      <c r="D737" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E737" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="F737" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A738" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C738" s="3">
+        <v>46197</v>
+      </c>
+      <c r="D738" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="E738" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F738" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A739" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C739" s="3">
+        <v>46197</v>
+      </c>
+      <c r="D739" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="E739" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F739" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A740" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C740" s="3">
+        <v>46197</v>
+      </c>
+      <c r="D740" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E740" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F740" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A741" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C741" s="3">
+        <v>46184</v>
+      </c>
+      <c r="D741" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E741" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F741" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A742" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C742" s="3">
+        <v>46174</v>
+      </c>
+      <c r="D742" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E742" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="F742" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A743" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C743" s="3">
+        <v>46189</v>
+      </c>
+      <c r="D743" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E743" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="F743" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A744" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C744" s="3">
+        <v>46192</v>
+      </c>
+      <c r="D744" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E744" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="F744" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A745" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C745" s="3">
+        <v>46184</v>
+      </c>
+      <c r="D745" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="E745" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="F745" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A746" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C746" s="3">
+        <v>46184</v>
+      </c>
+      <c r="D746" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E746" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="F746" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A747" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C747" s="3">
+        <v>46184</v>
+      </c>
+      <c r="D747" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E747" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="F747" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A748" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C748" s="3">
+        <v>46184</v>
+      </c>
+      <c r="D748" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="E748" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="F748" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A749" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C749" s="3">
+        <v>46190</v>
+      </c>
+      <c r="D749" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="E749" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F749" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A750" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C750" s="3">
+        <v>46190</v>
+      </c>
+      <c r="D750" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E750" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F750" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A751" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C751" s="3">
+        <v>46190</v>
+      </c>
+      <c r="D751" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="E751" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F751" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A752" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C752" s="3">
+        <v>46183</v>
+      </c>
+      <c r="D752" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E752" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="F752" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A753" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C753" s="3">
+        <v>46199</v>
+      </c>
+      <c r="D753" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E753" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="F753" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A754" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C754" s="3">
+        <v>46193</v>
+      </c>
+      <c r="D754" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E754" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="F754" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A755" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C755" s="3">
+        <v>46198</v>
+      </c>
+      <c r="D755" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E755" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="F755" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A756" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C756" s="3">
+        <v>46199</v>
+      </c>
+      <c r="D756" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="E729" t="s">
-        <v>665</v>
-      </c>
-      <c r="F729" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A730" t="s">
-        <v>144</v>
-      </c>
-      <c r="B730" t="s">
-        <v>15</v>
-      </c>
-      <c r="C730" s="1">
-        <v>46163</v>
-      </c>
-      <c r="D730" t="s">
-        <v>670</v>
-      </c>
-      <c r="E730" t="s">
-        <v>671</v>
-      </c>
-      <c r="F730" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A731" t="s">
-        <v>483</v>
-      </c>
-      <c r="B731" t="s">
-        <v>192</v>
-      </c>
-      <c r="C731" s="1">
-        <v>46184</v>
-      </c>
-      <c r="D731" t="s">
+      <c r="E756" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="F756" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A757" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C757" s="3">
+        <v>46199</v>
+      </c>
+      <c r="D757" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="E757" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="F757" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A758" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C758" s="3">
+        <v>46199</v>
+      </c>
+      <c r="D758" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="E758" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="F758" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A759" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C759" s="3">
+        <v>46199</v>
+      </c>
+      <c r="D759" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="E731" t="s">
-        <v>723</v>
-      </c>
-      <c r="F731" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A732" t="s">
-        <v>725</v>
-      </c>
-      <c r="B732" t="s">
-        <v>5</v>
-      </c>
-      <c r="C732" s="1">
-        <v>46174</v>
-      </c>
-      <c r="D732" t="s">
-        <v>378</v>
-      </c>
-      <c r="E732" t="s">
-        <v>726</v>
-      </c>
-      <c r="F732" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A733" t="s">
-        <v>673</v>
-      </c>
-      <c r="B733" t="s">
-        <v>19</v>
-      </c>
-      <c r="C733" s="1">
-        <v>46153</v>
-      </c>
-      <c r="D733" t="s">
+      <c r="E759" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="F759" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A760" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C760" s="3">
+        <v>46183</v>
+      </c>
+      <c r="D760" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="E733" t="s">
-        <v>674</v>
-      </c>
-      <c r="F733" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A734" t="s">
-        <v>75</v>
-      </c>
-      <c r="B734" t="s">
-        <v>19</v>
-      </c>
-      <c r="C734" s="1">
+      <c r="E760" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="F760" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A761" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C761" s="3">
+        <v>46185</v>
+      </c>
+      <c r="D761" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E761" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="F761" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A762" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C762" s="3">
+        <v>46178</v>
+      </c>
+      <c r="D762" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E762" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="F762" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A763" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C763" s="3">
         <v>46189</v>
       </c>
-      <c r="D734" t="s">
-        <v>360</v>
-      </c>
-      <c r="E734" t="s">
-        <v>728</v>
-      </c>
-      <c r="F734" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A735" t="s">
-        <v>676</v>
-      </c>
-      <c r="B735" t="s">
-        <v>13</v>
-      </c>
-      <c r="C735" s="1">
-        <v>46161</v>
-      </c>
-      <c r="D735" t="s">
+      <c r="D763" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E735" t="s">
-        <v>677</v>
-      </c>
-      <c r="F735" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A736" t="s">
-        <v>383</v>
-      </c>
-      <c r="B736" t="s">
-        <v>192</v>
-      </c>
-      <c r="C736" s="1">
-        <v>46192</v>
-      </c>
-      <c r="D736" t="s">
-        <v>360</v>
-      </c>
-      <c r="E736" t="s">
-        <v>730</v>
-      </c>
-      <c r="F736" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A737" t="s">
-        <v>732</v>
-      </c>
-      <c r="B737" t="s">
-        <v>15</v>
-      </c>
-      <c r="C737" s="1">
-        <v>46184</v>
-      </c>
-      <c r="D737" t="s">
-        <v>733</v>
-      </c>
-      <c r="E737" t="s">
-        <v>734</v>
-      </c>
-      <c r="F737" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A738" t="s">
-        <v>732</v>
-      </c>
-      <c r="B738" t="s">
-        <v>15</v>
-      </c>
-      <c r="C738" s="1">
-        <v>46184</v>
-      </c>
-      <c r="D738" t="s">
-        <v>736</v>
-      </c>
-      <c r="E738" t="s">
-        <v>734</v>
-      </c>
-      <c r="F738" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A739" t="s">
-        <v>732</v>
-      </c>
-      <c r="B739" t="s">
-        <v>15</v>
-      </c>
-      <c r="C739" s="1">
-        <v>46184</v>
-      </c>
-      <c r="D739" t="s">
-        <v>386</v>
-      </c>
-      <c r="E739" t="s">
-        <v>737</v>
-      </c>
-      <c r="F739" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A740" t="s">
-        <v>732</v>
-      </c>
-      <c r="B740" t="s">
-        <v>15</v>
-      </c>
-      <c r="C740" s="1">
-        <v>46184</v>
-      </c>
-      <c r="D740" t="s">
-        <v>739</v>
-      </c>
-      <c r="E740" t="s">
-        <v>734</v>
-      </c>
-      <c r="F740" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A741" t="s">
-        <v>679</v>
-      </c>
-      <c r="B741" t="s">
+      <c r="E763" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="F763" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A764" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B764" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="C741" s="1">
-        <v>46156</v>
-      </c>
-      <c r="D741" t="s">
-        <v>387</v>
-      </c>
-      <c r="E741" t="s">
-        <v>680</v>
-      </c>
-      <c r="F741" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A742" t="s">
-        <v>133</v>
-      </c>
-      <c r="B742" t="s">
-        <v>13</v>
-      </c>
-      <c r="C742" s="1">
-        <v>46190</v>
-      </c>
-      <c r="D742" t="s">
-        <v>733</v>
-      </c>
-      <c r="E742" t="s">
-        <v>740</v>
-      </c>
-      <c r="F742" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A743" t="s">
-        <v>133</v>
-      </c>
-      <c r="B743" t="s">
-        <v>13</v>
-      </c>
-      <c r="C743" s="1">
-        <v>46190</v>
-      </c>
-      <c r="D743" t="s">
-        <v>736</v>
-      </c>
-      <c r="E743" t="s">
-        <v>740</v>
-      </c>
-      <c r="F743" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A744" t="s">
-        <v>133</v>
-      </c>
-      <c r="B744" t="s">
-        <v>13</v>
-      </c>
-      <c r="C744" s="1">
-        <v>46190</v>
-      </c>
-      <c r="D744" t="s">
-        <v>739</v>
-      </c>
-      <c r="E744" t="s">
-        <v>740</v>
-      </c>
-      <c r="F744" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A745" t="s">
-        <v>742</v>
-      </c>
-      <c r="B745" t="s">
-        <v>15</v>
-      </c>
-      <c r="C745" s="1">
-        <v>46183</v>
-      </c>
-      <c r="D745" t="s">
-        <v>386</v>
-      </c>
-      <c r="E745" t="s">
-        <v>743</v>
-      </c>
-      <c r="F745" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A746" t="s">
-        <v>359</v>
-      </c>
-      <c r="B746" t="s">
-        <v>13</v>
-      </c>
-      <c r="C746" s="1">
-        <v>46199</v>
-      </c>
-      <c r="D746" t="s">
-        <v>353</v>
-      </c>
-      <c r="E746" t="s">
-        <v>745</v>
-      </c>
-      <c r="F746" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A747" t="s">
-        <v>118</v>
-      </c>
-      <c r="B747" t="s">
-        <v>11</v>
-      </c>
-      <c r="C747" s="1">
-        <v>46162</v>
-      </c>
-      <c r="D747" t="s">
-        <v>353</v>
-      </c>
-      <c r="E747" t="s">
-        <v>682</v>
-      </c>
-      <c r="F747" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A748" t="s">
-        <v>684</v>
-      </c>
-      <c r="B748" t="s">
-        <v>54</v>
-      </c>
-      <c r="C748" s="1">
-        <v>46163</v>
-      </c>
-      <c r="D748" t="s">
-        <v>685</v>
-      </c>
-      <c r="E748" t="s">
-        <v>686</v>
-      </c>
-      <c r="F748" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A749" t="s">
-        <v>684</v>
-      </c>
-      <c r="B749" t="s">
-        <v>54</v>
-      </c>
-      <c r="C749" s="1">
-        <v>46163</v>
-      </c>
-      <c r="D749" t="s">
-        <v>388</v>
-      </c>
-      <c r="E749" t="s">
-        <v>686</v>
-      </c>
-      <c r="F749" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A750" t="s">
-        <v>688</v>
-      </c>
-      <c r="B750" t="s">
-        <v>192</v>
-      </c>
-      <c r="C750" s="1">
-        <v>46167</v>
-      </c>
-      <c r="D750" t="s">
-        <v>362</v>
-      </c>
-      <c r="E750" t="s">
-        <v>689</v>
-      </c>
-      <c r="F750" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A751" t="s">
-        <v>747</v>
-      </c>
-      <c r="B751" t="s">
-        <v>54</v>
-      </c>
-      <c r="C751" s="1">
-        <v>46193</v>
-      </c>
-      <c r="D751" t="s">
-        <v>357</v>
-      </c>
-      <c r="E751" t="s">
-        <v>748</v>
-      </c>
-      <c r="F751" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A752" t="s">
-        <v>247</v>
-      </c>
-      <c r="B752" t="s">
-        <v>192</v>
-      </c>
-      <c r="C752" s="1">
-        <v>46198</v>
-      </c>
-      <c r="D752" t="s">
-        <v>355</v>
-      </c>
-      <c r="E752" t="s">
-        <v>750</v>
-      </c>
-      <c r="F752" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A753" t="s">
-        <v>691</v>
-      </c>
-      <c r="B753" t="s">
-        <v>192</v>
-      </c>
-      <c r="C753" s="1">
-        <v>46163</v>
-      </c>
-      <c r="D753" t="s">
-        <v>378</v>
-      </c>
-      <c r="E753" t="s">
-        <v>692</v>
-      </c>
-      <c r="F753" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A754" t="s">
-        <v>751</v>
-      </c>
-      <c r="B754" t="s">
-        <v>192</v>
-      </c>
-      <c r="C754" s="1">
-        <v>46199</v>
-      </c>
-      <c r="D754" t="s">
-        <v>362</v>
-      </c>
-      <c r="E754" t="s">
-        <v>752</v>
-      </c>
-      <c r="F754" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A755" t="s">
-        <v>560</v>
-      </c>
-      <c r="B755" t="s">
-        <v>19</v>
-      </c>
-      <c r="C755" s="1">
-        <v>46199</v>
-      </c>
-      <c r="D755" t="s">
-        <v>754</v>
-      </c>
-      <c r="E755" t="s">
-        <v>755</v>
-      </c>
-      <c r="F755" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A756" t="s">
-        <v>560</v>
-      </c>
-      <c r="B756" t="s">
-        <v>19</v>
-      </c>
-      <c r="C756" s="1">
-        <v>46199</v>
-      </c>
-      <c r="D756" t="s">
-        <v>757</v>
-      </c>
-      <c r="E756" t="s">
-        <v>755</v>
-      </c>
-      <c r="F756" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A757" t="s">
-        <v>560</v>
-      </c>
-      <c r="B757" t="s">
-        <v>19</v>
-      </c>
-      <c r="C757" s="1">
-        <v>46199</v>
-      </c>
-      <c r="D757" t="s">
-        <v>388</v>
-      </c>
-      <c r="E757" t="s">
-        <v>755</v>
-      </c>
-      <c r="F757" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A758" t="s">
-        <v>82</v>
-      </c>
-      <c r="B758" t="s">
-        <v>13</v>
-      </c>
-      <c r="C758" s="1">
-        <v>46161</v>
-      </c>
-      <c r="D758" t="s">
-        <v>360</v>
-      </c>
-      <c r="E758" t="s">
-        <v>694</v>
-      </c>
-      <c r="F758" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A759" t="s">
-        <v>696</v>
-      </c>
-      <c r="B759" t="s">
-        <v>13</v>
-      </c>
-      <c r="C759" s="1">
-        <v>46157</v>
-      </c>
-      <c r="D759" t="s">
-        <v>355</v>
-      </c>
-      <c r="E759" t="s">
-        <v>697</v>
-      </c>
-      <c r="F759" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A760" t="s">
-        <v>758</v>
-      </c>
-      <c r="B760" t="s">
-        <v>759</v>
-      </c>
-      <c r="C760" s="1">
-        <v>46183</v>
-      </c>
-      <c r="D760" t="s">
-        <v>357</v>
-      </c>
-      <c r="E760" t="s">
-        <v>760</v>
-      </c>
-      <c r="F760" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A761" t="s">
-        <v>762</v>
-      </c>
-      <c r="B761" t="s">
-        <v>763</v>
-      </c>
-      <c r="C761" s="1">
-        <v>46185</v>
-      </c>
-      <c r="D761" t="s">
-        <v>357</v>
-      </c>
-      <c r="E761" t="s">
-        <v>764</v>
-      </c>
-      <c r="F761" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A762" t="s">
-        <v>637</v>
-      </c>
-      <c r="B762" t="s">
-        <v>13</v>
-      </c>
-      <c r="C762" s="1">
-        <v>46178</v>
-      </c>
-      <c r="D762" t="s">
-        <v>353</v>
-      </c>
-      <c r="E762" t="s">
-        <v>766</v>
-      </c>
-      <c r="F762" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A763" t="s">
-        <v>93</v>
-      </c>
-      <c r="B763" t="s">
-        <v>54</v>
-      </c>
-      <c r="C763" s="1">
-        <v>46189</v>
-      </c>
-      <c r="D763" t="s">
-        <v>353</v>
-      </c>
-      <c r="E763" t="s">
-        <v>768</v>
-      </c>
-      <c r="F763" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A764" t="s">
+      <c r="C764" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D764" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="E764" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="F764" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="765" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A765" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="B764" t="s">
+      <c r="B765" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="C764" s="1">
+      <c r="C765" s="3">
         <v>46177</v>
       </c>
-      <c r="D764" t="s">
-        <v>771</v>
-      </c>
-      <c r="E764" t="s">
+      <c r="D765" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="E765" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="F764" t="s">
+      <c r="F765" s="2" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A765" t="s">
+    <row r="766" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A766" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="B765" t="s">
+      <c r="B766" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="C765" s="1">
+      <c r="C766" s="3">
         <v>46177</v>
       </c>
-      <c r="D765" t="s">
-        <v>774</v>
-      </c>
-      <c r="E765" t="s">
+      <c r="D766" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="E766" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="F765" t="s">
+      <c r="F766" s="2" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A766" t="s">
-        <v>770</v>
-      </c>
-      <c r="B766" t="s">
-        <v>645</v>
-      </c>
-      <c r="C766" s="1">
-        <v>46177</v>
-      </c>
-      <c r="D766" t="s">
-        <v>775</v>
-      </c>
-      <c r="E766" t="s">
-        <v>772</v>
-      </c>
-      <c r="F766" t="s">
-        <v>773</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:F766" xr:uid="{BC693A2A-F179-40D8-AD99-91C43C3325E0}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F766">
+      <sortCondition ref="C1:C766"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F708">
     <sortCondition ref="C2:C708"/>
   </sortState>
